--- a/LexicalBand2.xlsx
+++ b/LexicalBand2.xlsx
@@ -430,7 +430,7 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>מעט</v>
+        <v>קצת</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -499,7 +499,7 @@
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>מגוון של דברים/דברות</v>
+        <v>מגוון של sth/sb</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -522,7 +522,7 @@
         <v>adv</v>
       </c>
       <c r="C6" t="str">
-        <v>חו"ל</v>
+        <v>בחו"ל</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -545,7 +545,7 @@
         <v>n</v>
       </c>
       <c r="C7" t="str">
-        <v>הדגשה</v>
+        <v>מבטא</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -568,7 +568,7 @@
         <v>v</v>
       </c>
       <c r="C8" t="str">
-        <v>קבלה</v>
+        <v>לקבל</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -637,7 +637,7 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>על פגי</v>
+        <v>על פי</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -683,7 +683,7 @@
         <v>v</v>
       </c>
       <c r="C13" t="str">
-        <v>השג</v>
+        <v>להשיג</v>
       </c>
       <c r="D13" t="str">
         <v>achievement</v>
@@ -752,7 +752,7 @@
         <v>adj</v>
       </c>
       <c r="C16" t="str">
-        <v>הסתגלות אבולוציונית</v>
+        <v>הולם</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -775,7 +775,7 @@
         <v>n</v>
       </c>
       <c r="C17" t="str">
-        <v>שם תואר</v>
+        <v>תואר</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>v</v>
       </c>
       <c r="C24" t="str">
-        <v>פרסום</v>
+        <v>לפרסם</v>
       </c>
       <c r="D24" t="str">
         <v>advertisement, ad, advert</v>
@@ -959,7 +959,7 @@
         <v>v</v>
       </c>
       <c r="C25" t="str">
-        <v>משפיע</v>
+        <v>להשפיע</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -982,7 +982,7 @@
         <v>v</v>
       </c>
       <c r="C26" t="str">
-        <v>משפיע</v>
+        <v>להשפיע</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -1005,7 +1005,7 @@
         <v>adj</v>
       </c>
       <c r="C27" t="str">
-        <v>חוֹשֵׁשׁ</v>
+        <v>מפחד</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -1028,7 +1028,7 @@
         <v>adv</v>
       </c>
       <c r="C28" t="str">
-        <v>לאחר מכן/אחרי המלחמה</v>
+        <v>לאחר מכן/אחרי המלחמה ד</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -1051,7 +1051,7 @@
         <v>v, n</v>
       </c>
       <c r="C29" t="str">
-        <v>מַטָרָה</v>
+        <v>לכוון</v>
       </c>
       <c r="D29" t="str">
         <v>aimed at</v>
@@ -1074,7 +1074,7 @@
         <v>n</v>
       </c>
       <c r="C30" t="str">
-        <v>שדה תעופה</v>
+        <v>נמל תעופה</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -1120,7 +1120,7 @@
         <v>adj</v>
       </c>
       <c r="C32" t="str">
-        <v>חי</v>
+        <v>בחיים</v>
       </c>
       <c r="D32" t="str">
         <v>living</v>
@@ -1143,7 +1143,7 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>כל טוב,</v>
+        <v>כל טוב</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -1189,7 +1189,7 @@
         <v>adv</v>
       </c>
       <c r="C35" t="str">
-        <v>&lt;x id="1"/&gt;קולית</v>
+        <v>בקול רם</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -1212,7 +1212,7 @@
         <v>v</v>
       </c>
       <c r="C36" t="str">
-        <v>אלטר</v>
+        <v>לשנות</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -1235,7 +1235,7 @@
         <v>conj</v>
       </c>
       <c r="C37" t="str">
-        <v>למרות ש</v>
+        <v>למרות</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -1258,7 +1258,7 @@
         <v>adj</v>
       </c>
       <c r="C38" t="str">
-        <v>מדהים.</v>
+        <v>מדהים</v>
       </c>
       <c r="D38" t="str">
         <v>amaze</v>
@@ -1281,7 +1281,7 @@
         <v>prep</v>
       </c>
       <c r="C39" t="str">
-        <v>באמצע</v>
+        <v>בין</v>
       </c>
       <c r="D39" t="str">
         <v/>
@@ -1304,7 +1304,7 @@
         <v>n</v>
       </c>
       <c r="C40" t="str">
-        <v>כמות</v>
+        <v>סכום</v>
       </c>
       <c r="D40" t="str">
         <v/>
@@ -1419,7 +1419,7 @@
         <v>adv</v>
       </c>
       <c r="C45" t="str">
-        <v>בכל מקרה...</v>
+        <v>בכל מקרה</v>
       </c>
       <c r="D45" t="str">
         <v/>
@@ -1442,7 +1442,7 @@
         <v>n</v>
       </c>
       <c r="C46" t="str">
-        <v>דירתי</v>
+        <v>דירה</v>
       </c>
       <c r="D46" t="str">
         <v/>
@@ -1488,7 +1488,7 @@
         <v>n</v>
       </c>
       <c r="C48" t="str">
-        <v>פעילות</v>
+        <v>פגישה</v>
       </c>
       <c r="D48" t="str">
         <v/>
@@ -1534,7 +1534,7 @@
         <v>n</v>
       </c>
       <c r="C50" t="str">
-        <v>ערבית</v>
+        <v>ערבי</v>
       </c>
       <c r="D50" t="str">
         <v/>
@@ -1557,7 +1557,7 @@
         <v>n</v>
       </c>
       <c r="C51" t="str">
-        <v>כירורגיה פלסטית</v>
+        <v>אזור</v>
       </c>
       <c r="D51" t="str">
         <v/>
@@ -1603,7 +1603,7 @@
         <v>adv, prep</v>
       </c>
       <c r="C53" t="str">
-        <v>בסביבה</v>
+        <v>מסביב</v>
       </c>
       <c r="D53" t="str">
         <v/>
@@ -1626,7 +1626,7 @@
         <v>adv</v>
       </c>
       <c r="C54" t="str">
-        <v>בערך</v>
+        <v>מסביב</v>
       </c>
       <c r="D54" t="str">
         <v/>
@@ -1695,7 +1695,7 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>כמה שיותר / מהר / בקרוב וכו'</v>
+        <v>כמה שיותר / מהר / בהקדם וכו'</v>
       </c>
       <c r="D57" t="str">
         <v/>
@@ -1718,7 +1718,7 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>ברגע ש</v>
+        <v>ברגע</v>
       </c>
       <c r="D58" t="str">
         <v/>
@@ -1787,7 +1787,7 @@
         <v>prep</v>
       </c>
       <c r="C61" t="str">
-        <v>ב-</v>
+        <v>ב</v>
       </c>
       <c r="D61" t="str">
         <v/>
@@ -1833,7 +1833,7 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>עכשיו (akhsháv)</v>
+        <v>כיום</v>
       </c>
       <c r="D63" t="str">
         <v/>
@@ -1856,7 +1856,7 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>"לא כרגע.</v>
+        <v>כרגע</v>
       </c>
       <c r="D64" t="str">
         <v/>
@@ -1879,7 +1879,7 @@
         <v>n</v>
       </c>
       <c r="C65" t="str">
-        <v>קשב</v>
+        <v>תשומת לב</v>
       </c>
       <c r="D65" t="str">
         <v/>
@@ -1902,7 +1902,7 @@
         <v>exclam</v>
       </c>
       <c r="C66" t="str">
-        <v>שימו לב!</v>
+        <v>תשומת לב!</v>
       </c>
       <c r="D66" t="str">
         <v/>
@@ -1971,7 +1971,7 @@
         <v>n</v>
       </c>
       <c r="C69" t="str">
-        <v>מחבר/ת</v>
+        <v>מחבר</v>
       </c>
       <c r="D69" t="str">
         <v/>
@@ -1994,7 +1994,7 @@
         <v>adj</v>
       </c>
       <c r="C70" t="str">
-        <v>נותרו</v>
+        <v>זמין</v>
       </c>
       <c r="D70" t="str">
         <v/>
@@ -2017,7 +2017,7 @@
         <v>adj</v>
       </c>
       <c r="C71" t="str">
-        <v>ערנות</v>
+        <v>ער</v>
       </c>
       <c r="D71" t="str">
         <v/>
@@ -2040,7 +2040,7 @@
         <v>adv</v>
       </c>
       <c r="C72" t="str">
-        <v>לא נמצא</v>
+        <v>רחוק</v>
       </c>
       <c r="D72" t="str">
         <v>two weeks/five hours, etc. away</v>
@@ -2063,7 +2063,7 @@
         <v>adj</v>
       </c>
       <c r="C73" t="str">
-        <v>גב</v>
+        <v>מאחור</v>
       </c>
       <c r="D73" t="str">
         <v/>
@@ -2201,7 +2201,7 @@
         <v>n</v>
       </c>
       <c r="C79" t="str">
-        <v>מנגל</v>
+        <v>ברביקיו</v>
       </c>
       <c r="D79" t="str">
         <v/>
@@ -2316,7 +2316,7 @@
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>להיות מסוגל לעשות משהו</v>
+        <v>להיות מסוגל לעשות דבר</v>
       </c>
       <c r="D84" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>להיות משוגע על מישהו/מישהו</v>
+        <v>להשתגע על sb/sth</v>
       </c>
       <c r="D85" t="str">
         <v/>
@@ -2362,7 +2362,7 @@
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>להיות ממוקם בתוך / ליד / על / וכו'.</v>
+        <v>להיות ממוקם ב / ליד / על / וכו '.</v>
       </c>
       <c r="D86" t="str">
         <v/>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>להיות עשוי מ</v>
+        <v>להיות עשוי</v>
       </c>
       <c r="D87" t="str">
         <v/>
@@ -2431,7 +2431,7 @@
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>להיות אחראי על משהו/לעשות משהו</v>
+        <v>להיות אחראי על sb/sth/עשיית sth</v>
       </c>
       <c r="D89" t="str">
         <v/>
@@ -2454,7 +2454,7 @@
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>אמור לעשות משהו</v>
+        <v>אמור לעשות דבר</v>
       </c>
       <c r="D90" t="str">
         <v/>
@@ -2477,7 +2477,7 @@
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>לא להיות מסוגל לעשות משהו</v>
+        <v>לא מסוגל לעשות דבר</v>
       </c>
       <c r="D91" t="str">
         <v/>
@@ -2500,7 +2500,7 @@
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>להיות רגיל לעשות משהו</v>
+        <v>לשמש ל-sb/sth/לעשות sth</v>
       </c>
       <c r="D92" t="str">
         <v/>
@@ -2523,7 +2523,7 @@
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>להיות מוכן (לעשות משהו)</v>
+        <v>להיות מוכן</v>
       </c>
       <c r="D93" t="str">
         <v/>
@@ -2592,7 +2592,7 @@
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>להיות טועה</v>
+        <v>לטעות</v>
       </c>
       <c r="D96" t="str">
         <v/>
@@ -2615,7 +2615,7 @@
         <v>aux v</v>
       </c>
       <c r="C97" t="str">
-        <v>ע"י</v>
+        <v>להיות</v>
       </c>
       <c r="D97" t="str">
         <v/>
@@ -2822,7 +2822,7 @@
         <v>adv</v>
       </c>
       <c r="C106" t="str">
-        <v>בהמשך</v>
+        <v>מתחת</v>
       </c>
       <c r="D106" t="str">
         <v/>
@@ -2845,7 +2845,7 @@
         <v>prep</v>
       </c>
       <c r="C107" t="str">
-        <v>חוץ מזה</v>
+        <v>ליד</v>
       </c>
       <c r="D107" t="str">
         <v/>
@@ -3006,7 +3006,7 @@
         <v>n</v>
       </c>
       <c r="C114" t="str">
-        <v>מרכב</v>
+        <v>גוף</v>
       </c>
       <c r="D114" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>v</v>
       </c>
       <c r="C115" t="str">
-        <v>פורונקל</v>
+        <v>רתיחה</v>
       </c>
       <c r="D115" t="str">
         <v/>
@@ -3075,7 +3075,7 @@
         <v>n</v>
       </c>
       <c r="C117" t="str">
-        <v>בעיטה</v>
+        <v>מגף</v>
       </c>
       <c r="D117" t="str">
         <v/>
@@ -3098,7 +3098,7 @@
         <v>n</v>
       </c>
       <c r="C118" t="str">
-        <v>קצה</v>
+        <v>גבול</v>
       </c>
       <c r="D118" t="str">
         <v/>
@@ -3121,7 +3121,7 @@
         <v>v</v>
       </c>
       <c r="C119" t="str">
-        <v>השאלה</v>
+        <v>ללוות</v>
       </c>
       <c r="D119" t="str">
         <v/>
@@ -3190,7 +3190,7 @@
         <v>n</v>
       </c>
       <c r="C122" t="str">
-        <v>חבר (m)</v>
+        <v>החבר</v>
       </c>
       <c r="D122" t="str">
         <v/>
@@ -3236,7 +3236,7 @@
         <v>n</v>
       </c>
       <c r="C124" t="str">
-        <v>סניף</v>
+        <v>ענף</v>
       </c>
       <c r="D124" t="str">
         <v/>
@@ -3282,7 +3282,7 @@
         <v>n</v>
       </c>
       <c r="C126" t="str">
-        <v>לשבור</v>
+        <v>הפסקה</v>
       </c>
       <c r="D126" t="str">
         <v/>
@@ -3305,7 +3305,7 @@
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>שבירה</v>
+        <v>להתקלקל</v>
       </c>
       <c r="D127" t="str">
         <v/>
@@ -3328,7 +3328,7 @@
         <v>n</v>
       </c>
       <c r="C128" t="str">
-        <v>גשר</v>
+        <v>לגשר</v>
       </c>
       <c r="D128" t="str">
         <v/>
@@ -3351,7 +3351,7 @@
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>להחזיר משהו או להחזיר משהו</v>
+        <v>להחזיר sth או להחזיר sth בחזרה</v>
       </c>
       <c r="D129" t="str">
         <v/>
@@ -3397,7 +3397,7 @@
         <v>v</v>
       </c>
       <c r="C131" t="str">
-        <v>צרוב</v>
+        <v>לשרוף</v>
       </c>
       <c r="D131" t="str">
         <v/>
@@ -3466,7 +3466,7 @@
         <v>prep</v>
       </c>
       <c r="C134" t="str">
-        <v>על ידי</v>
+        <v>ליד</v>
       </c>
       <c r="D134" t="str">
         <v/>
@@ -3489,7 +3489,7 @@
         <v>prep</v>
       </c>
       <c r="C135" t="str">
-        <v>על ידי</v>
+        <v>ליד</v>
       </c>
       <c r="D135" t="str">
         <v/>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>דרך אגב.</v>
+        <v>אגב</v>
       </c>
       <c r="D137" t="str">
         <v/>
@@ -3581,7 +3581,7 @@
         <v>n</v>
       </c>
       <c r="C139" t="str">
-        <v>יומן</v>
+        <v>לוח שנה</v>
       </c>
       <c r="D139" t="str">
         <v/>
@@ -3604,7 +3604,7 @@
         <v>v</v>
       </c>
       <c r="C140" t="str">
-        <v>סטנסיליםStencils</v>
+        <v>להתקשר</v>
       </c>
       <c r="D140" t="str">
         <v/>
@@ -3627,7 +3627,7 @@
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>להתקשר בחזרה (sb) או להתקשר בחזרה (sb)</v>
+        <v>להתקשר בחזרה</v>
       </c>
       <c r="D141" t="str">
         <v/>
@@ -3650,7 +3650,7 @@
         <v>adj</v>
       </c>
       <c r="C142" t="str">
-        <v>נעה</v>
+        <v>רגוע</v>
       </c>
       <c r="D142" t="str">
         <v/>
@@ -3673,7 +3673,7 @@
         <v>n</v>
       </c>
       <c r="C143" t="str">
-        <v>בית שימוש</v>
+        <v>יכול</v>
       </c>
       <c r="D143" t="str">
         <v/>
@@ -3765,7 +3765,7 @@
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>לא סובל/ת מישהו/מישהו</v>
+        <v>לא יכול לסבול sb/sth</v>
       </c>
       <c r="D147" t="str">
         <v/>
@@ -3788,7 +3788,7 @@
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>לא יכולה לחכות !!!</v>
+        <v>לא יכול לחכות</v>
       </c>
       <c r="D148" t="str">
         <v/>
@@ -3834,7 +3834,7 @@
         <v>n</v>
       </c>
       <c r="C150" t="str">
-        <v>אותיות רישיות</v>
+        <v>בירה</v>
       </c>
       <c r="D150" t="str">
         <v/>
@@ -3926,7 +3926,7 @@
         <v>adj</v>
       </c>
       <c r="C154" t="str">
-        <v>רשלן</v>
+        <v>רשלני</v>
       </c>
       <c r="D154" t="str">
         <v/>
@@ -3995,7 +3995,7 @@
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>ממשיכים.</v>
+        <v>להמשיך</v>
       </c>
       <c r="D157" t="str">
         <v/>
@@ -4018,7 +4018,7 @@
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>ביצוע</v>
+        <v>לבצע</v>
       </c>
       <c r="D158" t="str">
         <v/>
@@ -4041,7 +4041,7 @@
         <v>n</v>
       </c>
       <c r="C159" t="str">
-        <v>מופע</v>
+        <v>תיק</v>
       </c>
       <c r="D159" t="str">
         <v/>
@@ -4064,7 +4064,7 @@
         <v>n</v>
       </c>
       <c r="C160" t="str">
-        <v>מופע</v>
+        <v>תיק</v>
       </c>
       <c r="D160" t="str">
         <v/>
@@ -4179,7 +4179,7 @@
         <v>n</v>
       </c>
       <c r="C165" t="str">
-        <v>קתוליות</v>
+        <v>קתולי</v>
       </c>
       <c r="D165" t="str">
         <v/>
@@ -4248,7 +4248,7 @@
         <v>n</v>
       </c>
       <c r="C168" t="str">
-        <v>מאה</v>
+        <v>סנט</v>
       </c>
       <c r="D168" t="str">
         <v/>
@@ -4317,7 +4317,7 @@
         <v>adj</v>
       </c>
       <c r="C171" t="str">
-        <v>ודאי</v>
+        <v>מסויים</v>
       </c>
       <c r="D171" t="str">
         <v>certainly</v>
@@ -4363,7 +4363,7 @@
         <v>n</v>
       </c>
       <c r="C173" t="str">
-        <v>הזדמנות</v>
+        <v>סיכוי</v>
       </c>
       <c r="D173" t="str">
         <v/>
@@ -4386,7 +4386,7 @@
         <v>v</v>
       </c>
       <c r="C174" t="str">
-        <v>עודף</v>
+        <v>לשנות</v>
       </c>
       <c r="D174" t="str">
         <v/>
@@ -4409,7 +4409,7 @@
         <v>n</v>
       </c>
       <c r="C175" t="str">
-        <v>עודף</v>
+        <v>לשנות</v>
       </c>
       <c r="D175" t="str">
         <v/>
@@ -4455,7 +4455,7 @@
         <v>n</v>
       </c>
       <c r="C177" t="str">
-        <v>תו</v>
+        <v>אופי</v>
       </c>
       <c r="D177" t="str">
         <v/>
@@ -4478,7 +4478,7 @@
         <v>v, n</v>
       </c>
       <c r="C178" t="str">
-        <v>מטען חשמלי</v>
+        <v>תשלום</v>
       </c>
       <c r="D178" t="str">
         <v/>
@@ -4501,7 +4501,7 @@
         <v>v, n</v>
       </c>
       <c r="C179" t="str">
-        <v>צ’אט</v>
+        <v>לשוחח</v>
       </c>
       <c r="D179" t="str">
         <v/>
@@ -4524,7 +4524,7 @@
         <v>v ,n</v>
       </c>
       <c r="C180" t="str">
-        <v>שיק</v>
+        <v>לבדוק</v>
       </c>
       <c r="D180" t="str">
         <v/>
@@ -4547,7 +4547,7 @@
         <v>n</v>
       </c>
       <c r="C181" t="str">
-        <v>צ'ק אין (דלפק)</v>
+        <v>צ'ק-אין</v>
       </c>
       <c r="D181" t="str">
         <v/>
@@ -4616,7 +4616,7 @@
         <v>n</v>
       </c>
       <c r="C184" t="str">
-        <v>צ'יפ</v>
+        <v>שבב</v>
       </c>
       <c r="D184" t="str">
         <v/>
@@ -4639,7 +4639,7 @@
         <v>n</v>
       </c>
       <c r="C185" t="str">
-        <v>סטנסיליםStencils</v>
+        <v>בחירה</v>
       </c>
       <c r="D185" t="str">
         <v/>
@@ -4662,7 +4662,7 @@
         <v>n</v>
       </c>
       <c r="C186" t="str">
-        <v>נוצריה</v>
+        <v>נוצרי</v>
       </c>
       <c r="D186" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>adj</v>
       </c>
       <c r="C191" t="str">
-        <v>נקה/י חיפוש</v>
+        <v>ברור</v>
       </c>
       <c r="D191" t="str">
         <v>clearly</v>
@@ -4800,7 +4800,7 @@
         <v>v, n</v>
       </c>
       <c r="C192" t="str">
-        <v>לחיצה</v>
+        <v>נקישה</v>
       </c>
       <c r="D192" t="str">
         <v/>
@@ -4846,7 +4846,7 @@
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>שעת הסגירה</v>
+        <v>שעת סגירה</v>
       </c>
       <c r="D194" t="str">
         <v/>
@@ -4961,7 +4961,7 @@
         <v>n,v</v>
       </c>
       <c r="C199" t="str">
-        <v>לסרק</v>
+        <v>מסרק</v>
       </c>
       <c r="D199" t="str">
         <v/>
@@ -5076,7 +5076,7 @@
         <v>v</v>
       </c>
       <c r="C204" t="str">
-        <v>אהבתי</v>
+        <v>להשוות</v>
       </c>
       <c r="D204" t="str">
         <v>comparison</v>
@@ -5099,7 +5099,7 @@
         <v>v</v>
       </c>
       <c r="C205" t="str">
-        <v>תחרות</v>
+        <v>להתחרות</v>
       </c>
       <c r="D205" t="str">
         <v/>
@@ -5122,7 +5122,7 @@
         <v>adj</v>
       </c>
       <c r="C206" t="str">
-        <v>מלאה</v>
+        <v>מלא</v>
       </c>
       <c r="D206" t="str">
         <v>completely</v>
@@ -5191,7 +5191,7 @@
         <v>exclam</v>
       </c>
       <c r="C209" t="str">
-        <v>ברכותינו!</v>
+        <v>מזל טוב!</v>
       </c>
       <c r="D209" t="str">
         <v/>
@@ -5214,7 +5214,7 @@
         <v>n</v>
       </c>
       <c r="C210" t="str">
-        <v>מחבר</v>
+        <v>חיבור</v>
       </c>
       <c r="D210" t="str">
         <v>connect</v>
@@ -5237,7 +5237,7 @@
         <v>n, v</v>
       </c>
       <c r="C211" t="str">
-        <v>יצירת קשר</v>
+        <v>מגע</v>
       </c>
       <c r="D211" t="str">
         <v/>
@@ -5260,7 +5260,7 @@
         <v>n</v>
       </c>
       <c r="C212" t="str">
-        <v>תוכן ענינים</v>
+        <v>תוכן</v>
       </c>
       <c r="D212" t="str">
         <v/>
@@ -5306,7 +5306,7 @@
         <v>v</v>
       </c>
       <c r="C214" t="str">
-        <v>המשך</v>
+        <v>להמשיך</v>
       </c>
       <c r="D214" t="str">
         <v>continuous</v>
@@ -5352,7 +5352,7 @@
         <v>n, v</v>
       </c>
       <c r="C216" t="str">
-        <v>שליטה</v>
+        <v>לשלוט</v>
       </c>
       <c r="D216" t="str">
         <v/>
@@ -5421,7 +5421,7 @@
         <v>n, v</v>
       </c>
       <c r="C219" t="str">
-        <v>העתק</v>
+        <v>העתקה</v>
       </c>
       <c r="D219" t="str">
         <v/>
@@ -5513,7 +5513,7 @@
         <v>v, n</v>
       </c>
       <c r="C223" t="str">
-        <v>שיעול</v>
+        <v>להשתעל</v>
       </c>
       <c r="D223" t="str">
         <v/>
@@ -5536,7 +5536,7 @@
         <v>v</v>
       </c>
       <c r="C224" t="str">
-        <v>הָיָה יָכוֹל</v>
+        <v>יכול</v>
       </c>
       <c r="D224" t="str">
         <v/>
@@ -5628,7 +5628,7 @@
         <v>n, adj</v>
       </c>
       <c r="C228" t="str">
-        <v>שמנת</v>
+        <v>קרם</v>
       </c>
       <c r="D228" t="str">
         <v/>
@@ -5674,7 +5674,7 @@
         <v>n</v>
       </c>
       <c r="C230" t="str">
-        <v>זכות</v>
+        <v>אשראי</v>
       </c>
       <c r="D230" t="str">
         <v/>
@@ -5697,7 +5697,7 @@
         <v>adj, n</v>
       </c>
       <c r="C231" t="str">
-        <v>חטיף תפוחי אדמה</v>
+        <v>פריך</v>
       </c>
       <c r="D231" t="str">
         <v/>
@@ -5835,7 +5835,7 @@
         <v/>
       </c>
       <c r="C237" t="str">
-        <v>לחתוך משהו או לחתוך משהו</v>
+        <v>לחתוך sth או לחתוך sth למעלה</v>
       </c>
       <c r="D237" t="str">
         <v/>
@@ -5858,7 +5858,7 @@
         <v>adj, adv</v>
       </c>
       <c r="C238" t="str">
-        <v>יומיים</v>
+        <v>יומי</v>
       </c>
       <c r="D238" t="str">
         <v/>
@@ -5904,7 +5904,7 @@
         <v/>
       </c>
       <c r="C240" t="str">
-        <v>תאריך הלידה</v>
+        <v>תאריך לידה</v>
       </c>
       <c r="D240" t="str">
         <v/>
@@ -5927,7 +5927,7 @@
         <v>n</v>
       </c>
       <c r="C241" t="str">
-        <v>חלוקה</v>
+        <v>עסקה</v>
       </c>
       <c r="D241" t="str">
         <v/>
@@ -5950,7 +5950,7 @@
         <v>n</v>
       </c>
       <c r="C242" t="str">
-        <v>מוות</v>
+        <v>מות</v>
       </c>
       <c r="D242" t="str">
         <v/>
@@ -5973,7 +5973,7 @@
         <v>adv</v>
       </c>
       <c r="C243" t="str">
-        <v>בהחלט.</v>
+        <v>בהחלט</v>
       </c>
       <c r="D243" t="str">
         <v/>
@@ -5996,7 +5996,7 @@
         <v>n</v>
       </c>
       <c r="C244" t="str">
-        <v>מעלה</v>
+        <v>תואר</v>
       </c>
       <c r="D244" t="str">
         <v/>
@@ -6019,7 +6019,7 @@
         <v>n, v</v>
       </c>
       <c r="C245" t="str">
-        <v>תקופת עיכוב</v>
+        <v>לעכב</v>
       </c>
       <c r="D245" t="str">
         <v/>
@@ -6042,7 +6042,7 @@
         <v>v, n</v>
       </c>
       <c r="C246" t="str">
-        <v>צורך</v>
+        <v>לדרוש</v>
       </c>
       <c r="D246" t="str">
         <v/>
@@ -6065,7 +6065,7 @@
         <v>n</v>
       </c>
       <c r="C247" t="str">
-        <v>רופא שינים</v>
+        <v>רופא שיניים</v>
       </c>
       <c r="D247" t="str">
         <v/>
@@ -6088,7 +6088,7 @@
         <v>n</v>
       </c>
       <c r="C248" t="str">
-        <v>כל-בו</v>
+        <v>חנות כלבו</v>
       </c>
       <c r="D248" t="str">
         <v/>
@@ -6111,7 +6111,7 @@
         <v>adj</v>
       </c>
       <c r="C249" t="str">
-        <v>תלות</v>
+        <v>תלוי</v>
       </c>
       <c r="D249" t="str">
         <v/>
@@ -6134,7 +6134,7 @@
         <v>n</v>
       </c>
       <c r="C250" t="str">
-        <v>תיאור</v>
+        <v>תאור</v>
       </c>
       <c r="D250" t="str">
         <v/>
@@ -6203,7 +6203,7 @@
         <v>v</v>
       </c>
       <c r="C253" t="str">
-        <v>להרוס</v>
+        <v>להשמיד</v>
       </c>
       <c r="D253" t="str">
         <v/>
@@ -6226,7 +6226,7 @@
         <v>v</v>
       </c>
       <c r="C254" t="str">
-        <v>פיתוח</v>
+        <v>להתפתח</v>
       </c>
       <c r="D254" t="str">
         <v>development</v>
@@ -6318,7 +6318,7 @@
         <v>adv</v>
       </c>
       <c r="C258" t="str">
-        <v>אחרת.</v>
+        <v>אחרת</v>
       </c>
       <c r="D258" t="str">
         <v/>
@@ -6410,7 +6410,7 @@
         <v>n</v>
       </c>
       <c r="C262" t="str">
-        <v>דיפלומה</v>
+        <v>תעודה</v>
       </c>
       <c r="D262" t="str">
         <v/>
@@ -6433,7 +6433,7 @@
         <v>v</v>
       </c>
       <c r="C263" t="str">
-        <v>ישירות</v>
+        <v>ישיר</v>
       </c>
       <c r="D263" t="str">
         <v/>
@@ -6456,7 +6456,7 @@
         <v>n</v>
       </c>
       <c r="C264" t="str">
-        <v>הוראות הכנה</v>
+        <v>כיוונים</v>
       </c>
       <c r="D264" t="str">
         <v/>
@@ -6479,7 +6479,7 @@
         <v>n</v>
       </c>
       <c r="C265" t="str">
-        <v>במאי</v>
+        <v>דירקטור</v>
       </c>
       <c r="D265" t="str">
         <v/>
@@ -6502,7 +6502,7 @@
         <v>n</v>
       </c>
       <c r="C266" t="str">
-        <v>לכלוך</v>
+        <v>עפר</v>
       </c>
       <c r="D266" t="str">
         <v>dirty</v>
@@ -6525,7 +6525,7 @@
         <v>v</v>
       </c>
       <c r="C267" t="str">
-        <v>להיעלם</v>
+        <v>להעלם</v>
       </c>
       <c r="D267" t="str">
         <v/>
@@ -6548,7 +6548,7 @@
         <v>n</v>
       </c>
       <c r="C268" t="str">
-        <v>מבצע</v>
+        <v>דיסקונט</v>
       </c>
       <c r="D268" t="str">
         <v/>
@@ -6571,7 +6571,7 @@
         <v>v</v>
       </c>
       <c r="C269" t="str">
-        <v>הצעות</v>
+        <v>לגלות</v>
       </c>
       <c r="D269" t="str">
         <v/>
@@ -6594,7 +6594,7 @@
         <v>v</v>
       </c>
       <c r="C270" t="str">
-        <v>דיבייט</v>
+        <v>לדון</v>
       </c>
       <c r="D270" t="str">
         <v>discussion</v>
@@ -6640,7 +6640,7 @@
         <v>n</v>
       </c>
       <c r="C272" t="str">
-        <v>צלחת.</v>
+        <v>מנה</v>
       </c>
       <c r="D272" t="str">
         <v/>
@@ -6732,7 +6732,7 @@
         <v>n</v>
       </c>
       <c r="C276" t="str">
-        <v>מגירה</v>
+        <v>מגרה</v>
       </c>
       <c r="D276" t="str">
         <v/>
@@ -6778,7 +6778,7 @@
         <v>n</v>
       </c>
       <c r="C278" t="str">
-        <v>לנהוג</v>
+        <v>נסיעה</v>
       </c>
       <c r="D278" t="str">
         <v/>
@@ -6801,7 +6801,7 @@
         <v>v</v>
       </c>
       <c r="C279" t="str">
-        <v>להפיל</v>
+        <v>ירידה</v>
       </c>
       <c r="D279" t="str">
         <v/>
@@ -6847,7 +6847,7 @@
         <v>n</v>
       </c>
       <c r="C281" t="str">
-        <v>דרוזים</v>
+        <v>דרוזי</v>
       </c>
       <c r="D281" t="str">
         <v/>
@@ -6870,7 +6870,7 @@
         <v>n</v>
       </c>
       <c r="C282" t="str">
-        <v>ברווז</v>
+        <v>להתכופף</v>
       </c>
       <c r="D282" t="str">
         <v/>
@@ -6893,7 +6893,7 @@
         <v>adj</v>
       </c>
       <c r="C283" t="str">
-        <v>אחר המועד</v>
+        <v>בשל</v>
       </c>
       <c r="D283" t="str">
         <v/>
@@ -6939,7 +6939,7 @@
         <v/>
       </c>
       <c r="C285" t="str">
-        <v>אחד את השני.</v>
+        <v>אחד את השני</v>
       </c>
       <c r="D285" t="str">
         <v/>
@@ -6962,7 +6962,7 @@
         <v>v</v>
       </c>
       <c r="C286" t="str">
-        <v>זכות</v>
+        <v>לזכות</v>
       </c>
       <c r="D286" t="str">
         <v/>
@@ -6985,7 +6985,7 @@
         <v>n</v>
       </c>
       <c r="C287" t="str">
-        <v>עגילים</v>
+        <v>עגיל</v>
       </c>
       <c r="D287" t="str">
         <v/>
@@ -7008,7 +7008,7 @@
         <v>n</v>
       </c>
       <c r="C288" t="str">
-        <v>אדמה</v>
+        <v>כדור הארץ</v>
       </c>
       <c r="D288" t="str">
         <v/>
@@ -7054,7 +7054,7 @@
         <v>n</v>
       </c>
       <c r="C290" t="str">
-        <v>השפעה</v>
+        <v>אפקט</v>
       </c>
       <c r="D290" t="str">
         <v/>
@@ -7077,7 +7077,7 @@
         <v>n</v>
       </c>
       <c r="C291" t="str">
-        <v>בחירות</v>
+        <v>בחירה</v>
       </c>
       <c r="D291" t="str">
         <v/>
@@ -7146,7 +7146,7 @@
         <v>n</v>
       </c>
       <c r="C294" t="str">
-        <v>אימייל</v>
+        <v>אלקטרוני</v>
       </c>
       <c r="D294" t="str">
         <v/>
@@ -7192,7 +7192,7 @@
         <v>v</v>
       </c>
       <c r="C296" t="str">
-        <v>החל</v>
+        <v>להעסיק</v>
       </c>
       <c r="D296" t="str">
         <v>employee employer</v>
@@ -7422,7 +7422,7 @@
         <v>n</v>
       </c>
       <c r="C306" t="str">
-        <v>אירו</v>
+        <v>יורו</v>
       </c>
       <c r="D306" t="str">
         <v/>
@@ -7445,7 +7445,7 @@
         <v>adv</v>
       </c>
       <c r="C307" t="str">
-        <v>זוגי (zoogi)</v>
+        <v>אפילו</v>
       </c>
       <c r="D307" t="str">
         <v/>
@@ -7468,7 +7468,7 @@
         <v>n</v>
       </c>
       <c r="C308" t="str">
-        <v>אירוע</v>
+        <v>מקרה</v>
       </c>
       <c r="D308" t="str">
         <v/>
@@ -7514,7 +7514,7 @@
         <v>adj</v>
       </c>
       <c r="C310" t="str">
-        <v>במדויק</v>
+        <v>מדויק</v>
       </c>
       <c r="D310" t="str">
         <v/>
@@ -7537,7 +7537,7 @@
         <v>v</v>
       </c>
       <c r="C311" t="str">
-        <v>מבחן</v>
+        <v>לבחון</v>
       </c>
       <c r="D311" t="str">
         <v/>
@@ -7560,7 +7560,7 @@
         <v>adj</v>
       </c>
       <c r="C312" t="str">
-        <v>עירור</v>
+        <v>נרגש</v>
       </c>
       <c r="D312" t="str">
         <v>exciting</v>
@@ -7583,7 +7583,7 @@
         <v>n</v>
       </c>
       <c r="C313" t="str">
-        <v>תרגיל</v>
+        <v>פעילות גופנית</v>
       </c>
       <c r="D313" t="str">
         <v/>
@@ -7606,7 +7606,7 @@
         <v>n</v>
       </c>
       <c r="C314" t="str">
-        <v>לצאת</v>
+        <v>יציאה</v>
       </c>
       <c r="D314" t="str">
         <v/>
@@ -7721,7 +7721,7 @@
         <v>v</v>
       </c>
       <c r="C319" t="str">
-        <v>גלה/י</v>
+        <v>לחקור</v>
       </c>
       <c r="D319" t="str">
         <v/>
@@ -7744,7 +7744,7 @@
         <v>v</v>
       </c>
       <c r="C320" t="str">
-        <v>אקספרס</v>
+        <v>להביע</v>
       </c>
       <c r="D320" t="str">
         <v/>
@@ -7813,7 +7813,7 @@
         <v>n</v>
       </c>
       <c r="C323" t="str">
-        <v>בית חרושת</v>
+        <v>מפעל</v>
       </c>
       <c r="D323" t="str">
         <v/>
@@ -7836,7 +7836,7 @@
         <v>adj</v>
       </c>
       <c r="C324" t="str">
-        <v>בהיר</v>
+        <v>הוגן</v>
       </c>
       <c r="D324" t="str">
         <v/>
@@ -7882,7 +7882,7 @@
         <v>adv</v>
       </c>
       <c r="C326" t="str">
-        <v>לְמַדַי</v>
+        <v>בהגינות</v>
       </c>
       <c r="D326" t="str">
         <v/>
@@ -7905,7 +7905,7 @@
         <v>n</v>
       </c>
       <c r="C327" t="str">
-        <v>ליפול</v>
+        <v>נפילה</v>
       </c>
       <c r="D327" t="str">
         <v/>
@@ -7951,7 +7951,7 @@
         <v>adj</v>
       </c>
       <c r="C329" t="str">
-        <v>שרק</v>
+        <v>שקר</v>
       </c>
       <c r="D329" t="str">
         <v/>
@@ -7974,7 +7974,7 @@
         <v>adj</v>
       </c>
       <c r="C330" t="str">
-        <v>נחמד!</v>
+        <v>מוכר</v>
       </c>
       <c r="D330" t="str">
         <v/>
@@ -7997,7 +7997,7 @@
         <v>n</v>
       </c>
       <c r="C331" t="str">
-        <v>השטחה</v>
+        <v>אוהד</v>
       </c>
       <c r="D331" t="str">
         <v/>
@@ -8020,7 +8020,7 @@
         <v>adj</v>
       </c>
       <c r="C332" t="str">
-        <v>פנטסטי.</v>
+        <v>פנטסטי</v>
       </c>
       <c r="D332" t="str">
         <v/>
@@ -8043,7 +8043,7 @@
         <v>n</v>
       </c>
       <c r="C333" t="str">
-        <v>אופן</v>
+        <v>לעצב</v>
       </c>
       <c r="D333" t="str">
         <v/>
@@ -8135,7 +8135,7 @@
         <v>v,n</v>
       </c>
       <c r="C337" t="str">
-        <v>להלחם!</v>
+        <v>להילחם</v>
       </c>
       <c r="D337" t="str">
         <v/>
@@ -8158,7 +8158,7 @@
         <v/>
       </c>
       <c r="C338" t="str">
-        <v>למלא/להוציא משהו או למלא/להוציא משהו</v>
+        <v>למלא/לחוץ sth או למלא sth in/out</v>
       </c>
       <c r="D338" t="str">
         <v/>
@@ -8181,7 +8181,7 @@
         <v>adj</v>
       </c>
       <c r="C339" t="str">
-        <v>מקושר</v>
+        <v>בסדר</v>
       </c>
       <c r="D339" t="str">
         <v/>
@@ -8204,7 +8204,7 @@
         <v>adj</v>
       </c>
       <c r="C340" t="str">
-        <v>מקושר</v>
+        <v>בסדר</v>
       </c>
       <c r="D340" t="str">
         <v/>
@@ -8227,7 +8227,7 @@
         <v/>
       </c>
       <c r="C341" t="str">
-        <v>קודם כל,</v>
+        <v>קודם כל</v>
       </c>
       <c r="D341" t="str">
         <v/>
@@ -8250,7 +8250,7 @@
         <v>v</v>
       </c>
       <c r="C342" t="str">
-        <v>דג</v>
+        <v>לדוג</v>
       </c>
       <c r="D342" t="str">
         <v/>
@@ -8296,7 +8296,7 @@
         <v>v</v>
       </c>
       <c r="C344" t="str">
-        <v>התאמה</v>
+        <v>להתאים</v>
       </c>
       <c r="D344" t="str">
         <v/>
@@ -8342,7 +8342,7 @@
         <v>n</v>
       </c>
       <c r="C346" t="str">
-        <v>סימון בדגל</v>
+        <v>דגל</v>
       </c>
       <c r="D346" t="str">
         <v/>
@@ -8365,7 +8365,7 @@
         <v>adj</v>
       </c>
       <c r="C347" t="str">
-        <v>דירה</v>
+        <v>שטוח</v>
       </c>
       <c r="D347" t="str">
         <v/>
@@ -8388,7 +8388,7 @@
         <v>n</v>
       </c>
       <c r="C348" t="str">
-        <v>תעופה</v>
+        <v>טיסה</v>
       </c>
       <c r="D348" t="str">
         <v/>
@@ -8457,7 +8457,7 @@
         <v>v</v>
       </c>
       <c r="C351" t="str">
-        <v>עקוב</v>
+        <v>לעקוב</v>
       </c>
       <c r="D351" t="str">
         <v/>
@@ -8480,7 +8480,7 @@
         <v>prep</v>
       </c>
       <c r="C352" t="str">
-        <v>ל</v>
+        <v>עבור</v>
       </c>
       <c r="D352" t="str">
         <v/>
@@ -8664,7 +8664,7 @@
         <v>adj</v>
       </c>
       <c r="C360" t="str">
-        <v>רענן.</v>
+        <v>צח</v>
       </c>
       <c r="D360" t="str">
         <v/>
@@ -8687,7 +8687,7 @@
         <v>adj</v>
       </c>
       <c r="C361" t="str">
-        <v>רענן.</v>
+        <v>צח</v>
       </c>
       <c r="D361" t="str">
         <v/>
@@ -8710,7 +8710,7 @@
         <v/>
       </c>
       <c r="C362" t="str">
-        <v>אוויר צח.................................................................................................</v>
+        <v>אוויר צח</v>
       </c>
       <c r="D362" t="str">
         <v/>
@@ -8733,7 +8733,7 @@
         <v>n</v>
       </c>
       <c r="C363" t="str">
-        <v>ידידות</v>
+        <v>חברות</v>
       </c>
       <c r="D363" t="str">
         <v/>
@@ -8756,7 +8756,7 @@
         <v>prep</v>
       </c>
       <c r="C364" t="str">
-        <v>מאת</v>
+        <v>מ</v>
       </c>
       <c r="D364" t="str">
         <v/>
@@ -8779,7 +8779,7 @@
         <v/>
       </c>
       <c r="C365" t="str">
-        <v>נקודה</v>
+        <v>סוף פסוק</v>
       </c>
       <c r="D365" t="str">
         <v/>
@@ -8802,7 +8802,7 @@
         <v>adv</v>
       </c>
       <c r="C366" t="str">
-        <v>במלאו</v>
+        <v>לגמרי</v>
       </c>
       <c r="D366" t="str">
         <v>in full</v>
@@ -8848,7 +8848,7 @@
         <v>n</v>
       </c>
       <c r="C368" t="str">
-        <v>ריהוט</v>
+        <v>רהיטים</v>
       </c>
       <c r="D368" t="str">
         <v/>
@@ -8871,7 +8871,7 @@
         <v>v</v>
       </c>
       <c r="C369" t="str">
-        <v>לְהַשִׂיג</v>
+        <v>להרוויח</v>
       </c>
       <c r="D369" t="str">
         <v/>
@@ -8894,7 +8894,7 @@
         <v>n</v>
       </c>
       <c r="C370" t="str">
-        <v>מרווח# #מגעים</v>
+        <v>פער</v>
       </c>
       <c r="D370" t="str">
         <v/>
@@ -8917,7 +8917,7 @@
         <v>n</v>
       </c>
       <c r="C371" t="str">
-        <v>פסולת</v>
+        <v>אשפה</v>
       </c>
       <c r="D371" t="str">
         <v/>
@@ -9032,7 +9032,7 @@
         <v>n</v>
       </c>
       <c r="C376" t="str">
-        <v>גיאוגרפיה</v>
+        <v>גאוגרפיה</v>
       </c>
       <c r="D376" t="str">
         <v/>
@@ -9055,7 +9055,7 @@
         <v/>
       </c>
       <c r="C377" t="str">
-        <v>לחזור משהו או לחזור משהו</v>
+        <v>חזור sth או קבל sth בחזרה</v>
       </c>
       <c r="D377" t="str">
         <v/>
@@ -9101,7 +9101,7 @@
         <v/>
       </c>
       <c r="C379" t="str">
-        <v>להכיר מישהו/מישהו</v>
+        <v>להכיר את sb/sth</v>
       </c>
       <c r="D379" t="str">
         <v/>
@@ -9124,7 +9124,7 @@
         <v/>
       </c>
       <c r="C380" t="str">
-        <v>...להיפגש.</v>
+        <v>להפגש</v>
       </c>
       <c r="D380" t="str">
         <v/>
@@ -9170,7 +9170,7 @@
         <v/>
       </c>
       <c r="C382" t="str">
-        <v>להחזיר משהו או להחזיר משהו</v>
+        <v>להחזיר sth או להחזיר sth</v>
       </c>
       <c r="D382" t="str">
         <v/>
@@ -9216,7 +9216,7 @@
         <v/>
       </c>
       <c r="C384" t="str">
-        <v>לנסוע לחו&amp;quot;ל</v>
+        <v>לנסוע לחו"ל</v>
       </c>
       <c r="D384" t="str">
         <v/>
@@ -9239,7 +9239,7 @@
         <v/>
       </c>
       <c r="C385" t="str">
-        <v>חזרה</v>
+        <v>לחזור</v>
       </c>
       <c r="D385" t="str">
         <v/>
@@ -9262,7 +9262,7 @@
         <v>n</v>
       </c>
       <c r="C386" t="str">
-        <v>אני שייך לאלוהים</v>
+        <v>אל</v>
       </c>
       <c r="D386" t="str">
         <v/>
@@ -9331,7 +9331,7 @@
         <v>adj</v>
       </c>
       <c r="C389" t="str">
-        <v>גולדן</v>
+        <v>זהוב</v>
       </c>
       <c r="D389" t="str">
         <v/>
@@ -9354,7 +9354,7 @@
         <v/>
       </c>
       <c r="C390" t="str">
-        <v>נאה</v>
+        <v>נאה למראה</v>
       </c>
       <c r="D390" t="str">
         <v/>
@@ -9423,7 +9423,7 @@
         <v>adj</v>
       </c>
       <c r="C393" t="str">
-        <v>גדול</v>
+        <v>נהדר</v>
       </c>
       <c r="D393" t="str">
         <v/>
@@ -9446,7 +9446,7 @@
         <v>adj</v>
       </c>
       <c r="C394" t="str">
-        <v>גדול</v>
+        <v>נהדר</v>
       </c>
       <c r="D394" t="str">
         <v>greatly</v>
@@ -9492,7 +9492,7 @@
         <v>n</v>
       </c>
       <c r="C396" t="str">
-        <v>גארד</v>
+        <v>משמר</v>
       </c>
       <c r="D396" t="str">
         <v/>
@@ -9515,7 +9515,7 @@
         <v>n</v>
       </c>
       <c r="C397" t="str">
-        <v>משתתף</v>
+        <v>אורח</v>
       </c>
       <c r="D397" t="str">
         <v/>
@@ -9538,7 +9538,7 @@
         <v>n</v>
       </c>
       <c r="C398" t="str">
-        <v>משתתף</v>
+        <v>אורח</v>
       </c>
       <c r="D398" t="str">
         <v/>
@@ -9561,7 +9561,7 @@
         <v>n, v</v>
       </c>
       <c r="C399" t="str">
-        <v>המדריך</v>
+        <v>מדריך</v>
       </c>
       <c r="D399" t="str">
         <v/>
@@ -9584,7 +9584,7 @@
         <v>n</v>
       </c>
       <c r="C400" t="str">
-        <v>גיא</v>
+        <v>בחור</v>
       </c>
       <c r="D400" t="str">
         <v/>
@@ -9607,7 +9607,7 @@
         <v>n</v>
       </c>
       <c r="C401" t="str">
-        <v>מכון כושר</v>
+        <v>חדר כושר</v>
       </c>
       <c r="D401" t="str">
         <v/>
@@ -9653,7 +9653,7 @@
         <v>n</v>
       </c>
       <c r="C403" t="str">
-        <v>מבואה</v>
+        <v>אולם</v>
       </c>
       <c r="D403" t="str">
         <v/>
@@ -9676,7 +9676,7 @@
         <v/>
       </c>
       <c r="C404" t="str">
-        <v>לחלק משהו או לחלק משהו</v>
+        <v>לחלק sth או לחלק sth</v>
       </c>
       <c r="D404" t="str">
         <v/>
@@ -9791,7 +9791,7 @@
         <v>n</v>
       </c>
       <c r="C409" t="str">
-        <v>לשנוא</v>
+        <v>שנאה</v>
       </c>
       <c r="D409" t="str">
         <v/>
@@ -9814,7 +9814,7 @@
         <v/>
       </c>
       <c r="C410" t="str">
-        <v>צריך לעשות משהו</v>
+        <v>יש</v>
       </c>
       <c r="D410" t="str">
         <v/>
@@ -9837,7 +9837,7 @@
         <v/>
       </c>
       <c r="C411" t="str">
-        <v>יש לי שאלה / רעיון / תוכנית</v>
+        <v>יש לך שאלה/רעיון/תוכנית</v>
       </c>
       <c r="D411" t="str">
         <v/>
@@ -9860,7 +9860,7 @@
         <v/>
       </c>
       <c r="C412" t="str">
-        <v>לקיים שיחה / פגישה / פגישה</v>
+        <v>לנהל שיחה / פגישה / פגישה</v>
       </c>
       <c r="D412" t="str">
         <v/>
@@ -9883,7 +9883,7 @@
         <v/>
       </c>
       <c r="C413" t="str">
-        <v>יש לי / יש לי</v>
+        <v>יש/יש</v>
       </c>
       <c r="D413" t="str">
         <v/>
@@ -10044,7 +10044,7 @@
         <v>n</v>
       </c>
       <c r="C420" t="str">
-        <v>שימוע:</v>
+        <v>שמיעה</v>
       </c>
       <c r="D420" t="str">
         <v/>
@@ -10136,7 +10136,7 @@
         <v>adj</v>
       </c>
       <c r="C424" t="str">
-        <v>עוזר...</v>
+        <v>מועיל</v>
       </c>
       <c r="D424" t="str">
         <v/>
@@ -10251,7 +10251,7 @@
         <v>n</v>
       </c>
       <c r="C429" t="str">
-        <v>כביש מהיר</v>
+        <v>כביש</v>
       </c>
       <c r="D429" t="str">
         <v/>
@@ -10366,7 +10366,7 @@
         <v>adj</v>
       </c>
       <c r="C434" t="str">
-        <v>מַחרִיד?</v>
+        <v>מחריד</v>
       </c>
       <c r="D434" t="str">
         <v/>
@@ -10389,7 +10389,7 @@
         <v>n</v>
       </c>
       <c r="C435" t="str">
-        <v>עקייב</v>
+        <v>עקרת הבית</v>
       </c>
       <c r="D435" t="str">
         <v/>
@@ -10412,7 +10412,7 @@
         <v/>
       </c>
       <c r="C436" t="str">
-        <v>מה שלומך?</v>
+        <v>איך אתה מסתדר?</v>
       </c>
       <c r="D436" t="str">
         <v/>
@@ -10435,7 +10435,7 @@
         <v/>
       </c>
       <c r="C437" t="str">
-        <v>איך/על מה?</v>
+        <v>איך/מה לגבי?</v>
       </c>
       <c r="D437" t="str">
         <v/>
@@ -10458,7 +10458,7 @@
         <v>adv, conj</v>
       </c>
       <c r="C438" t="str">
-        <v>בכל אופן</v>
+        <v>אולם</v>
       </c>
       <c r="D438" t="str">
         <v/>
@@ -10481,7 +10481,7 @@
         <v>v, n</v>
       </c>
       <c r="C439" t="str">
-        <v>חיבוק</v>
+        <v>לחבק</v>
       </c>
       <c r="D439" t="str">
         <v/>
@@ -10504,7 +10504,7 @@
         <v>adj</v>
       </c>
       <c r="C440" t="str">
-        <v>האדם הנבון</v>
+        <v>אנושי</v>
       </c>
       <c r="D440" t="str">
         <v/>
@@ -10619,7 +10619,7 @@
         <v>v</v>
       </c>
       <c r="C445" t="str">
-        <v>פְּגִיעָה</v>
+        <v>כאב</v>
       </c>
       <c r="D445" t="str">
         <v/>
@@ -10665,7 +10665,7 @@
         <v>v</v>
       </c>
       <c r="C447" t="str">
-        <v>מזהה</v>
+        <v>לזהות</v>
       </c>
       <c r="D447" t="str">
         <v/>
@@ -10688,7 +10688,7 @@
         <v>conj</v>
       </c>
       <c r="C448" t="str">
-        <v>סכומי</v>
+        <v>אם</v>
       </c>
       <c r="D448" t="str">
         <v/>
@@ -10711,7 +10711,7 @@
         <v>conj</v>
       </c>
       <c r="C449" t="str">
-        <v>סכומי</v>
+        <v>אם</v>
       </c>
       <c r="D449" t="str">
         <v/>
@@ -10734,7 +10734,7 @@
         <v/>
       </c>
       <c r="C450" t="str">
-        <v>אם אהבת את</v>
+        <v>אם תרצה</v>
       </c>
       <c r="D450" t="str">
         <v/>
@@ -10757,7 +10757,7 @@
         <v>v</v>
       </c>
       <c r="C451" t="str">
-        <v>קשב</v>
+        <v>להתעלם</v>
       </c>
       <c r="D451" t="str">
         <v/>
@@ -10803,7 +10803,7 @@
         <v/>
       </c>
       <c r="C453" t="str">
-        <v>ואני מפחדת.</v>
+        <v>אני חושש…</v>
       </c>
       <c r="D453" t="str">
         <v/>
@@ -10895,7 +10895,7 @@
         <v>adj</v>
       </c>
       <c r="C457" t="str">
-        <v>מיידי</v>
+        <v>מידי</v>
       </c>
       <c r="D457" t="str">
         <v/>
@@ -10964,7 +10964,7 @@
         <v>adj</v>
       </c>
       <c r="C460" t="str">
-        <v>אי אפשר.</v>
+        <v>בלתי אפשרי</v>
       </c>
       <c r="D460" t="str">
         <v/>
@@ -11010,7 +11010,7 @@
         <v>prep</v>
       </c>
       <c r="C462" t="str">
-        <v>ב-</v>
+        <v>ב</v>
       </c>
       <c r="D462" t="str">
         <v/>
@@ -11033,7 +11033,7 @@
         <v>prep</v>
       </c>
       <c r="C463" t="str">
-        <v>ב-</v>
+        <v>ב</v>
       </c>
       <c r="D463" t="str">
         <v/>
@@ -11056,7 +11056,7 @@
         <v>prep</v>
       </c>
       <c r="C464" t="str">
-        <v>ב-</v>
+        <v>ב</v>
       </c>
       <c r="D464" t="str">
         <v/>
@@ -11079,7 +11079,7 @@
         <v>prep</v>
       </c>
       <c r="C465" t="str">
-        <v>ב-</v>
+        <v>ב</v>
       </c>
       <c r="D465" t="str">
         <v/>
@@ -11102,7 +11102,7 @@
         <v>prep</v>
       </c>
       <c r="C466" t="str">
-        <v>ב-</v>
+        <v>ב</v>
       </c>
       <c r="D466" t="str">
         <v/>
@@ -11148,7 +11148,7 @@
         <v/>
       </c>
       <c r="C468" t="str">
-        <v>במקרה של משהו</v>
+        <v>במקרה של sth</v>
       </c>
       <c r="D468" t="str">
         <v/>
@@ -11194,7 +11194,7 @@
         <v/>
       </c>
       <c r="C470" t="str">
-        <v>אהבה רומנטית</v>
+        <v>מאוהב</v>
       </c>
       <c r="D470" t="str">
         <v/>
@@ -11240,7 +11240,7 @@
         <v/>
       </c>
       <c r="C472" t="str">
-        <v>בבוא הזמן.</v>
+        <v>בזמן</v>
       </c>
       <c r="D472" t="str">
         <v/>
@@ -11286,7 +11286,7 @@
         <v>adj</v>
       </c>
       <c r="C474" t="str">
-        <v>כלול</v>
+        <v>כולל</v>
       </c>
       <c r="D474" t="str">
         <v>including</v>
@@ -11309,7 +11309,7 @@
         <v>v, n</v>
       </c>
       <c r="C475" t="str">
-        <v>העלה</v>
+        <v>להגדיל</v>
       </c>
       <c r="D475" t="str">
         <v/>
@@ -11332,7 +11332,7 @@
         <v>n</v>
       </c>
       <c r="C476" t="str">
-        <v>תעשייה</v>
+        <v>תעשיה</v>
       </c>
       <c r="D476" t="str">
         <v>industrial</v>
@@ -11355,7 +11355,7 @@
         <v>v</v>
       </c>
       <c r="C477" t="str">
-        <v>ליידע</v>
+        <v>להודיע</v>
       </c>
       <c r="D477" t="str">
         <v/>
@@ -11378,7 +11378,7 @@
         <v/>
       </c>
       <c r="C478" t="str">
-        <v>מחשוב</v>
+        <v>טכנולוגיית מידע</v>
       </c>
       <c r="D478" t="str">
         <v/>
@@ -11447,7 +11447,7 @@
         <v>n</v>
       </c>
       <c r="C481" t="str">
-        <v>חרקים</v>
+        <v>חרק</v>
       </c>
       <c r="D481" t="str">
         <v/>
@@ -11470,7 +11470,7 @@
         <v>n</v>
       </c>
       <c r="C482" t="str">
-        <v>בתוך המבנה</v>
+        <v>בפנים</v>
       </c>
       <c r="D482" t="str">
         <v/>
@@ -11539,7 +11539,7 @@
         <v>n</v>
       </c>
       <c r="C485" t="str">
-        <v>אִינטֶרֶס</v>
+        <v>עניין</v>
       </c>
       <c r="D485" t="str">
         <v/>
@@ -11585,7 +11585,7 @@
         <v>n</v>
       </c>
       <c r="C487" t="str">
-        <v>מרווח זמן</v>
+        <v>הפסקה</v>
       </c>
       <c r="D487" t="str">
         <v/>
@@ -11608,7 +11608,7 @@
         <v>v</v>
       </c>
       <c r="C488" t="str">
-        <v>להכיר</v>
+        <v>להציג</v>
       </c>
       <c r="D488" t="str">
         <v/>
@@ -11631,7 +11631,7 @@
         <v>v</v>
       </c>
       <c r="C489" t="str">
-        <v>המצאה</v>
+        <v>להמציא</v>
       </c>
       <c r="D489" t="str">
         <v>invention</v>
@@ -11677,7 +11677,7 @@
         <v>n</v>
       </c>
       <c r="C491" t="str">
-        <v>איסלם</v>
+        <v>אסלאם</v>
       </c>
       <c r="D491" t="str">
         <v/>
@@ -11792,7 +11792,7 @@
         <v>n</v>
       </c>
       <c r="C496" t="str">
-        <v>בית סוהר</v>
+        <v>כלא</v>
       </c>
       <c r="D496" t="str">
         <v/>
@@ -11815,7 +11815,7 @@
         <v>n</v>
       </c>
       <c r="C497" t="str">
-        <v>ג'אז</v>
+        <v>ג'ז</v>
       </c>
       <c r="D497" t="str">
         <v/>
@@ -11838,7 +11838,7 @@
         <v>n</v>
       </c>
       <c r="C498" t="str">
-        <v>יהודים</v>
+        <v>יהודי</v>
       </c>
       <c r="D498" t="str">
         <v>Jewish</v>
@@ -11861,7 +11861,7 @@
         <v>n</v>
       </c>
       <c r="C499" t="str">
-        <v>תכשיט</v>
+        <v>תכשיטים</v>
       </c>
       <c r="D499" t="str">
         <v/>
@@ -11884,7 +11884,7 @@
         <v>n</v>
       </c>
       <c r="C500" t="str">
-        <v>המשרה</v>
+        <v>עבודה</v>
       </c>
       <c r="D500" t="str">
         <v/>
@@ -11907,7 +11907,7 @@
         <v>v</v>
       </c>
       <c r="C501" t="str">
-        <v>הרשמה</v>
+        <v>להצטרף</v>
       </c>
       <c r="D501" t="str">
         <v/>
@@ -11999,7 +11999,7 @@
         <v>n, v</v>
       </c>
       <c r="C505" t="str">
-        <v>שופט</v>
+        <v>לשפוט</v>
       </c>
       <c r="D505" t="str">
         <v/>
@@ -12022,7 +12022,7 @@
         <v>adv</v>
       </c>
       <c r="C506" t="str">
-        <v>כמעט.</v>
+        <v>רק</v>
       </c>
       <c r="D506" t="str">
         <v/>
@@ -12045,7 +12045,7 @@
         <v>adv</v>
       </c>
       <c r="C507" t="str">
-        <v>כמעט.</v>
+        <v>רק</v>
       </c>
       <c r="D507" t="str">
         <v/>
@@ -12068,7 +12068,7 @@
         <v/>
       </c>
       <c r="C508" t="str">
-        <v>טוען ..</v>
+        <v>רק רגע</v>
       </c>
       <c r="D508" t="str">
         <v/>
@@ -12091,7 +12091,7 @@
         <v>n</v>
       </c>
       <c r="C509" t="str">
-        <v>לבעוט</v>
+        <v>בעיטה</v>
       </c>
       <c r="D509" t="str">
         <v/>
@@ -12206,7 +12206,7 @@
         <v/>
       </c>
       <c r="C514" t="str">
-        <v>חוסר במשהו</v>
+        <v>חוסר ע"ש</v>
       </c>
       <c r="D514" t="str">
         <v/>
@@ -12275,7 +12275,7 @@
         <v>n</v>
       </c>
       <c r="C517" t="str">
-        <v>לנחות</v>
+        <v>קרקע</v>
       </c>
       <c r="D517" t="str">
         <v/>
@@ -12298,7 +12298,7 @@
         <v>v</v>
       </c>
       <c r="C518" t="str">
-        <v>לנחות</v>
+        <v>קרקע</v>
       </c>
       <c r="D518" t="str">
         <v>landing</v>
@@ -12367,7 +12367,7 @@
         <v>adj</v>
       </c>
       <c r="C521" t="str">
-        <v>אחרון</v>
+        <v>האחרון</v>
       </c>
       <c r="D521" t="str">
         <v/>
@@ -12390,7 +12390,7 @@
         <v/>
       </c>
       <c r="C522" t="str">
-        <v>לצחוק על מישהו/מישהו</v>
+        <v>לצחוק על sb/sth</v>
       </c>
       <c r="D522" t="str">
         <v/>
@@ -12413,7 +12413,7 @@
         <v>n</v>
       </c>
       <c r="C523" t="str">
-        <v>דין</v>
+        <v>משפטים</v>
       </c>
       <c r="D523" t="str">
         <v/>
@@ -12459,7 +12459,7 @@
         <v>v</v>
       </c>
       <c r="C525" t="str">
-        <v>עופרת</v>
+        <v>להוביל</v>
       </c>
       <c r="D525" t="str">
         <v/>
@@ -12551,7 +12551,7 @@
         <v/>
       </c>
       <c r="C529" t="str">
-        <v>להשמיט sb/sth או להשמיט sb/sth בחוץ</v>
+        <v>עזוב את sb/sth או השאר את sb/sth בחוץ</v>
       </c>
       <c r="D529" t="str">
         <v/>
@@ -12574,7 +12574,7 @@
         <v>n</v>
       </c>
       <c r="C530" t="str">
-        <v>שמאלה</v>
+        <v>שמאל</v>
       </c>
       <c r="D530" t="str">
         <v/>
@@ -12666,7 +12666,7 @@
         <v/>
       </c>
       <c r="C534" t="str">
-        <v>ליידע מישהו (איזה דבר)</v>
+        <v>ליידע את sb</v>
       </c>
       <c r="D534" t="str">
         <v/>
@@ -12689,7 +12689,7 @@
         <v>n</v>
       </c>
       <c r="C535" t="str">
-        <v>דרגה</v>
+        <v>רמה</v>
       </c>
       <c r="D535" t="str">
         <v/>
@@ -12712,7 +12712,7 @@
         <v>n</v>
       </c>
       <c r="C536" t="str">
-        <v>דרגה</v>
+        <v>רמה</v>
       </c>
       <c r="D536" t="str">
         <v/>
@@ -12735,7 +12735,7 @@
         <v>n</v>
       </c>
       <c r="C537" t="str">
-        <v>ספרייה</v>
+        <v>ספריה</v>
       </c>
       <c r="D537" t="str">
         <v/>
@@ -12804,7 +12804,7 @@
         <v>v</v>
       </c>
       <c r="C540" t="str">
-        <v>להרים</v>
+        <v>מעלית</v>
       </c>
       <c r="D540" t="str">
         <v/>
@@ -12827,7 +12827,7 @@
         <v>n</v>
       </c>
       <c r="C541" t="str">
-        <v>להרים</v>
+        <v>מעלית</v>
       </c>
       <c r="D541" t="str">
         <v/>
@@ -12850,7 +12850,7 @@
         <v>prep</v>
       </c>
       <c r="C542" t="str">
-        <v>לאהוב</v>
+        <v>כמו</v>
       </c>
       <c r="D542" t="str">
         <v/>
@@ -12873,7 +12873,7 @@
         <v>v, n</v>
       </c>
       <c r="C543" t="str">
-        <v>גבול</v>
+        <v>להגביל</v>
       </c>
       <c r="D543" t="str">
         <v/>
@@ -12896,7 +12896,7 @@
         <v>n</v>
       </c>
       <c r="C544" t="str">
-        <v>עריכת שורה</v>
+        <v>שורה</v>
       </c>
       <c r="D544" t="str">
         <v/>
@@ -12988,7 +12988,7 @@
         <v>v</v>
       </c>
       <c r="C548" t="str">
-        <v>אתר</v>
+        <v>לאתר</v>
       </c>
       <c r="D548" t="str">
         <v>location</v>
@@ -13034,7 +13034,7 @@
         <v>adj</v>
       </c>
       <c r="C550" t="str">
-        <v>:he:ארך'ארוך</v>
+        <v>ארוך</v>
       </c>
       <c r="D550" t="str">
         <v/>
@@ -13057,7 +13057,7 @@
         <v/>
       </c>
       <c r="C551" t="str">
-        <v>להסתכל מסביב/סיבוב</v>
+        <v>להסתכל מסביב/עגול</v>
       </c>
       <c r="D551" t="str">
         <v/>
@@ -13103,7 +13103,7 @@
         <v/>
       </c>
       <c r="C553" t="str">
-        <v>להיראות נחמד/מוזר וכו'.</v>
+        <v>נראה נחמד/מוזר וכו'.</v>
       </c>
       <c r="D553" t="str">
         <v/>
@@ -13126,7 +13126,7 @@
         <v/>
       </c>
       <c r="C554" t="str">
-        <v>זהירות!</v>
+        <v>להשגיח!</v>
       </c>
       <c r="D554" t="str">
         <v/>
@@ -13149,7 +13149,7 @@
         <v/>
       </c>
       <c r="C555" t="str">
-        <v>חפש משהו או חפש משהו למעלה</v>
+        <v>תסתכל למעלה או תסתכל למעלה</v>
       </c>
       <c r="D555" t="str">
         <v/>
@@ -13172,7 +13172,7 @@
         <v>v</v>
       </c>
       <c r="C556" t="str">
-        <v>לאבד</v>
+        <v>לרדת</v>
       </c>
       <c r="D556" t="str">
         <v/>
@@ -13195,7 +13195,7 @@
         <v>adj</v>
       </c>
       <c r="C557" t="str">
-        <v>רועש</v>
+        <v>בקול רם</v>
       </c>
       <c r="D557" t="str">
         <v/>
@@ -13218,7 +13218,7 @@
         <v>n</v>
       </c>
       <c r="C558" t="str">
-        <v>לאהוב</v>
+        <v>אהבה</v>
       </c>
       <c r="D558" t="str">
         <v/>
@@ -13241,7 +13241,7 @@
         <v>n</v>
       </c>
       <c r="C559" t="str">
-        <v>לאהוב</v>
+        <v>אהבה</v>
       </c>
       <c r="D559" t="str">
         <v/>
@@ -13264,7 +13264,7 @@
         <v/>
       </c>
       <c r="C560" t="str">
-        <v>אהבה / (עם) אהבה מ / כל אהבתי / המון אהבה</v>
+        <v>אהבה / אהבה מ / כל אהבתי / המון אהבה</v>
       </c>
       <c r="D560" t="str">
         <v/>
@@ -13287,7 +13287,7 @@
         <v>n</v>
       </c>
       <c r="C561" t="str">
-        <v>מזל.</v>
+        <v>מזל</v>
       </c>
       <c r="D561" t="str">
         <v/>
@@ -13310,7 +13310,7 @@
         <v>n</v>
       </c>
       <c r="C562" t="str">
-        <v>מזל.</v>
+        <v>מזל</v>
       </c>
       <c r="D562" t="str">
         <v/>
@@ -13333,7 +13333,7 @@
         <v>adj</v>
       </c>
       <c r="C563" t="str">
-        <v>בר מזל (bar mazal) (m)</v>
+        <v>בר מזל</v>
       </c>
       <c r="D563" t="str">
         <v/>
@@ -13402,7 +13402,7 @@
         <v>n</v>
       </c>
       <c r="C566" t="str">
-        <v>קסם.</v>
+        <v>קסם</v>
       </c>
       <c r="D566" t="str">
         <v/>
@@ -13425,7 +13425,7 @@
         <v>n</v>
       </c>
       <c r="C567" t="str">
-        <v>קסם.</v>
+        <v>קסם</v>
       </c>
       <c r="D567" t="str">
         <v/>
@@ -13540,7 +13540,7 @@
         <v/>
       </c>
       <c r="C572" t="str">
-        <v>לוודא (ש)</v>
+        <v>לוודא</v>
       </c>
       <c r="D572" t="str">
         <v/>
@@ -13563,7 +13563,7 @@
         <v>v</v>
       </c>
       <c r="C573" t="str">
-        <v>להצליח</v>
+        <v>לנהל</v>
       </c>
       <c r="D573" t="str">
         <v/>
@@ -13609,7 +13609,7 @@
         <v>v</v>
       </c>
       <c r="C575" t="str">
-        <v>נישואים</v>
+        <v>להתחתן</v>
       </c>
       <c r="D575" t="str">
         <v/>
@@ -13632,7 +13632,7 @@
         <v>n</v>
       </c>
       <c r="C576" t="str">
-        <v>התאמה</v>
+        <v>משחק</v>
       </c>
       <c r="D576" t="str">
         <v/>
@@ -13678,7 +13678,7 @@
         <v>v</v>
       </c>
       <c r="C578" t="str">
-        <v>מדידה</v>
+        <v>למדוד</v>
       </c>
       <c r="D578" t="str">
         <v/>
@@ -13701,7 +13701,7 @@
         <v>n</v>
       </c>
       <c r="C579" t="str">
-        <v>מדליות ועיטורים</v>
+        <v>מדליה</v>
       </c>
       <c r="D579" t="str">
         <v/>
@@ -13724,7 +13724,7 @@
         <v>n</v>
       </c>
       <c r="C580" t="str">
-        <v>תרופה</v>
+        <v>רפואה</v>
       </c>
       <c r="D580" t="str">
         <v/>
@@ -13747,7 +13747,7 @@
         <v>n</v>
       </c>
       <c r="C581" t="str">
-        <v>תרופה</v>
+        <v>רפואה</v>
       </c>
       <c r="D581" t="str">
         <v/>
@@ -13770,7 +13770,7 @@
         <v>adj, n</v>
       </c>
       <c r="C582" t="str">
-        <v>בינונית</v>
+        <v>בינוני</v>
       </c>
       <c r="D582" t="str">
         <v/>
@@ -13885,7 +13885,7 @@
         <v>adj</v>
       </c>
       <c r="C587" t="str">
-        <v>צבא</v>
+        <v>צבאי</v>
       </c>
       <c r="D587" t="str">
         <v/>
@@ -13908,7 +13908,7 @@
         <v>n</v>
       </c>
       <c r="C588" t="str">
-        <v>רוח (f)</v>
+        <v>ראש</v>
       </c>
       <c r="D588" t="str">
         <v/>
@@ -13977,7 +13977,7 @@
         <v>v</v>
       </c>
       <c r="C591" t="str">
-        <v>בת</v>
+        <v>מתגעגע</v>
       </c>
       <c r="D591" t="str">
         <v/>
@@ -14000,7 +14000,7 @@
         <v>adj</v>
       </c>
       <c r="C592" t="str">
-        <v>חדיש</v>
+        <v>מודרני</v>
       </c>
       <c r="D592" t="str">
         <v/>
@@ -14092,7 +14092,7 @@
         <v>adj, det</v>
       </c>
       <c r="C596" t="str">
-        <v>ביותר!</v>
+        <v>רוב</v>
       </c>
       <c r="D596" t="str">
         <v/>
@@ -14184,7 +14184,7 @@
         <v/>
       </c>
       <c r="C600" t="str">
-        <v>לעבור דירה/לעבור דירה</v>
+        <v>לעבור פנימה / לצאת</v>
       </c>
       <c r="D600" t="str">
         <v/>
@@ -14253,7 +14253,7 @@
         <v>adj</v>
       </c>
       <c r="C603" t="str">
-        <v>מיוזיקל</v>
+        <v>מוסיקלי</v>
       </c>
       <c r="D603" t="str">
         <v/>
@@ -14276,7 +14276,7 @@
         <v>n</v>
       </c>
       <c r="C604" t="str">
-        <v>מוזיקאי</v>
+        <v>מוסיקאי</v>
       </c>
       <c r="D604" t="str">
         <v/>
@@ -14299,7 +14299,7 @@
         <v>pron</v>
       </c>
       <c r="C605" t="str">
-        <v>את עצמי</v>
+        <v>עצמי</v>
       </c>
       <c r="D605" t="str">
         <v/>
@@ -14368,7 +14368,7 @@
         <v>n</v>
       </c>
       <c r="C608" t="str">
-        <v>הלאום</v>
+        <v>אזרחות</v>
       </c>
       <c r="D608" t="str">
         <v/>
@@ -14414,7 +14414,7 @@
         <v>adj, adv</v>
       </c>
       <c r="C610" t="str">
-        <v>באיזור</v>
+        <v>קרוב</v>
       </c>
       <c r="D610" t="str">
         <v/>
@@ -14483,7 +14483,7 @@
         <v>n</v>
       </c>
       <c r="C613" t="str">
-        <v>יפהפייה.</v>
+        <v>שרשרת</v>
       </c>
       <c r="D613" t="str">
         <v/>
@@ -14506,7 +14506,7 @@
         <v>adv, det</v>
       </c>
       <c r="C614" t="str">
-        <v>אף אחד מהעיל</v>
+        <v>גם לא</v>
       </c>
       <c r="D614" t="str">
         <v/>
@@ -14529,7 +14529,7 @@
         <v/>
       </c>
       <c r="C615" t="str">
-        <v>לא חשוב</v>
+        <v>לא משנה</v>
       </c>
       <c r="D615" t="str">
         <v/>
@@ -14552,7 +14552,7 @@
         <v>adv</v>
       </c>
       <c r="C616" t="str">
-        <v>נורמליות</v>
+        <v>בדרך כלל</v>
       </c>
       <c r="D616" t="str">
         <v/>
@@ -14575,7 +14575,7 @@
         <v>n</v>
       </c>
       <c r="C617" t="str">
-        <v>פתק</v>
+        <v>הערה</v>
       </c>
       <c r="D617" t="str">
         <v/>
@@ -14598,7 +14598,7 @@
         <v>pron</v>
       </c>
       <c r="C618" t="str">
-        <v>כלום</v>
+        <v>שום דבר</v>
       </c>
       <c r="D618" t="str">
         <v/>
@@ -14621,7 +14621,7 @@
         <v>v</v>
       </c>
       <c r="C619" t="str">
-        <v>שים לב</v>
+        <v>לשים לב</v>
       </c>
       <c r="D619" t="str">
         <v/>
@@ -14690,7 +14690,7 @@
         <v>n</v>
       </c>
       <c r="C622" t="str">
-        <v>עצם מאושר</v>
+        <v>להתנגד</v>
       </c>
       <c r="D622" t="str">
         <v/>
@@ -14736,7 +14736,7 @@
         <v>prep</v>
       </c>
       <c r="C624" t="str">
-        <v>מתוך</v>
+        <v>של</v>
       </c>
       <c r="D624" t="str">
         <v/>
@@ -14759,7 +14759,7 @@
         <v/>
       </c>
       <c r="C625" t="str">
-        <v>כמובן.</v>
+        <v>כמובן</v>
       </c>
       <c r="D625" t="str">
         <v/>
@@ -14782,7 +14782,7 @@
         <v/>
       </c>
       <c r="C626" t="str">
-        <v>מובן שלא.</v>
+        <v>כמובן שלא</v>
       </c>
       <c r="D626" t="str">
         <v/>
@@ -14851,7 +14851,7 @@
         <v>v</v>
       </c>
       <c r="C629" t="str">
-        <v>מבצע</v>
+        <v>להציע</v>
       </c>
       <c r="D629" t="str">
         <v/>
@@ -14874,7 +14874,7 @@
         <v>n</v>
       </c>
       <c r="C630" t="str">
-        <v>שוטר</v>
+        <v>קצין</v>
       </c>
       <c r="D630" t="str">
         <v/>
@@ -14897,7 +14897,7 @@
         <v>exclam</v>
       </c>
       <c r="C631" t="str">
-        <v>או</v>
+        <v>הו</v>
       </c>
       <c r="D631" t="str">
         <v/>
@@ -14943,7 +14943,7 @@
         <v/>
       </c>
       <c r="C633" t="str">
-        <v>בעניינים עסקיים</v>
+        <v>על עסקים</v>
       </c>
       <c r="D633" t="str">
         <v/>
@@ -14989,7 +14989,7 @@
         <v/>
       </c>
       <c r="C635" t="str">
-        <v>- ברגל.</v>
+        <v>ברגל</v>
       </c>
       <c r="D635" t="str">
         <v/>
@@ -15012,7 +15012,7 @@
         <v/>
       </c>
       <c r="C636" t="str">
-        <v>בהצעה</v>
+        <v>בהיצע</v>
       </c>
       <c r="D636" t="str">
         <v/>
@@ -15035,7 +15035,7 @@
         <v/>
       </c>
       <c r="C637" t="str">
-        <v>במועדם,</v>
+        <v>בזמן</v>
       </c>
       <c r="D637" t="str">
         <v/>
@@ -15058,7 +15058,7 @@
         <v>pron</v>
       </c>
       <c r="C638" t="str">
-        <v>אחד</v>
+        <v>אחת</v>
       </c>
       <c r="D638" t="str">
         <v/>
@@ -15104,7 +15104,7 @@
         <v/>
       </c>
       <c r="C640" t="str">
-        <v>יום</v>
+        <v>יום אחד</v>
       </c>
       <c r="D640" t="str">
         <v/>
@@ -15127,7 +15127,7 @@
         <v>v</v>
       </c>
       <c r="C641" t="str">
-        <v>לפתוח</v>
+        <v>פתוח</v>
       </c>
       <c r="D641" t="str">
         <v/>
@@ -15150,7 +15150,7 @@
         <v>v, adj</v>
       </c>
       <c r="C642" t="str">
-        <v>לפתוח</v>
+        <v>פתוח</v>
       </c>
       <c r="D642" t="str">
         <v/>
@@ -15265,7 +15265,7 @@
         <v/>
       </c>
       <c r="C647" t="str">
-        <v>. או משהו כזה...</v>
+        <v>או משהו</v>
       </c>
       <c r="D647" t="str">
         <v/>
@@ -15288,7 +15288,7 @@
         <v>n</v>
       </c>
       <c r="C648" t="str">
-        <v>הזמנה</v>
+        <v>סדר</v>
       </c>
       <c r="D648" t="str">
         <v/>
@@ -15311,7 +15311,7 @@
         <v>adj</v>
       </c>
       <c r="C649" t="str">
-        <v>החלטה</v>
+        <v>רגיל</v>
       </c>
       <c r="D649" t="str">
         <v/>
@@ -15426,7 +15426,7 @@
         <v/>
       </c>
       <c r="C654" t="str">
-        <v>פעמון לא תקין</v>
+        <v>מקולקל</v>
       </c>
       <c r="D654" t="str">
         <v/>
@@ -15449,7 +15449,7 @@
         <v>prep</v>
       </c>
       <c r="C655" t="str">
-        <v>יותר מאשר</v>
+        <v>נגמר</v>
       </c>
       <c r="D655" t="str">
         <v/>
@@ -15472,7 +15472,7 @@
         <v>prep</v>
       </c>
       <c r="C656" t="str">
-        <v>יותר מאשר</v>
+        <v>נגמר</v>
       </c>
       <c r="D656" t="str">
         <v/>
@@ -15518,7 +15518,7 @@
         <v/>
       </c>
       <c r="C658" t="str">
-        <v>רֹאשׁ הַמֶמשָׁלָה.</v>
+        <v>אחה"צ</v>
       </c>
       <c r="D658" t="str">
         <v/>
@@ -15587,7 +15587,7 @@
         <v>n</v>
       </c>
       <c r="C661" t="str">
-        <v>פיג'מה</v>
+        <v>פיג'מה/פיג'מה</v>
       </c>
       <c r="D661" t="str">
         <v/>
@@ -15633,7 +15633,7 @@
         <v>n</v>
       </c>
       <c r="C663" t="str">
-        <v>חלקה</v>
+        <v>חבילה</v>
       </c>
       <c r="D663" t="str">
         <v/>
@@ -15656,7 +15656,7 @@
         <v/>
       </c>
       <c r="C664" t="str">
-        <v>חלק מ-sth</v>
+        <v>חלק מס'</v>
       </c>
       <c r="D664" t="str">
         <v/>
@@ -15679,7 +15679,7 @@
         <v>v</v>
       </c>
       <c r="C665" t="str">
-        <v>הלך'הָלַךְ</v>
+        <v>להעביר</v>
       </c>
       <c r="D665" t="str">
         <v/>
@@ -15794,7 +15794,7 @@
         <v>n</v>
       </c>
       <c r="C670" t="str">
-        <v>דוגמה</v>
+        <v>תבנית</v>
       </c>
       <c r="D670" t="str">
         <v/>
@@ -15909,7 +15909,7 @@
         <v>n</v>
       </c>
       <c r="C675" t="str">
-        <v>מופע</v>
+        <v>ביצועים</v>
       </c>
       <c r="D675" t="str">
         <v/>
@@ -16001,7 +16001,7 @@
         <v>adj</v>
       </c>
       <c r="C679" t="str">
-        <v>פיזי</v>
+        <v>גופני</v>
       </c>
       <c r="D679" t="str">
         <v>physically</v>
@@ -16024,7 +16024,7 @@
         <v>n</v>
       </c>
       <c r="C680" t="str">
-        <v>פיזיקה</v>
+        <v>פיסיקה</v>
       </c>
       <c r="D680" t="str">
         <v/>
@@ -16070,7 +16070,7 @@
         <v/>
       </c>
       <c r="C682" t="str">
-        <v>לאסוף מישהו/מישהו או לאסוף מישהו/מישהו</v>
+        <v>להרים sb/sth או לקחת sb/sth up</v>
       </c>
       <c r="D682" t="str">
         <v/>
@@ -16139,7 +16139,7 @@
         <v>v</v>
       </c>
       <c r="C685" t="str">
-        <v>לשחק</v>
+        <v>משחק</v>
       </c>
       <c r="D685" t="str">
         <v/>
@@ -16185,7 +16185,7 @@
         <v>v</v>
       </c>
       <c r="C687" t="str">
-        <v>בבקשה</v>
+        <v>אנא</v>
       </c>
       <c r="D687" t="str">
         <v/>
@@ -16231,7 +16231,7 @@
         <v>n</v>
       </c>
       <c r="C689" t="str">
-        <v>עונג</v>
+        <v>הנאה</v>
       </c>
       <c r="D689" t="str">
         <v/>
@@ -16254,7 +16254,7 @@
         <v>n</v>
       </c>
       <c r="C690" t="str">
-        <v>שירה</v>
+        <v>שיר</v>
       </c>
       <c r="D690" t="str">
         <v/>
@@ -16346,7 +16346,7 @@
         <v>adj</v>
       </c>
       <c r="C694" t="str">
-        <v>עני</v>
+        <v>מסכן</v>
       </c>
       <c r="D694" t="str">
         <v/>
@@ -16392,7 +16392,7 @@
         <v>n</v>
       </c>
       <c r="C696" t="str">
-        <v>למקם</v>
+        <v>מיקום</v>
       </c>
       <c r="D696" t="str">
         <v/>
@@ -16438,7 +16438,7 @@
         <v>n, v</v>
       </c>
       <c r="C698" t="str">
-        <v>פוסט</v>
+        <v>פוסט )</v>
       </c>
       <c r="D698" t="str">
         <v>postman post office</v>
@@ -16484,7 +16484,7 @@
         <v>adj</v>
       </c>
       <c r="C700" t="str">
-        <v>כוח</v>
+        <v>עוצמתי</v>
       </c>
       <c r="D700" t="str">
         <v/>
@@ -16507,7 +16507,7 @@
         <v>n</v>
       </c>
       <c r="C701" t="str">
-        <v>תרגול</v>
+        <v>הכנה</v>
       </c>
       <c r="D701" t="str">
         <v>prepared</v>
@@ -16530,7 +16530,7 @@
         <v>v</v>
       </c>
       <c r="C702" t="str">
-        <v>לחוץ</v>
+        <v>ללחוץ</v>
       </c>
       <c r="D702" t="str">
         <v/>
@@ -16553,7 +16553,7 @@
         <v>n</v>
       </c>
       <c r="C703" t="str">
-        <v>בית סוהר</v>
+        <v>כלא</v>
       </c>
       <c r="D703" t="str">
         <v>prisoner</v>
@@ -16576,7 +16576,7 @@
         <v>adj</v>
       </c>
       <c r="C704" t="str">
-        <v>טוראי</v>
+        <v>פרטי</v>
       </c>
       <c r="D704" t="str">
         <v/>
@@ -16599,7 +16599,7 @@
         <v>v</v>
       </c>
       <c r="C705" t="str">
-        <v>תוֹצֶרֶת</v>
+        <v>לייצר</v>
       </c>
       <c r="D705" t="str">
         <v>product production</v>
@@ -16622,7 +16622,7 @@
         <v>adj</v>
       </c>
       <c r="C706" t="str">
-        <v>מקצועיים</v>
+        <v>מקצועי</v>
       </c>
       <c r="D706" t="str">
         <v/>
@@ -16691,7 +16691,7 @@
         <v>n</v>
       </c>
       <c r="C709" t="str">
-        <v>נכס</v>
+        <v>רכוש</v>
       </c>
       <c r="D709" t="str">
         <v/>
@@ -16737,7 +16737,7 @@
         <v>v</v>
       </c>
       <c r="C711" t="str">
-        <v>הגנה</v>
+        <v>להגן</v>
       </c>
       <c r="D711" t="str">
         <v>protection</v>
@@ -16829,7 +16829,7 @@
         <v>n</v>
       </c>
       <c r="C715" t="str">
-        <v>גור</v>
+        <v>כלבלב</v>
       </c>
       <c r="D715" t="str">
         <v/>
@@ -16898,7 +16898,7 @@
         <v>n</v>
       </c>
       <c r="C718" t="str">
-        <v>פונקציה</v>
+        <v>מטרה</v>
       </c>
       <c r="D718" t="str">
         <v/>
@@ -16967,7 +16967,7 @@
         <v/>
       </c>
       <c r="C721" t="str">
-        <v>לדחות מישהו או לדחות אותו (אדם/משהו עושה משהו)</v>
+        <v>דחה sb או דחה sb</v>
       </c>
       <c r="D721" t="str">
         <v/>
@@ -16990,7 +16990,7 @@
         <v/>
       </c>
       <c r="C722" t="str">
-        <v>לדחות משהו/לעשות משהו או לדחות משהו</v>
+        <v>לדחות sth/לעשות sth או לדחות sth off</v>
       </c>
       <c r="D722" t="str">
         <v/>
@@ -17013,7 +17013,7 @@
         <v/>
       </c>
       <c r="C723" t="str">
-        <v>ללבוש משהו או ללבוש משהו (מוזיקה/סרט)</v>
+        <v>לשים על sth או לשים sth על</v>
       </c>
       <c r="D723" t="str">
         <v/>
@@ -17036,7 +17036,7 @@
         <v/>
       </c>
       <c r="C724" t="str">
-        <v>ללבוש משהו או ללבוש משהו (בגדים)</v>
+        <v>ללבוש sth או לשים sth על</v>
       </c>
       <c r="D724" t="str">
         <v/>
@@ -17059,7 +17059,7 @@
         <v/>
       </c>
       <c r="C725" t="str">
-        <v>לשים מישהו למעלה</v>
+        <v>לשים sb למעלה</v>
       </c>
       <c r="D725" t="str">
         <v/>
@@ -17082,7 +17082,7 @@
         <v/>
       </c>
       <c r="C726" t="str">
-        <v>לרשום משהו בכתב</v>
+        <v>להעלות על הכתב</v>
       </c>
       <c r="D726" t="str">
         <v/>
@@ -17105,7 +17105,7 @@
         <v/>
       </c>
       <c r="C727" t="str">
-        <v>לשים משהו ביחד או לשים משהו ביחד</v>
+        <v>להרכיב sth או להרכיב sth</v>
       </c>
       <c r="D727" t="str">
         <v/>
@@ -17128,7 +17128,7 @@
         <v/>
       </c>
       <c r="C728" t="str">
-        <v>לשים משהו או לשים משהו</v>
+        <v>לשים sth או לשים sth</v>
       </c>
       <c r="D728" t="str">
         <v/>
@@ -17151,7 +17151,7 @@
         <v>n</v>
       </c>
       <c r="C729" t="str">
-        <v>פאזל</v>
+        <v>חידה</v>
       </c>
       <c r="D729" t="str">
         <v/>
@@ -17243,7 +17243,7 @@
         <v>adv, n</v>
       </c>
       <c r="C733" t="str">
-        <v>בשקט.</v>
+        <v>בשקט</v>
       </c>
       <c r="D733" t="str">
         <v>quiet</v>
@@ -17266,7 +17266,7 @@
         <v>adv</v>
       </c>
       <c r="C734" t="str">
-        <v>די.</v>
+        <v>די</v>
       </c>
       <c r="D734" t="str">
         <v/>
@@ -17289,7 +17289,7 @@
         <v>n</v>
       </c>
       <c r="C735" t="str">
-        <v>גזע</v>
+        <v>מירוץ</v>
       </c>
       <c r="D735" t="str">
         <v/>
@@ -17335,7 +17335,7 @@
         <v>n</v>
       </c>
       <c r="C737" t="str">
-        <v>חולדה</v>
+        <v>להלשין</v>
       </c>
       <c r="D737" t="str">
         <v/>
@@ -17358,7 +17358,7 @@
         <v>v</v>
       </c>
       <c r="C738" t="str">
-        <v>תפוצה</v>
+        <v>להגיע</v>
       </c>
       <c r="D738" t="str">
         <v/>
@@ -17404,7 +17404,7 @@
         <v/>
       </c>
       <c r="C740" t="str">
-        <v>לקרוא משהו בקול רם או לקרוא משהו בקול רם</v>
+        <v>תקראו sth או תקראו sth</v>
       </c>
       <c r="D740" t="str">
         <v/>
@@ -17427,7 +17427,7 @@
         <v>adj</v>
       </c>
       <c r="C741" t="str">
-        <v>מאוד (məód) (1)</v>
+        <v>אמיתי</v>
       </c>
       <c r="D741" t="str">
         <v/>
@@ -17473,7 +17473,7 @@
         <v>adv</v>
       </c>
       <c r="C743" t="str">
-        <v>באמת.</v>
+        <v>באמת</v>
       </c>
       <c r="D743" t="str">
         <v/>
@@ -17496,7 +17496,7 @@
         <v>adv</v>
       </c>
       <c r="C744" t="str">
-        <v>באמת.</v>
+        <v>באמת</v>
       </c>
       <c r="D744" t="str">
         <v/>
@@ -17519,7 +17519,7 @@
         <v>adj</v>
       </c>
       <c r="C745" t="str">
-        <v>סביר?</v>
+        <v>סביר</v>
       </c>
       <c r="D745" t="str">
         <v/>
@@ -17565,7 +17565,7 @@
         <v>adj</v>
       </c>
       <c r="C747" t="str">
-        <v>אחרון</v>
+        <v>לאחרונה</v>
       </c>
       <c r="D747" t="str">
         <v>recently</v>
@@ -17611,7 +17611,7 @@
         <v>v, n</v>
       </c>
       <c r="C749" t="str">
-        <v>להקליט</v>
+        <v>שיא</v>
       </c>
       <c r="D749" t="str">
         <v>recording</v>
@@ -17634,7 +17634,7 @@
         <v>v</v>
       </c>
       <c r="C750" t="str">
-        <v>הפחיתו</v>
+        <v>להפחית</v>
       </c>
       <c r="D750" t="str">
         <v/>
@@ -17657,7 +17657,7 @@
         <v/>
       </c>
       <c r="C751" t="str">
-        <v>התייחס ל-sb/sth</v>
+        <v>עיין sb/sth</v>
       </c>
       <c r="D751" t="str">
         <v/>
@@ -17726,7 +17726,7 @@
         <v>v</v>
       </c>
       <c r="C754" t="str">
-        <v>לְהִשָׁאֵר</v>
+        <v>להישאר</v>
       </c>
       <c r="D754" t="str">
         <v>remaining</v>
@@ -17749,7 +17749,7 @@
         <v>v</v>
       </c>
       <c r="C755" t="str">
-        <v>הסר</v>
+        <v>להסיר</v>
       </c>
       <c r="D755" t="str">
         <v/>
@@ -17795,7 +17795,7 @@
         <v>v, n</v>
       </c>
       <c r="C757" t="str">
-        <v>להשיב</v>
+        <v>תגובה</v>
       </c>
       <c r="D757" t="str">
         <v/>
@@ -17818,7 +17818,7 @@
         <v>n</v>
       </c>
       <c r="C758" t="str">
-        <v>מערך</v>
+        <v>משאב</v>
       </c>
       <c r="D758" t="str">
         <v>money, etc. A1) EVP resource</v>
@@ -17910,7 +17910,7 @@
         <v>v, n</v>
       </c>
       <c r="C762" t="str">
-        <v>התקשר</v>
+        <v>טבעת</v>
       </c>
       <c r="D762" t="str">
         <v/>
@@ -17933,7 +17933,7 @@
         <v>n</v>
       </c>
       <c r="C763" t="str">
-        <v>אבן</v>
+        <v>רוק</v>
       </c>
       <c r="D763" t="str">
         <v/>
@@ -17956,7 +17956,7 @@
         <v>n</v>
       </c>
       <c r="C764" t="str">
-        <v>אבן</v>
+        <v>רוק</v>
       </c>
       <c r="D764" t="str">
         <v/>
@@ -18002,7 +18002,7 @@
         <v>v, n</v>
       </c>
       <c r="C766" t="str">
-        <v>לגלגל</v>
+        <v>גליל</v>
       </c>
       <c r="D766" t="str">
         <v/>
@@ -18094,7 +18094,7 @@
         <v>adj</v>
       </c>
       <c r="C770" t="str">
-        <v>מלוח.</v>
+        <v>מלוח</v>
       </c>
       <c r="D770" t="str">
         <v/>
@@ -18140,7 +18140,7 @@
         <v>n</v>
       </c>
       <c r="C772" t="str">
-        <v>נַקְנִיקִיָּה</v>
+        <v>נקניק</v>
       </c>
       <c r="D772" t="str">
         <v/>
@@ -18163,7 +18163,7 @@
         <v>v</v>
       </c>
       <c r="C773" t="str">
-        <v>שמירה</v>
+        <v>לשמור</v>
       </c>
       <c r="D773" t="str">
         <v/>
@@ -18232,7 +18232,7 @@
         <v>n</v>
       </c>
       <c r="C776" t="str">
-        <v>מספריים</v>
+        <v>מספרים</v>
       </c>
       <c r="D776" t="str">
         <v/>
@@ -18278,7 +18278,7 @@
         <v>v, n</v>
       </c>
       <c r="C778" t="str">
-        <v>תוצאה</v>
+        <v>ציון</v>
       </c>
       <c r="D778" t="str">
         <v/>
@@ -18301,7 +18301,7 @@
         <v>v, n</v>
       </c>
       <c r="C779" t="str">
-        <v>צעקה</v>
+        <v>לצרוח</v>
       </c>
       <c r="D779" t="str">
         <v/>
@@ -18324,7 +18324,7 @@
         <v>n</v>
       </c>
       <c r="C780" t="str">
-        <v>עונות השנה</v>
+        <v>עונה</v>
       </c>
       <c r="D780" t="str">
         <v/>
@@ -18347,7 +18347,7 @@
         <v>n</v>
       </c>
       <c r="C781" t="str">
-        <v>סוד (m)</v>
+        <v>סוד</v>
       </c>
       <c r="D781" t="str">
         <v>in secret</v>
@@ -18370,7 +18370,7 @@
         <v>n</v>
       </c>
       <c r="C782" t="str">
-        <v>מזכירה</v>
+        <v>מזכיר</v>
       </c>
       <c r="D782" t="str">
         <v/>
@@ -18393,7 +18393,7 @@
         <v/>
       </c>
       <c r="C783" t="str">
-        <v>נראה שמח / אדם נחמד וכו'.</v>
+        <v>נראה מאושר/אדם נחמד וכו'.</v>
       </c>
       <c r="D783" t="str">
         <v/>
@@ -18416,7 +18416,7 @@
         <v>v</v>
       </c>
       <c r="C784" t="str">
-        <v>בחירה</v>
+        <v>לבחור</v>
       </c>
       <c r="D784" t="str">
         <v>selection</v>
@@ -18462,7 +18462,7 @@
         <v>n</v>
       </c>
       <c r="C786" t="str">
-        <v>חמשת_החושים</v>
+        <v>חוש</v>
       </c>
       <c r="D786" t="str">
         <v>sensation</v>
@@ -18485,7 +18485,7 @@
         <v>adj,</v>
       </c>
       <c r="C787" t="str">
-        <v>להפריד</v>
+        <v>נפרד</v>
       </c>
       <c r="D787" t="str">
         <v>separate</v>
@@ -18508,7 +18508,7 @@
         <v>v</v>
       </c>
       <c r="C788" t="str">
-        <v>להגיש!</v>
+        <v>להגיש</v>
       </c>
       <c r="D788" t="str">
         <v>service</v>
@@ -18531,7 +18531,7 @@
         <v>v</v>
       </c>
       <c r="C789" t="str">
-        <v>להניח</v>
+        <v>להגדיר</v>
       </c>
       <c r="D789" t="str">
         <v/>
@@ -18554,7 +18554,7 @@
         <v>n</v>
       </c>
       <c r="C790" t="str">
-        <v>זוויג</v>
+        <v>מין</v>
       </c>
       <c r="D790" t="str">
         <v/>
@@ -18577,7 +18577,7 @@
         <v>n</v>
       </c>
       <c r="C791" t="str">
-        <v>הצללה</v>
+        <v>צל</v>
       </c>
       <c r="D791" t="str">
         <v/>
@@ -18600,7 +18600,7 @@
         <v/>
       </c>
       <c r="C792" t="str">
-        <v>בוא מלחץ ידיים.</v>
+        <v>ללחוץ ידיים</v>
       </c>
       <c r="D792" t="str">
         <v/>
@@ -18669,7 +18669,7 @@
         <v>n</v>
       </c>
       <c r="C795" t="str">
-        <v>גיליון</v>
+        <v>סדין</v>
       </c>
       <c r="D795" t="str">
         <v/>
@@ -18738,7 +18738,7 @@
         <v>v</v>
       </c>
       <c r="C798" t="str">
-        <v>'שוט'...</v>
+        <v>לירות</v>
       </c>
       <c r="D798" t="str">
         <v>shot</v>
@@ -18761,7 +18761,7 @@
         <v>n</v>
       </c>
       <c r="C799" t="str">
-        <v>קניות יבוא</v>
+        <v>קניות</v>
       </c>
       <c r="D799" t="str">
         <v>shopping mall</v>
@@ -18807,7 +18807,7 @@
         <v>adj</v>
       </c>
       <c r="C801" t="str">
-        <v>לסגור</v>
+        <v>סגור</v>
       </c>
       <c r="D801" t="str">
         <v/>
@@ -18830,7 +18830,7 @@
         <v>adj</v>
       </c>
       <c r="C802" t="str">
-        <v>ביישנות</v>
+        <v>ביישן</v>
       </c>
       <c r="D802" t="str">
         <v/>
@@ -18876,7 +18876,7 @@
         <v>n</v>
       </c>
       <c r="C804" t="str">
-        <v>כוונת</v>
+        <v>מראה</v>
       </c>
       <c r="D804" t="str">
         <v/>
@@ -18899,7 +18899,7 @@
         <v>n, adj</v>
       </c>
       <c r="C805" t="str">
-        <v>שקט</v>
+        <v>להשתיק</v>
       </c>
       <c r="D805" t="str">
         <v/>
@@ -18922,7 +18922,7 @@
         <v>adj</v>
       </c>
       <c r="C806" t="str">
-        <v>טיפשון!</v>
+        <v>טפשי</v>
       </c>
       <c r="D806" t="str">
         <v/>
@@ -18968,7 +18968,7 @@
         <v>adj</v>
       </c>
       <c r="C808" t="str">
-        <v>כנ״ל.</v>
+        <v>דומה</v>
       </c>
       <c r="D808" t="str">
         <v/>
@@ -18991,7 +18991,7 @@
         <v>adj</v>
       </c>
       <c r="C809" t="str">
-        <v>כחול</v>
+        <v>פשוט</v>
       </c>
       <c r="D809" t="str">
         <v/>
@@ -19014,7 +19014,7 @@
         <v>adj</v>
       </c>
       <c r="C810" t="str">
-        <v>יחיד</v>
+        <v>רווק</v>
       </c>
       <c r="D810" t="str">
         <v/>
@@ -19060,7 +19060,7 @@
         <v>n</v>
       </c>
       <c r="C812" t="str">
-        <v>סר _</v>
+        <v>אדוני</v>
       </c>
       <c r="D812" t="str">
         <v/>
@@ -19198,7 +19198,7 @@
         <v>n, v</v>
       </c>
       <c r="C818" t="str">
-        <v>חתיכה</v>
+        <v>פרוסה</v>
       </c>
       <c r="D818" t="str">
         <v/>
@@ -19244,7 +19244,7 @@
         <v>adj</v>
       </c>
       <c r="C820" t="str">
-        <v>חכם</v>
+        <v>לכאוב</v>
       </c>
       <c r="D820" t="str">
         <v/>
@@ -19267,7 +19267,7 @@
         <v>n, v</v>
       </c>
       <c r="C821" t="str">
-        <v>להריח</v>
+        <v>ריח</v>
       </c>
       <c r="D821" t="str">
         <v/>
@@ -19313,7 +19313,7 @@
         <v>adv</v>
       </c>
       <c r="C823" t="str">
-        <v>אז.</v>
+        <v>אז</v>
       </c>
       <c r="D823" t="str">
         <v/>
@@ -19382,7 +19382,7 @@
         <v>adj</v>
       </c>
       <c r="C826" t="str">
-        <v>זריקה רכה</v>
+        <v>רך</v>
       </c>
       <c r="D826" t="str">
         <v/>
@@ -19428,7 +19428,7 @@
         <v>n</v>
       </c>
       <c r="C828" t="str">
-        <v>תכנות</v>
+        <v>תוכנה</v>
       </c>
       <c r="D828" t="str">
         <v/>
@@ -19451,7 +19451,7 @@
         <v>n</v>
       </c>
       <c r="C829" t="str">
-        <v>חייל</v>
+        <v>לוחם</v>
       </c>
       <c r="D829" t="str">
         <v/>
@@ -19497,7 +19497,7 @@
         <v>n</v>
       </c>
       <c r="C831" t="str">
-        <v>למיין</v>
+        <v>מיון</v>
       </c>
       <c r="D831" t="str">
         <v/>
@@ -19520,7 +19520,7 @@
         <v>n</v>
       </c>
       <c r="C832" t="str">
-        <v>מקום</v>
+        <v>חלל</v>
       </c>
       <c r="D832" t="str">
         <v/>
@@ -19543,7 +19543,7 @@
         <v>n</v>
       </c>
       <c r="C833" t="str">
-        <v>דיבור:</v>
+        <v>דיבור</v>
       </c>
       <c r="D833" t="str">
         <v/>
@@ -19566,7 +19566,7 @@
         <v>n</v>
       </c>
       <c r="C834" t="str">
-        <v>ספוט</v>
+        <v>מקום</v>
       </c>
       <c r="D834" t="str">
         <v/>
@@ -19589,7 +19589,7 @@
         <v>n</v>
       </c>
       <c r="C835" t="str">
-        <v>הצוות</v>
+        <v>סגל</v>
       </c>
       <c r="D835" t="str">
         <v/>
@@ -19612,7 +19612,7 @@
         <v>n</v>
       </c>
       <c r="C836" t="str">
-        <v>מוקדם.</v>
+        <v>שלב</v>
       </c>
       <c r="D836" t="str">
         <v/>
@@ -19635,7 +19635,7 @@
         <v>adj</v>
       </c>
       <c r="C837" t="str">
-        <v>רגיל</v>
+        <v>סטנדרטי</v>
       </c>
       <c r="D837" t="str">
         <v/>
@@ -19727,7 +19727,7 @@
         <v>n</v>
       </c>
       <c r="C841" t="str">
-        <v>אדים, קיטור</v>
+        <v>קיטור</v>
       </c>
       <c r="D841" t="str">
         <v/>
@@ -19796,7 +19796,7 @@
         <v>n</v>
       </c>
       <c r="C844" t="str">
-        <v>כאב בטן</v>
+        <v>כאבי בטן</v>
       </c>
       <c r="D844" t="str">
         <v/>
@@ -19842,7 +19842,7 @@
         <v>v</v>
       </c>
       <c r="C846" t="str">
-        <v>לעצור</v>
+        <v>עצירה</v>
       </c>
       <c r="D846" t="str">
         <v/>
@@ -19865,7 +19865,7 @@
         <v>n</v>
       </c>
       <c r="C847" t="str">
-        <v>לעצור</v>
+        <v>עצירה</v>
       </c>
       <c r="D847" t="str">
         <v/>
@@ -19911,7 +19911,7 @@
         <v>adv</v>
       </c>
       <c r="C849" t="str">
-        <v>ישירות</v>
+        <v>ישר</v>
       </c>
       <c r="D849" t="str">
         <v>straight away</v>
@@ -19934,7 +19934,7 @@
         <v>n</v>
       </c>
       <c r="C850" t="str">
-        <v>תות שדה</v>
+        <v>תות</v>
       </c>
       <c r="D850" t="str">
         <v/>
@@ -19980,7 +19980,7 @@
         <v>adv</v>
       </c>
       <c r="C852" t="str">
-        <v>בְּתוֹקֶף</v>
+        <v>חזק</v>
       </c>
       <c r="D852" t="str">
         <v>strongly</v>
@@ -20003,7 +20003,7 @@
         <v>n</v>
       </c>
       <c r="C853" t="str">
-        <v>ללמוד</v>
+        <v>חדר עבודה)</v>
       </c>
       <c r="D853" t="str">
         <v/>
@@ -20072,7 +20072,7 @@
         <v>v</v>
       </c>
       <c r="C856" t="str">
-        <v>מצליח</v>
+        <v>להצליח</v>
       </c>
       <c r="D856" t="str">
         <v/>
@@ -20095,7 +20095,7 @@
         <v/>
       </c>
       <c r="C857" t="str">
-        <v>כזה/כזה</v>
+        <v>כזה</v>
       </c>
       <c r="D857" t="str">
         <v/>
@@ -20118,7 +20118,7 @@
         <v/>
       </c>
       <c r="C858" t="str">
-        <v>כגון,</v>
+        <v>כגון</v>
       </c>
       <c r="D858" t="str">
         <v/>
@@ -20141,7 +20141,7 @@
         <v>v</v>
       </c>
       <c r="C859" t="str">
-        <v>להציע (li-hitsi‘a)</v>
+        <v>להציע</v>
       </c>
       <c r="D859" t="str">
         <v>suggestion</v>
@@ -20187,7 +20187,7 @@
         <v>n</v>
       </c>
       <c r="C861" t="str">
-        <v>משקפי_שמש</v>
+        <v>משקפי שמש</v>
       </c>
       <c r="D861" t="str">
         <v/>
@@ -20233,7 +20233,7 @@
         <v>adv</v>
       </c>
       <c r="C863" t="str">
-        <v>בוודאי .</v>
+        <v>ללא ספק</v>
       </c>
       <c r="D863" t="str">
         <v>ensure</v>
@@ -20371,7 +20371,7 @@
         <v/>
       </c>
       <c r="C869" t="str">
-        <v>לעשות מבחן</v>
+        <v>לגשת לבחינה</v>
       </c>
       <c r="D869" t="str">
         <v/>
@@ -20394,7 +20394,7 @@
         <v/>
       </c>
       <c r="C870" t="str">
-        <v>לקחת מישהו/מישהו ברצינות</v>
+        <v>לקחת את sb/sth ברצינות</v>
       </c>
       <c r="D870" t="str">
         <v/>
@@ -20417,7 +20417,7 @@
         <v/>
       </c>
       <c r="C871" t="str">
-        <v>לקחת משהו בחזרה או לקחת משהו בחזרה</v>
+        <v>לקחת sth בחזרה או לקחת בחזרה sth</v>
       </c>
       <c r="D871" t="str">
         <v/>
@@ -20440,7 +20440,7 @@
         <v/>
       </c>
       <c r="C872" t="str">
-        <v>להוציא משהו או להוציא משהו</v>
+        <v>להוציא sth או להוציא sth</v>
       </c>
       <c r="D872" t="str">
         <v/>
@@ -20463,7 +20463,7 @@
         <v>n, v</v>
       </c>
       <c r="C873" t="str">
-        <v>לטעום</v>
+        <v>טעם</v>
       </c>
       <c r="D873" t="str">
         <v/>
@@ -20486,7 +20486,7 @@
         <v>n</v>
       </c>
       <c r="C874" t="str">
-        <v>חינוך</v>
+        <v>הוראה</v>
       </c>
       <c r="D874" t="str">
         <v/>
@@ -20509,7 +20509,7 @@
         <v>n</v>
       </c>
       <c r="C875" t="str">
-        <v>צוות</v>
+        <v>קבוצה</v>
       </c>
       <c r="D875" t="str">
         <v/>
@@ -20578,7 +20578,7 @@
         <v>n</v>
       </c>
       <c r="C878" t="str">
-        <v>הנדסה</v>
+        <v>טכנולוגיה</v>
       </c>
       <c r="D878" t="str">
         <v>technological</v>
@@ -20601,7 +20601,7 @@
         <v>n</v>
       </c>
       <c r="C879" t="str">
-        <v>גיל נעורים</v>
+        <v>מתבגר</v>
       </c>
       <c r="D879" t="str">
         <v>teenage</v>
@@ -20647,7 +20647,7 @@
         <v/>
       </c>
       <c r="C881" t="str">
-        <v>להגיד לאדם לעשות משהו</v>
+        <v>תגיד ל-sb לעשות את זה</v>
       </c>
       <c r="D881" t="str">
         <v/>
@@ -20670,7 +20670,7 @@
         <v/>
       </c>
       <c r="C882" t="str">
-        <v>נוטים לעשות משהו</v>
+        <v>נוטים לעשות דבר</v>
       </c>
       <c r="D882" t="str">
         <v/>
@@ -20693,7 +20693,7 @@
         <v>adj</v>
       </c>
       <c r="C883" t="str">
-        <v>גרוע</v>
+        <v>נורא</v>
       </c>
       <c r="D883" t="str">
         <v>terribly</v>
@@ -20716,7 +20716,7 @@
         <v>adj</v>
       </c>
       <c r="C884" t="str">
-        <v>גרוע</v>
+        <v>נורא</v>
       </c>
       <c r="D884" t="str">
         <v>terribly</v>
@@ -20762,7 +20762,7 @@
         <v>n</v>
       </c>
       <c r="C886" t="str">
-        <v>תודה.</v>
+        <v>תודה</v>
       </c>
       <c r="D886" t="str">
         <v/>
@@ -20785,7 +20785,7 @@
         <v>det</v>
       </c>
       <c r="C887" t="str">
-        <v>החוב</v>
+        <v>זה</v>
       </c>
       <c r="D887" t="str">
         <v/>
@@ -20808,7 +20808,7 @@
         <v>pron</v>
       </c>
       <c r="C888" t="str">
-        <v>החוב</v>
+        <v>זה</v>
       </c>
       <c r="D888" t="str">
         <v/>
@@ -20831,7 +20831,7 @@
         <v/>
       </c>
       <c r="C889" t="str">
-        <v>זה בסדר.</v>
+        <v>זה בסדר</v>
       </c>
       <c r="D889" t="str">
         <v/>
@@ -20854,7 +20854,7 @@
         <v/>
       </c>
       <c r="C890" t="str">
-        <v>האוויר</v>
+        <v>את האוויר</v>
       </c>
       <c r="D890" t="str">
         <v/>
@@ -20900,7 +20900,7 @@
         <v/>
       </c>
       <c r="C892" t="str">
-        <v>הכי טוב!</v>
+        <v>מיטב</v>
       </c>
       <c r="D892" t="str">
         <v/>
@@ -20923,7 +20923,7 @@
         <v/>
       </c>
       <c r="C893" t="str">
-        <v>תבוא מחרתיים.</v>
+        <v>מחרתיים</v>
       </c>
       <c r="D893" t="str">
         <v/>
@@ -20946,7 +20946,7 @@
         <v/>
       </c>
       <c r="C894" t="str">
-        <v>שלפני אתמול</v>
+        <v>שלשום</v>
       </c>
       <c r="D894" t="str">
         <v/>
@@ -20969,7 +20969,7 @@
         <v/>
       </c>
       <c r="C895" t="str">
-        <v>הכלים.</v>
+        <v>המנות</v>
       </c>
       <c r="D895" t="str">
         <v/>
@@ -21038,7 +21038,7 @@
         <v/>
       </c>
       <c r="C898" t="str">
-        <v>הכי מושך / חשוב / פופולרי וכו'.</v>
+        <v>הכי אטרקטיבי/חשוב/פופולרי וכו'.</v>
       </c>
       <c r="D898" t="str">
         <v/>
@@ -21061,7 +21061,7 @@
         <v/>
       </c>
       <c r="C899" t="str">
-        <v>אותו הדבר.</v>
+        <v>אותו הדבר</v>
       </c>
       <c r="D899" t="str">
         <v/>
@@ -21107,7 +21107,7 @@
         <v>n</v>
       </c>
       <c r="C901" t="str">
-        <v>תיאטרון</v>
+        <v>תאטרון</v>
       </c>
       <c r="D901" t="str">
         <v/>
@@ -21176,7 +21176,7 @@
         <v>adv</v>
       </c>
       <c r="C904" t="str">
-        <v>אז</v>
+        <v>ואז</v>
       </c>
       <c r="D904" t="str">
         <v/>
@@ -21222,7 +21222,7 @@
         <v/>
       </c>
       <c r="C906" t="str">
-        <v>אין ספק.</v>
+        <v>אין ספק</v>
       </c>
       <c r="D906" t="str">
         <v/>
@@ -21268,7 +21268,7 @@
         <v/>
       </c>
       <c r="C908" t="str">
-        <v>לחשוב על משהו</v>
+        <v>לחשוב על sth</v>
       </c>
       <c r="D908" t="str">
         <v/>
@@ -21314,7 +21314,7 @@
         <v>adv</v>
       </c>
       <c r="C910" t="str">
-        <v>למרות זאת</v>
+        <v>אמנם</v>
       </c>
       <c r="D910" t="str">
         <v/>
@@ -21337,7 +21337,7 @@
         <v>n</v>
       </c>
       <c r="C911" t="str">
-        <v>רעיון</v>
+        <v>מחשבה</v>
       </c>
       <c r="D911" t="str">
         <v/>
@@ -21383,7 +21383,7 @@
         <v>n</v>
       </c>
       <c r="C913" t="str">
-        <v>לוע</v>
+        <v>גרון</v>
       </c>
       <c r="D913" t="str">
         <v/>
@@ -21429,7 +21429,7 @@
         <v>n</v>
       </c>
       <c r="C915" t="str">
-        <v>רעמים</v>
+        <v>רעם</v>
       </c>
       <c r="D915" t="str">
         <v>thunderstorm</v>
@@ -21452,7 +21452,7 @@
         <v/>
       </c>
       <c r="C916" t="str">
-        <v>לסדר (sth) או לסדר (sth)</v>
+        <v>לסדר או לסדר up</v>
       </c>
       <c r="D916" t="str">
         <v/>
@@ -21475,7 +21475,7 @@
         <v>v</v>
       </c>
       <c r="C917" t="str">
-        <v>לקשור</v>
+        <v>עניבה</v>
       </c>
       <c r="D917" t="str">
         <v/>
@@ -21498,7 +21498,7 @@
         <v>n</v>
       </c>
       <c r="C918" t="str">
-        <v>לקשור</v>
+        <v>עניבה</v>
       </c>
       <c r="D918" t="str">
         <v/>
@@ -21544,7 +21544,7 @@
         <v>n</v>
       </c>
       <c r="C920" t="str">
-        <v>לו"ז</v>
+        <v>לוח זמנים</v>
       </c>
       <c r="D920" t="str">
         <v/>
@@ -21636,7 +21636,7 @@
         <v>prep</v>
       </c>
       <c r="C924" t="str">
-        <v>אֶל</v>
+        <v>כדי</v>
       </c>
       <c r="D924" t="str">
         <v/>
@@ -21705,7 +21705,7 @@
         <v>n</v>
       </c>
       <c r="C927" t="str">
-        <v>אצבע רגל</v>
+        <v>אצבע</v>
       </c>
       <c r="D927" t="str">
         <v>toenail</v>
@@ -21728,7 +21728,7 @@
         <v>adv</v>
       </c>
       <c r="C928" t="str">
-        <v>יַחַד</v>
+        <v>ביחד</v>
       </c>
       <c r="D928" t="str">
         <v/>
@@ -21843,7 +21843,7 @@
         <v>adj, adv</v>
       </c>
       <c r="C933" t="str">
-        <v>רֹאשׁ</v>
+        <v>למעלה</v>
       </c>
       <c r="D933" t="str">
         <v/>
@@ -21889,7 +21889,7 @@
         <v>adj</v>
       </c>
       <c r="C935" t="str">
-        <v>סַך הַכֹּל</v>
+        <v>סה"כ</v>
       </c>
       <c r="D935" t="str">
         <v>totally</v>
@@ -21912,7 +21912,7 @@
         <v>v, n</v>
       </c>
       <c r="C936" t="str">
-        <v>לגעת</v>
+        <v>מגע</v>
       </c>
       <c r="D936" t="str">
         <v/>
@@ -22027,7 +22027,7 @@
         <v>n, v</v>
       </c>
       <c r="C941" t="str">
-        <v>סַחַר</v>
+        <v>מסחר</v>
       </c>
       <c r="D941" t="str">
         <v/>
@@ -22073,7 +22073,7 @@
         <v>v</v>
       </c>
       <c r="C943" t="str">
-        <v>רכבת</v>
+        <v>להתאמן</v>
       </c>
       <c r="D943" t="str">
         <v>training trainer</v>
@@ -22165,7 +22165,7 @@
         <v>n</v>
       </c>
       <c r="C947" t="str">
-        <v>צָרָה</v>
+        <v>צרות</v>
       </c>
       <c r="D947" t="str">
         <v/>
@@ -22257,7 +22257,7 @@
         <v>v</v>
       </c>
       <c r="C951" t="str">
-        <v>לְנַסוֹת</v>
+        <v>נסה</v>
       </c>
       <c r="D951" t="str">
         <v/>
@@ -22349,7 +22349,7 @@
         <v>v</v>
       </c>
       <c r="C955" t="str">
-        <v>לפנות</v>
+        <v>להפוך</v>
       </c>
       <c r="D955" t="str">
         <v/>
@@ -22372,7 +22372,7 @@
         <v>n</v>
       </c>
       <c r="C956" t="str">
-        <v>חֲרִיטָה</v>
+        <v>פנייה</v>
       </c>
       <c r="D956" t="str">
         <v/>
@@ -22625,7 +22625,7 @@
         <v/>
       </c>
       <c r="C967" t="str">
-        <v>נהג לעשות/להיות sth</v>
+        <v>נהג לעשות/להיות דבר</v>
       </c>
       <c r="D967" t="str">
         <v/>
@@ -22694,7 +22694,7 @@
         <v>n</v>
       </c>
       <c r="C970" t="str">
-        <v>נגיף</v>
+        <v>וירוס</v>
       </c>
       <c r="D970" t="str">
         <v/>
@@ -22717,7 +22717,7 @@
         <v>v</v>
       </c>
       <c r="C971" t="str">
-        <v>לבקר</v>
+        <v>בקר</v>
       </c>
       <c r="D971" t="str">
         <v/>
@@ -22763,7 +22763,7 @@
         <v>n</v>
       </c>
       <c r="C973" t="str">
-        <v>כֶּרֶך</v>
+        <v>עוצמת קול</v>
       </c>
       <c r="D973" t="str">
         <v/>
@@ -22993,7 +22993,7 @@
         <v>adv</v>
       </c>
       <c r="C983" t="str">
-        <v>בריא</v>
+        <v>טוב</v>
       </c>
       <c r="D983" t="str">
         <v/>
@@ -23039,7 +23039,7 @@
         <v>adj</v>
       </c>
       <c r="C985" t="str">
-        <v>רָטוֹב</v>
+        <v>רטוב )</v>
       </c>
       <c r="D985" t="str">
         <v/>
@@ -23177,7 +23177,7 @@
         <v>det, pron</v>
       </c>
       <c r="C991" t="str">
-        <v>אֵיזֶה</v>
+        <v>אשר</v>
       </c>
       <c r="D991" t="str">
         <v/>
@@ -23361,7 +23361,7 @@
         <v>n</v>
       </c>
       <c r="C999" t="str">
-        <v>אֲגַף</v>
+        <v>כנף</v>
       </c>
       <c r="D999" t="str">
         <v/>
@@ -23384,7 +23384,7 @@
         <v>v, n</v>
       </c>
       <c r="C1000" t="str">
-        <v>משאלה</v>
+        <v>בקשה</v>
       </c>
       <c r="D1000" t="str">
         <v/>
@@ -23453,7 +23453,7 @@
         <v>v</v>
       </c>
       <c r="C1003" t="str">
-        <v>לעבוד</v>
+        <v>עבודה</v>
       </c>
       <c r="D1003" t="str">
         <v>working</v>
@@ -23545,7 +23545,7 @@
         <v/>
       </c>
       <c r="C1007" t="str">
-        <v>אשמח (לעשות)</v>
+        <v>אשמח</v>
       </c>
       <c r="D1007" t="str">
         <v/>
@@ -23637,7 +23637,7 @@
         <v>adj</v>
       </c>
       <c r="C1011" t="str">
-        <v>טָעוּת</v>
+        <v>שגוי</v>
       </c>
       <c r="D1011" t="str">
         <v/>
@@ -23844,7 +23844,7 @@
         <v>adv</v>
       </c>
       <c r="C1020" t="str">
-        <v>בְּהֶחלֵט</v>
+        <v>לחלוטין</v>
       </c>
       <c r="D1020" t="str">
         <v>absolute</v>
@@ -23913,7 +23913,7 @@
         <v>v</v>
       </c>
       <c r="C1023" t="str">
-        <v>קבלה</v>
+        <v>לקבל</v>
       </c>
       <c r="D1023" t="str">
         <v>acceptable</v>
@@ -23982,7 +23982,7 @@
         <v>n, v</v>
       </c>
       <c r="C1026" t="str">
-        <v>חוֹק</v>
+        <v>לפעול</v>
       </c>
       <c r="D1026" t="str">
         <v>actor actress</v>
@@ -24189,7 +24189,7 @@
         <v>v</v>
       </c>
       <c r="C1035" t="str">
-        <v>לְהַסכִּים</v>
+        <v>מסכים</v>
       </c>
       <c r="D1035" t="str">
         <v>agreement</v>
@@ -24258,7 +24258,7 @@
         <v>v, n</v>
       </c>
       <c r="C1038" t="str">
-        <v>מַטָרָה</v>
+        <v>לכוון</v>
       </c>
       <c r="D1038" t="str">
         <v>aim to do sth</v>
@@ -24718,7 +24718,7 @@
         <v>n</v>
       </c>
       <c r="C1058" t="str">
-        <v>בַּקָשָׁה</v>
+        <v>אפליקציה</v>
       </c>
       <c r="D1058" t="str">
         <v/>
@@ -24741,7 +24741,7 @@
         <v>v</v>
       </c>
       <c r="C1059" t="str">
-        <v>לִפְנוֹת</v>
+        <v>להחיל</v>
       </c>
       <c r="D1059" t="str">
         <v>application</v>
@@ -24787,7 +24787,7 @@
         <v>v, n</v>
       </c>
       <c r="C1061" t="str">
-        <v>גִישָׁה</v>
+        <v>להתקרב</v>
       </c>
       <c r="D1061" t="str">
         <v/>
@@ -24879,7 +24879,7 @@
         <v>n</v>
       </c>
       <c r="C1065" t="str">
-        <v>כירורגיה פלסטית</v>
+        <v>אזור</v>
       </c>
       <c r="D1065" t="str">
         <v/>
@@ -24902,7 +24902,7 @@
         <v>v</v>
       </c>
       <c r="C1066" t="str">
-        <v>טיעון</v>
+        <v>להתווכח</v>
       </c>
       <c r="D1066" t="str">
         <v>argument</v>
@@ -24925,7 +24925,7 @@
         <v>v</v>
       </c>
       <c r="C1067" t="str">
-        <v>לסדר</v>
+        <v>לארגן</v>
       </c>
       <c r="D1067" t="str">
         <v>arrangement</v>
@@ -25017,7 +25017,7 @@
         <v/>
       </c>
       <c r="C1071" t="str">
-        <v>ככל הידוע לי/עד כמה שידוע לי</v>
+        <v>עד כמה שידוע לי</v>
       </c>
       <c r="D1071" t="str">
         <v/>
@@ -25040,7 +25040,7 @@
         <v/>
       </c>
       <c r="C1072" t="str">
-        <v>כל עוד</v>
+        <v>ככל/כל עוד</v>
       </c>
       <c r="D1072" t="str">
         <v/>
@@ -25063,7 +25063,7 @@
         <v>n</v>
       </c>
       <c r="C1073" t="str">
-        <v>הבעת פנים</v>
+        <v>אספקט</v>
       </c>
       <c r="D1073" t="str">
         <v/>
@@ -25086,7 +25086,7 @@
         <v>v</v>
       </c>
       <c r="C1074" t="str">
-        <v>הערכה</v>
+        <v>להעריך</v>
       </c>
       <c r="D1074" t="str">
         <v>assessment</v>
@@ -25132,7 +25132,7 @@
         <v/>
       </c>
       <c r="C1076" t="str">
-        <v>סוף סוף (לאורך זמן)</v>
+        <v>סוף סוף .</v>
       </c>
       <c r="D1076" t="str">
         <v/>
@@ -25155,7 +25155,7 @@
         <v/>
       </c>
       <c r="C1077" t="str">
-        <v>בכלל לא.</v>
+        <v>בכלל</v>
       </c>
       <c r="D1077" t="str">
         <v/>
@@ -25247,7 +25247,7 @@
         <v/>
       </c>
       <c r="C1081" t="str">
-        <v>באותו הזמן.</v>
+        <v>באותו זמן</v>
       </c>
       <c r="D1081" t="str">
         <v/>
@@ -25270,7 +25270,7 @@
         <v>n</v>
       </c>
       <c r="C1082" t="str">
-        <v>ספורטאי</v>
+        <v>אתלט</v>
       </c>
       <c r="D1082" t="str">
         <v/>
@@ -25293,7 +25293,7 @@
         <v>v</v>
       </c>
       <c r="C1083" t="str">
-        <v>צירוף</v>
+        <v>לצרף</v>
       </c>
       <c r="D1083" t="str">
         <v/>
@@ -25316,7 +25316,7 @@
         <v>n, v</v>
       </c>
       <c r="C1084" t="str">
-        <v>מתקפה</v>
+        <v>לתקוף</v>
       </c>
       <c r="D1084" t="str">
         <v/>
@@ -25339,7 +25339,7 @@
         <v>n, v</v>
       </c>
       <c r="C1085" t="str">
-        <v>נסיון</v>
+        <v>לנסות</v>
       </c>
       <c r="D1085" t="str">
         <v/>
@@ -25362,7 +25362,7 @@
         <v/>
       </c>
       <c r="C1086" t="str">
-        <v>ללכת לכנסייה / מכללה / בית ספר וכו'.</v>
+        <v>ללמוד בכנסייה / מכללה / בית ספר וכו'.</v>
       </c>
       <c r="D1086" t="str">
         <v/>
@@ -25385,7 +25385,7 @@
         <v>v</v>
       </c>
       <c r="C1087" t="str">
-        <v>קשב</v>
+        <v>לטפל</v>
       </c>
       <c r="D1087" t="str">
         <v>attendance</v>
@@ -25431,7 +25431,7 @@
         <v>n</v>
       </c>
       <c r="C1089" t="str">
-        <v>מתן הרשאות</v>
+        <v>רשות</v>
       </c>
       <c r="D1089" t="str">
         <v/>
@@ -25454,7 +25454,7 @@
         <v>n</v>
       </c>
       <c r="C1090" t="str">
-        <v>תמונת הפרופיל</v>
+        <v>גלגול</v>
       </c>
       <c r="D1090" t="str">
         <v/>
@@ -25477,7 +25477,7 @@
         <v>n</v>
       </c>
       <c r="C1091" t="str">
-        <v>טוב</v>
+        <v>ממוצע</v>
       </c>
       <c r="D1091" t="str">
         <v/>
@@ -25500,7 +25500,7 @@
         <v>v</v>
       </c>
       <c r="C1092" t="str">
-        <v>הימנע</v>
+        <v>להמנע</v>
       </c>
       <c r="D1092" t="str">
         <v/>
@@ -25546,7 +25546,7 @@
         <v>adj</v>
       </c>
       <c r="C1094" t="str">
-        <v>מודעות</v>
+        <v>מודע</v>
       </c>
       <c r="D1094" t="str">
         <v/>
@@ -25569,7 +25569,7 @@
         <v>adj</v>
       </c>
       <c r="C1095" t="str">
-        <v>נוראיתThe quality of music</v>
+        <v>נורא</v>
       </c>
       <c r="D1095" t="str">
         <v/>
@@ -25592,7 +25592,7 @@
         <v>v</v>
       </c>
       <c r="C1096" t="str">
-        <v>שמרטף</v>
+        <v>לשמור על הטף</v>
       </c>
       <c r="D1096" t="str">
         <v>babysitter</v>
@@ -25615,7 +25615,7 @@
         <v>n, v</v>
       </c>
       <c r="C1097" t="str">
-        <v>לאזן</v>
+        <v>איזון</v>
       </c>
       <c r="D1097" t="str">
         <v/>
@@ -25661,7 +25661,7 @@
         <v>n</v>
       </c>
       <c r="C1099" t="str">
-        <v>עיצוב_שיער</v>
+        <v>ספר</v>
       </c>
       <c r="D1099" t="str">
         <v/>
@@ -25684,7 +25684,7 @@
         <v/>
       </c>
       <c r="C1100" t="str">
-        <v>לבסס משהו על משהו</v>
+        <v>בסיס sth על sth</v>
       </c>
       <c r="D1100" t="str">
         <v/>
@@ -25730,7 +25730,7 @@
         <v>adj</v>
       </c>
       <c r="C1102" t="str">
-        <v>בסיסית</v>
+        <v>בסיסי</v>
       </c>
       <c r="D1102" t="str">
         <v/>
@@ -25822,7 +25822,7 @@
         <v/>
       </c>
       <c r="C1106" t="str">
-        <v>מת/למות לעשות משהו</v>
+        <v>למות על/לעשות משהו</v>
       </c>
       <c r="D1106" t="str">
         <v/>
@@ -25845,7 +25845,7 @@
         <v/>
       </c>
       <c r="C1107" t="str">
-        <v>להיות מצפה לילד/ילדה</v>
+        <v>מצפה ל-sb/sth</v>
       </c>
       <c r="D1107" t="str">
         <v/>
@@ -25868,7 +25868,7 @@
         <v/>
       </c>
       <c r="C1108" t="str">
-        <v>להיות מכיר/ה את המילה/מילה בשפת האם</v>
+        <v>להכיר sth/sb</v>
       </c>
       <c r="D1108" t="str">
         <v/>
@@ -25891,7 +25891,7 @@
         <v/>
       </c>
       <c r="C1109" t="str">
-        <v>להיות חברים (עם מישהו)</v>
+        <v>להיות חברים</v>
       </c>
       <c r="D1109" t="str">
         <v/>
@@ -25937,7 +25937,7 @@
         <v/>
       </c>
       <c r="C1111" t="str">
-        <v>להיות בעניין של משהו</v>
+        <v>להיות בעניין</v>
       </c>
       <c r="D1111" t="str">
         <v/>
@@ -25960,7 +25960,7 @@
         <v/>
       </c>
       <c r="C1112" t="str">
-        <v>להיות ידוע כ-sth</v>
+        <v>להיות ידוע בשם sth</v>
       </c>
       <c r="D1112" t="str">
         <v/>
@@ -25983,7 +25983,7 @@
         <v/>
       </c>
       <c r="C1113" t="str">
-        <v>להיות חסר במה</v>
+        <v>להיות קצר של sth</v>
       </c>
       <c r="D1113" t="str">
         <v/>
@@ -26006,7 +26006,7 @@
         <v/>
       </c>
       <c r="C1114" t="str">
-        <v>להיות מוכן</v>
+        <v>להיות עד sb</v>
       </c>
       <c r="D1114" t="str">
         <v/>
@@ -26029,7 +26029,7 @@
         <v/>
       </c>
       <c r="C1115" t="str">
-        <v>להיות מוכן למשהו</v>
+        <v>להיות עד הסוף</v>
       </c>
       <c r="D1115" t="str">
         <v/>
@@ -26052,7 +26052,7 @@
         <v/>
       </c>
       <c r="C1116" t="str">
-        <v>מוזמנים לעשות משהו</v>
+        <v>מוזמן לעשות sth</v>
       </c>
       <c r="D1116" t="str">
         <v/>
@@ -26075,7 +26075,7 @@
         <v/>
       </c>
       <c r="C1117" t="str">
-        <v>שווה משהו/לעשות משהו</v>
+        <v>להיות שווה sth / לעשות sth</v>
       </c>
       <c r="D1117" t="str">
         <v/>
@@ -26121,7 +26121,7 @@
         <v>n</v>
       </c>
       <c r="C1119" t="str">
-        <v>פולי קפה</v>
+        <v>שעועית</v>
       </c>
       <c r="D1119" t="str">
         <v/>
@@ -26167,7 +26167,7 @@
         <v>v</v>
       </c>
       <c r="C1121" t="str">
-        <v>משקל</v>
+        <v>לנצח</v>
       </c>
       <c r="D1121" t="str">
         <v/>
@@ -26190,7 +26190,7 @@
         <v/>
       </c>
       <c r="C1122" t="str">
-        <v>להפוך לזמין/עשיר/לסופר וכו'.</v>
+        <v>להיות זמין/עשיר/כותב וכו'.</v>
       </c>
       <c r="D1122" t="str">
         <v/>
@@ -26236,7 +26236,7 @@
         <v>n</v>
       </c>
       <c r="C1124" t="str">
-        <v>בשר בקר</v>
+        <v>בקר</v>
       </c>
       <c r="D1124" t="str">
         <v/>
@@ -26282,7 +26282,7 @@
         <v/>
       </c>
       <c r="C1126" t="str">
-        <v>לפני/אחרי רדת החשיכה</v>
+        <v>לפני/אחרי החשיכה</v>
       </c>
       <c r="D1126" t="str">
         <v/>
@@ -26328,7 +26328,7 @@
         <v/>
       </c>
       <c r="C1128" t="str">
-        <v>שייך ל-sth</v>
+        <v>שייך לס</v>
       </c>
       <c r="D1128" t="str">
         <v/>
@@ -26443,7 +26443,7 @@
         <v>n</v>
       </c>
       <c r="C1133" t="str">
-        <v>חשבונית</v>
+        <v>חשבון</v>
       </c>
       <c r="D1133" t="str">
         <v/>
@@ -26466,7 +26466,7 @@
         <v>n</v>
       </c>
       <c r="C1134" t="str">
-        <v>בליון</v>
+        <v>מיליארד</v>
       </c>
       <c r="D1134" t="str">
         <v/>
@@ -26512,7 +26512,7 @@
         <v/>
       </c>
       <c r="C1136" t="str">
-        <v>צפייה בינג'</v>
+        <v>שעון בינג'</v>
       </c>
       <c r="D1136" t="str">
         <v/>
@@ -26535,7 +26535,7 @@
         <v>n</v>
       </c>
       <c r="C1137" t="str">
-        <v>לידה</v>
+        <v>הולדת</v>
       </c>
       <c r="D1137" t="str">
         <v/>
@@ -26627,7 +26627,7 @@
         <v>adj</v>
       </c>
       <c r="C1141" t="str">
-        <v>עוור</v>
+        <v>לסמא</v>
       </c>
       <c r="D1141" t="str">
         <v/>
@@ -26834,7 +26834,7 @@
         <v>v</v>
       </c>
       <c r="C1150" t="str">
-        <v>טרח</v>
+        <v>להטריד</v>
       </c>
       <c r="D1150" t="str">
         <v/>
@@ -26857,7 +26857,7 @@
         <v>n</v>
       </c>
       <c r="C1151" t="str">
-        <v>למטה</v>
+        <v>תחתון</v>
       </c>
       <c r="D1151" t="str">
         <v/>
@@ -26903,7 +26903,7 @@
         <v/>
       </c>
       <c r="C1153" t="str">
-        <v>לשבור/לחתוך וכו'. משהו לשניים</v>
+        <v>לשבור/לחתוך וכו' לחצי</v>
       </c>
       <c r="D1153" t="str">
         <v/>
@@ -26926,7 +26926,7 @@
         <v>n</v>
       </c>
       <c r="C1154" t="str">
-        <v>נפש</v>
+        <v>נשימה</v>
       </c>
       <c r="D1154" t="str">
         <v>breathe</v>
@@ -26949,7 +26949,7 @@
         <v>adj</v>
       </c>
       <c r="C1155" t="str">
-        <v>מעגלים קלועים</v>
+        <v>קצר</v>
       </c>
       <c r="D1155" t="str">
         <v>briefly</v>
@@ -26972,7 +26972,7 @@
         <v/>
       </c>
       <c r="C1156" t="str">
-        <v>להביא (לדוגמה) אושר / מזל / שלום וכו'.</v>
+        <v>להביא אושר / מזל / שלום וכו'.</v>
       </c>
       <c r="D1156" t="str">
         <v/>
@@ -27018,7 +27018,7 @@
         <v>v, n</v>
       </c>
       <c r="C1158" t="str">
-        <v>שידור</v>
+        <v>משדר</v>
       </c>
       <c r="D1158" t="str">
         <v/>
@@ -27110,7 +27110,7 @@
         <v>n</v>
       </c>
       <c r="C1162" t="str">
-        <v>בורגר</v>
+        <v>המבורגר</v>
       </c>
       <c r="D1162" t="str">
         <v>hamburger</v>
@@ -27133,7 +27133,7 @@
         <v>v</v>
       </c>
       <c r="C1163" t="str">
-        <v>צרוב</v>
+        <v>לשרוף</v>
       </c>
       <c r="D1163" t="str">
         <v/>
@@ -27202,7 +27202,7 @@
         <v>n</v>
       </c>
       <c r="C1166" t="str">
-        <v>כפתור</v>
+        <v>לחצן</v>
       </c>
       <c r="D1166" t="str">
         <v/>
@@ -27225,7 +27225,7 @@
         <v>prep</v>
       </c>
       <c r="C1167" t="str">
-        <v>על ידי</v>
+        <v>ליד</v>
       </c>
       <c r="D1167" t="str">
         <v/>
@@ -27271,7 +27271,7 @@
         <v/>
       </c>
       <c r="C1169" t="str">
-        <v>ביד?</v>
+        <v>ביד</v>
       </c>
       <c r="D1169" t="str">
         <v/>
@@ -27294,7 +27294,7 @@
         <v/>
       </c>
       <c r="C1170" t="str">
-        <v>בעל פה.</v>
+        <v>בעל פה</v>
       </c>
       <c r="D1170" t="str">
         <v/>
@@ -27340,7 +27340,7 @@
         <v/>
       </c>
       <c r="C1172" t="str">
-        <v>בניגוד/בניגוד</v>
+        <v>על ידי/בניגוד</v>
       </c>
       <c r="D1172" t="str">
         <v/>
@@ -27409,7 +27409,7 @@
         <v/>
       </c>
       <c r="C1175" t="str">
-        <v>קריאה ל-sb</v>
+        <v>להתקשר ל-sb</v>
       </c>
       <c r="D1175" t="str">
         <v/>
@@ -27455,7 +27455,7 @@
         <v>v</v>
       </c>
       <c r="C1177" t="str">
-        <v>בית שימוש</v>
+        <v>יכול</v>
       </c>
       <c r="D1177" t="str">
         <v/>
@@ -27501,7 +27501,7 @@
         <v>v</v>
       </c>
       <c r="C1179" t="str">
-        <v>מחיקה</v>
+        <v>לבטל</v>
       </c>
       <c r="D1179" t="str">
         <v/>
@@ -27547,7 +27547,7 @@
         <v/>
       </c>
       <c r="C1181" t="str">
-        <v>לא יכול/לא יכול שלא לעשות משהו</v>
+        <v>לא יכול/לא יכול לעזור לעשות דבר כזה</v>
       </c>
       <c r="D1181" t="str">
         <v/>
@@ -27593,7 +27593,7 @@
         <v/>
       </c>
       <c r="C1183" t="str">
-        <v>מסוגל לעשות משהו/לעשות משהו</v>
+        <v>מסוגל sth / לעשות sth</v>
       </c>
       <c r="D1183" t="str">
         <v/>
@@ -27616,7 +27616,7 @@
         <v>n</v>
       </c>
       <c r="C1184" t="str">
-        <v>קפטן</v>
+        <v>סרן</v>
       </c>
       <c r="D1184" t="str">
         <v/>
@@ -27754,7 +27754,7 @@
         <v>n</v>
       </c>
       <c r="C1190" t="str">
-        <v>מופע</v>
+        <v>תיק</v>
       </c>
       <c r="D1190" t="str">
         <v/>
@@ -27777,7 +27777,7 @@
         <v>n</v>
       </c>
       <c r="C1191" t="str">
-        <v>צורה</v>
+        <v>יצוק</v>
       </c>
       <c r="D1191" t="str">
         <v/>
@@ -27800,7 +27800,7 @@
         <v/>
       </c>
       <c r="C1192" t="str">
-        <v>למשוך את תשומת ליבו, העניין וכו' של מישהו.</v>
+        <v>לתפוס את תשומת הלב, העניין וכו' של sb.</v>
       </c>
       <c r="D1192" t="str">
         <v/>
@@ -27869,7 +27869,7 @@
         <v>n, v</v>
       </c>
       <c r="C1195" t="str">
-        <v>סיבה</v>
+        <v>לגרום</v>
       </c>
       <c r="D1195" t="str">
         <v/>
@@ -27892,7 +27892,7 @@
         <v>n</v>
       </c>
       <c r="C1196" t="str">
-        <v>ידוען</v>
+        <v>אישיות מפורסמת</v>
       </c>
       <c r="D1196" t="str">
         <v/>
@@ -27915,7 +27915,7 @@
         <v>adj</v>
       </c>
       <c r="C1197" t="str">
-        <v>מרכז</v>
+        <v>מרכזי</v>
       </c>
       <c r="D1197" t="str">
         <v>centrally</v>
@@ -27938,7 +27938,7 @@
         <v>adj, pron</v>
       </c>
       <c r="C1198" t="str">
-        <v>ודאי</v>
+        <v>מסויים</v>
       </c>
       <c r="D1198" t="str">
         <v/>
@@ -28030,7 +28030,7 @@
         <v>n</v>
       </c>
       <c r="C1202" t="str">
-        <v>הזדמנות</v>
+        <v>סיכוי</v>
       </c>
       <c r="D1202" t="str">
         <v/>
@@ -28076,7 +28076,7 @@
         <v>v</v>
       </c>
       <c r="C1204" t="str">
-        <v>עודף</v>
+        <v>לשנות</v>
       </c>
       <c r="D1204" t="str">
         <v/>
@@ -28122,7 +28122,7 @@
         <v>n</v>
       </c>
       <c r="C1206" t="str">
-        <v>תו</v>
+        <v>אופי</v>
       </c>
       <c r="D1206" t="str">
         <v/>
@@ -28145,7 +28145,7 @@
         <v>n</v>
       </c>
       <c r="C1207" t="str">
-        <v>ארגון צדקה</v>
+        <v>צדקה</v>
       </c>
       <c r="D1207" t="str">
         <v/>
@@ -28168,7 +28168,7 @@
         <v>n</v>
       </c>
       <c r="C1208" t="str">
-        <v>גרף</v>
+        <v>תרשים</v>
       </c>
       <c r="D1208" t="str">
         <v/>
@@ -28306,7 +28306,7 @@
         <v>adj, n</v>
       </c>
       <c r="C1214" t="str">
-        <v>ראשי (Ra'shi) (m)</v>
+        <v>ראש</v>
       </c>
       <c r="D1214" t="str">
         <v/>
@@ -28352,7 +28352,7 @@
         <v>n</v>
       </c>
       <c r="C1216" t="str">
-        <v>סטנסיליםStencils</v>
+        <v>בחירה</v>
       </c>
       <c r="D1216" t="str">
         <v/>
@@ -28375,7 +28375,7 @@
         <v>adj</v>
       </c>
       <c r="C1217" t="str">
-        <v>עיגול</v>
+        <v>עגול</v>
       </c>
       <c r="D1217" t="str">
         <v/>
@@ -28421,7 +28421,7 @@
         <v>n</v>
       </c>
       <c r="C1219" t="str">
-        <v>אזרח/ית</v>
+        <v>אזרח</v>
       </c>
       <c r="D1219" t="str">
         <v/>
@@ -28444,7 +28444,7 @@
         <v>n</v>
       </c>
       <c r="C1220" t="str">
-        <v>שיעור</v>
+        <v>מעמד</v>
       </c>
       <c r="D1220" t="str">
         <v/>
@@ -28467,7 +28467,7 @@
         <v>v, adj</v>
       </c>
       <c r="C1221" t="str">
-        <v>נקה/י חיפוש</v>
+        <v>ברור</v>
       </c>
       <c r="D1221" t="str">
         <v/>
@@ -28605,7 +28605,7 @@
         <v>n</v>
       </c>
       <c r="C1227" t="str">
-        <v>נ.</v>
+        <v>עמית</v>
       </c>
       <c r="D1227" t="str">
         <v/>
@@ -28628,7 +28628,7 @@
         <v>v</v>
       </c>
       <c r="C1228" t="str">
-        <v>איסוף</v>
+        <v>לאסוף</v>
       </c>
       <c r="D1228" t="str">
         <v>collection</v>
@@ -28651,7 +28651,7 @@
         <v>n</v>
       </c>
       <c r="C1229" t="str">
-        <v>מולוי</v>
+        <v>מכללה</v>
       </c>
       <c r="D1229" t="str">
         <v/>
@@ -28674,7 +28674,7 @@
         <v>n</v>
       </c>
       <c r="C1230" t="str">
-        <v>עמודה :</v>
+        <v>עמודה</v>
       </c>
       <c r="D1230" t="str">
         <v/>
@@ -28743,7 +28743,7 @@
         <v/>
       </c>
       <c r="C1233" t="str">
-        <v>בחייך.</v>
+        <v>קדימה!</v>
       </c>
       <c r="D1233" t="str">
         <v/>
@@ -28858,7 +28858,7 @@
         <v>n, v</v>
       </c>
       <c r="C1238" t="str">
-        <v>הודעה</v>
+        <v>הערה</v>
       </c>
       <c r="D1238" t="str">
         <v/>
@@ -28881,7 +28881,7 @@
         <v>v</v>
       </c>
       <c r="C1239" t="str">
-        <v>בצע</v>
+        <v>לבצע</v>
       </c>
       <c r="D1239" t="str">
         <v/>
@@ -28950,7 +28950,7 @@
         <v/>
       </c>
       <c r="C1242" t="str">
-        <v>והגיוני.</v>
+        <v>הגיון</v>
       </c>
       <c r="D1242" t="str">
         <v/>
@@ -28973,7 +28973,7 @@
         <v>adj</v>
       </c>
       <c r="C1243" t="str">
-        <v>משותף (me'shutaf)</v>
+        <v>נפוץ</v>
       </c>
       <c r="D1243" t="str">
         <v>commonly</v>
@@ -29065,7 +29065,7 @@
         <v>v</v>
       </c>
       <c r="C1247" t="str">
-        <v>מלאה</v>
+        <v>מלא</v>
       </c>
       <c r="D1247" t="str">
         <v/>
@@ -29111,7 +29111,7 @@
         <v>v</v>
       </c>
       <c r="C1249" t="str">
-        <v>התרכז</v>
+        <v>להתרכז</v>
       </c>
       <c r="D1249" t="str">
         <v>concentration</v>
@@ -29157,7 +29157,7 @@
         <v>n</v>
       </c>
       <c r="C1251" t="str">
-        <v>החלטה</v>
+        <v>מסקנה</v>
       </c>
       <c r="D1251" t="str">
         <v>conclude</v>
@@ -29180,7 +29180,7 @@
         <v>n</v>
       </c>
       <c r="C1252" t="str">
-        <v>כנס</v>
+        <v>ועידה</v>
       </c>
       <c r="D1252" t="str">
         <v/>
@@ -29203,7 +29203,7 @@
         <v>n</v>
       </c>
       <c r="C1253" t="str">
-        <v>בטוחה,</v>
+        <v>ביטחון עצמי</v>
       </c>
       <c r="D1253" t="str">
         <v>confident</v>
@@ -29226,7 +29226,7 @@
         <v>v</v>
       </c>
       <c r="C1254" t="str">
-        <v>אישור</v>
+        <v>לאשר</v>
       </c>
       <c r="D1254" t="str">
         <v>confirmation</v>
@@ -29318,7 +29318,7 @@
         <v/>
       </c>
       <c r="C1258" t="str">
-        <v>לשקול אדם/כל דבר כמשהו</v>
+        <v>לשקול sb/sth sth</v>
       </c>
       <c r="D1258" t="str">
         <v/>
@@ -29364,7 +29364,7 @@
         <v/>
       </c>
       <c r="C1260" t="str">
-        <v>מורכב מ- sth</v>
+        <v>מורכב מס'</v>
       </c>
       <c r="D1260" t="str">
         <v/>
@@ -29410,7 +29410,7 @@
         <v>n</v>
       </c>
       <c r="C1262" t="str">
-        <v>בנייה</v>
+        <v>בניה</v>
       </c>
       <c r="D1262" t="str">
         <v>construct</v>
@@ -29456,7 +29456,7 @@
         <v>n</v>
       </c>
       <c r="C1264" t="str">
-        <v>ניגודיות</v>
+        <v>להשוות</v>
       </c>
       <c r="D1264" t="str">
         <v/>
@@ -29525,7 +29525,7 @@
         <v>v</v>
       </c>
       <c r="C1267" t="str">
-        <v>המירי</v>
+        <v>להמיר</v>
       </c>
       <c r="D1267" t="str">
         <v/>
@@ -29548,7 +29548,7 @@
         <v>v</v>
       </c>
       <c r="C1268" t="str">
-        <v>מגניב.</v>
+        <v>להתקרר</v>
       </c>
       <c r="D1268" t="str">
         <v/>
@@ -29594,7 +29594,7 @@
         <v>v</v>
       </c>
       <c r="C1270" t="str">
-        <v>הָיָה יָכוֹל</v>
+        <v>יכול</v>
       </c>
       <c r="D1270" t="str">
         <v/>
@@ -29617,7 +29617,7 @@
         <v>n</v>
       </c>
       <c r="C1271" t="str">
-        <v>עיצה</v>
+        <v>מועצה</v>
       </c>
       <c r="D1271" t="str">
         <v/>
@@ -29640,7 +29640,7 @@
         <v>v</v>
       </c>
       <c r="C1272" t="str">
-        <v>ספירה</v>
+        <v>לספור</v>
       </c>
       <c r="D1272" t="str">
         <v/>
@@ -29663,7 +29663,7 @@
         <v>n</v>
       </c>
       <c r="C1273" t="str">
-        <v>איזור</v>
+        <v>מחוז</v>
       </c>
       <c r="D1273" t="str">
         <v/>
@@ -29686,7 +29686,7 @@
         <v>n</v>
       </c>
       <c r="C1274" t="str">
-        <v>הזוג</v>
+        <v>זוג</v>
       </c>
       <c r="D1274" t="str">
         <v/>
@@ -29732,7 +29732,7 @@
         <v>n</v>
       </c>
       <c r="C1276" t="str">
-        <v>בית משפט</v>
+        <v>לחזר</v>
       </c>
       <c r="D1276" t="str">
         <v/>
@@ -29755,7 +29755,7 @@
         <v>n</v>
       </c>
       <c r="C1277" t="str">
-        <v>בעלי חיים</v>
+        <v>יצור</v>
       </c>
       <c r="D1277" t="str">
         <v/>
@@ -29801,7 +29801,7 @@
         <v>n</v>
       </c>
       <c r="C1279" t="str">
-        <v>עבירה</v>
+        <v>פשע</v>
       </c>
       <c r="D1279" t="str">
         <v>criminal</v>
@@ -29847,7 +29847,7 @@
         <v>n</v>
       </c>
       <c r="C1281" t="str">
-        <v>המון</v>
+        <v>קהל</v>
       </c>
       <c r="D1281" t="str">
         <v>crowded</v>
@@ -29916,7 +29916,7 @@
         <v>adj</v>
       </c>
       <c r="C1284" t="str">
-        <v>תלתל</v>
+        <v>אכזרי</v>
       </c>
       <c r="D1284" t="str">
         <v/>
@@ -29985,7 +29985,7 @@
         <v>adj</v>
       </c>
       <c r="C1287" t="str">
-        <v>סקרנית</v>
+        <v>סקרן</v>
       </c>
       <c r="D1287" t="str">
         <v/>
@@ -30054,7 +30054,7 @@
         <v>n</v>
       </c>
       <c r="C1290" t="str">
-        <v>סילבוס</v>
+        <v>תכנית הלימודים</v>
       </c>
       <c r="D1290" t="str">
         <v/>
@@ -30077,7 +30077,7 @@
         <v>n</v>
       </c>
       <c r="C1291" t="str">
-        <v>בהתאמה</v>
+        <v>מנהג</v>
       </c>
       <c r="D1291" t="str">
         <v/>
@@ -30100,7 +30100,7 @@
         <v>n</v>
       </c>
       <c r="C1292" t="str">
-        <v>לחתוך</v>
+        <v>חתך</v>
       </c>
       <c r="D1292" t="str">
         <v/>
@@ -30123,7 +30123,7 @@
         <v/>
       </c>
       <c r="C1293" t="str">
-        <v>לקצץ משהו או לקצץ משהו</v>
+        <v>קצץ sth או תחתוך sth למטה</v>
       </c>
       <c r="D1293" t="str">
         <v/>
@@ -30146,7 +30146,7 @@
         <v/>
       </c>
       <c r="C1294" t="str">
-        <v>לקצץ משהו או לקצץ משהו</v>
+        <v>קצץ sth או תחתוך sth למטה</v>
       </c>
       <c r="D1294" t="str">
         <v/>
@@ -30192,7 +30192,7 @@
         <v>n, v</v>
       </c>
       <c r="C1296" t="str">
-        <v>מחיר</v>
+        <v>נזק</v>
       </c>
       <c r="D1296" t="str">
         <v/>
@@ -30261,7 +30261,7 @@
         <v>n</v>
       </c>
       <c r="C1299" t="str">
-        <v>שדה נתונים</v>
+        <v>נתונים</v>
       </c>
       <c r="D1299" t="str">
         <v>database</v>
@@ -30284,7 +30284,7 @@
         <v/>
       </c>
       <c r="C1300" t="str">
-        <v>להתמודד עם משהו</v>
+        <v>להתמודד עם sth</v>
       </c>
       <c r="D1300" t="str">
         <v/>
@@ -30307,7 +30307,7 @@
         <v/>
       </c>
       <c r="C1301" t="str">
-        <v>גברת נכבדה,</v>
+        <v>גברת נכבדה</v>
       </c>
       <c r="D1301" t="str">
         <v/>
@@ -30330,7 +30330,7 @@
         <v/>
       </c>
       <c r="C1302" t="str">
-        <v>לכבוד: א.</v>
+        <v>אדוני היקר</v>
       </c>
       <c r="D1302" t="str">
         <v/>
@@ -30399,7 +30399,7 @@
         <v>v</v>
       </c>
       <c r="C1305" t="str">
-        <v>הגדרה</v>
+        <v>להגדיר</v>
       </c>
       <c r="D1305" t="str">
         <v>definition</v>
@@ -30422,7 +30422,7 @@
         <v>adj</v>
       </c>
       <c r="C1306" t="str">
-        <v>יידוע</v>
+        <v>מוגדר</v>
       </c>
       <c r="D1306" t="str">
         <v/>
@@ -30445,7 +30445,7 @@
         <v>n</v>
       </c>
       <c r="C1307" t="str">
-        <v>מעלה</v>
+        <v>תואר</v>
       </c>
       <c r="D1307" t="str">
         <v/>
@@ -30468,7 +30468,7 @@
         <v>v</v>
       </c>
       <c r="C1308" t="str">
-        <v>מחיקה</v>
+        <v>למחוק</v>
       </c>
       <c r="D1308" t="str">
         <v/>
@@ -30491,7 +30491,7 @@
         <v>adj</v>
       </c>
       <c r="C1309" t="str">
-        <v>טעים.</v>
+        <v>טעים מאוד</v>
       </c>
       <c r="D1309" t="str">
         <v/>
@@ -30514,7 +30514,7 @@
         <v>n</v>
       </c>
       <c r="C1310" t="str">
-        <v>רפובליקה</v>
+        <v>דמוקרטיה</v>
       </c>
       <c r="D1310" t="str">
         <v>democratic</v>
@@ -30560,7 +30560,7 @@
         <v>v</v>
       </c>
       <c r="C1312" t="str">
-        <v>לדחות</v>
+        <v>להכחיש</v>
       </c>
       <c r="D1312" t="str">
         <v/>
@@ -30583,7 +30583,7 @@
         <v/>
       </c>
       <c r="C1313" t="str">
-        <v>תלוי באדם/במשהו</v>
+        <v>תלוי/על sb/sth</v>
       </c>
       <c r="D1313" t="str">
         <v/>
@@ -30606,7 +30606,7 @@
         <v>n</v>
       </c>
       <c r="C1314" t="str">
-        <v>דיכאון</v>
+        <v>דכאון</v>
       </c>
       <c r="D1314" t="str">
         <v>depressed</v>
@@ -30652,7 +30652,7 @@
         <v>n</v>
       </c>
       <c r="C1316" t="str">
-        <v>כמיהה</v>
+        <v>תשוקה</v>
       </c>
       <c r="D1316" t="str">
         <v/>
@@ -30675,7 +30675,7 @@
         <v>n</v>
       </c>
       <c r="C1317" t="str">
-        <v>שולחן עבודה</v>
+        <v>שולחן העבודה</v>
       </c>
       <c r="D1317" t="str">
         <v/>
@@ -30721,7 +30721,7 @@
         <v>n</v>
       </c>
       <c r="C1319" t="str">
-        <v>פרטים</v>
+        <v>פרט</v>
       </c>
       <c r="D1319" t="str">
         <v>detailed</v>
@@ -30813,7 +30813,7 @@
         <v>n, v</v>
       </c>
       <c r="C1323" t="str">
-        <v>תזונה</v>
+        <v>דיאטה</v>
       </c>
       <c r="D1323" t="str">
         <v/>
@@ -30836,7 +30836,7 @@
         <v>adj</v>
       </c>
       <c r="C1324" t="str">
-        <v>ישירות</v>
+        <v>ישיר</v>
       </c>
       <c r="D1324" t="str">
         <v/>
@@ -30859,7 +30859,7 @@
         <v>n</v>
       </c>
       <c r="C1325" t="str">
-        <v>במאי</v>
+        <v>דירקטור</v>
       </c>
       <c r="D1325" t="str">
         <v/>
@@ -30905,7 +30905,7 @@
         <v>v</v>
       </c>
       <c r="C1327" t="str">
-        <v>לא מסכים</v>
+        <v>לא להסכים</v>
       </c>
       <c r="D1327" t="str">
         <v/>
@@ -30951,7 +30951,7 @@
         <v>n</v>
       </c>
       <c r="C1329" t="str">
-        <v>צלחת.</v>
+        <v>מנה</v>
       </c>
       <c r="D1329" t="str">
         <v/>
@@ -30974,7 +30974,7 @@
         <v>v, n</v>
       </c>
       <c r="C1330" t="str">
-        <v>תצוגה</v>
+        <v>להציג</v>
       </c>
       <c r="D1330" t="str">
         <v/>
@@ -31020,7 +31020,7 @@
         <v>v</v>
       </c>
       <c r="C1332" t="str">
-        <v>צלילה.</v>
+        <v>לצלול</v>
       </c>
       <c r="D1332" t="str">
         <v>diver</v>
@@ -31089,7 +31089,7 @@
         <v/>
       </c>
       <c r="C1335" t="str">
-        <v>תעשה כמיטב יכולתך</v>
+        <v>לעשות כמיטב יכולתך</v>
       </c>
       <c r="D1335" t="str">
         <v/>
@@ -31112,7 +31112,7 @@
         <v>n</v>
       </c>
       <c r="C1336" t="str">
-        <v>סרט תיעודי</v>
+        <v>תעודה</v>
       </c>
       <c r="D1336" t="str">
         <v/>
@@ -31158,7 +31158,7 @@
         <v>n</v>
       </c>
       <c r="C1338" t="str">
-        <v>ביתיות.</v>
+        <v>ביתי</v>
       </c>
       <c r="D1338" t="str">
         <v/>
@@ -31204,7 +31204,7 @@
         <v>v, n</v>
       </c>
       <c r="C1340" t="str">
-        <v>הורדת קובץ</v>
+        <v>להוריד</v>
       </c>
       <c r="D1340" t="str">
         <v/>
@@ -31250,7 +31250,7 @@
         <v/>
       </c>
       <c r="C1342" t="str">
-        <v>גרירה ושחרור</v>
+        <v>גרור ושחרר</v>
       </c>
       <c r="D1342" t="str">
         <v/>
@@ -31411,7 +31411,7 @@
         <v/>
       </c>
       <c r="C1349" t="str">
-        <v>עקב</v>
+        <v>בגלל</v>
       </c>
       <c r="D1349" t="str">
         <v/>
@@ -31480,7 +31480,7 @@
         <v>adj, n</v>
       </c>
       <c r="C1352" t="str">
-        <v>פטור ממכס.</v>
+        <v>פטור ממכס</v>
       </c>
       <c r="D1352" t="str">
         <v/>
@@ -31503,7 +31503,7 @@
         <v>adj</v>
       </c>
       <c r="C1353" t="str">
-        <v>חוףasia. kgm</v>
+        <v>מזרחי</v>
       </c>
       <c r="D1353" t="str">
         <v/>
@@ -31572,7 +31572,7 @@
         <v>adj</v>
       </c>
       <c r="C1356" t="str">
-        <v>אפקטיבי</v>
+        <v>יעיל</v>
       </c>
       <c r="D1356" t="str">
         <v>effectively</v>
@@ -31595,7 +31595,7 @@
         <v/>
       </c>
       <c r="C1357" t="str">
-        <v>או... או</v>
+        <v>או … או</v>
       </c>
       <c r="D1357" t="str">
         <v/>
@@ -31664,7 +31664,7 @@
         <v>adj</v>
       </c>
       <c r="C1360" t="str">
-        <v>בסיסי</v>
+        <v>יסודי</v>
       </c>
       <c r="D1360" t="str">
         <v/>
@@ -31687,7 +31687,7 @@
         <v>n</v>
       </c>
       <c r="C1361" t="str">
-        <v>שעת חרום</v>
+        <v>חרום</v>
       </c>
       <c r="D1361" t="str">
         <v/>
@@ -31779,7 +31779,7 @@
         <v>adj</v>
       </c>
       <c r="C1365" t="str">
-        <v>אינסופית</v>
+        <v>אין סוף</v>
       </c>
       <c r="D1365" t="str">
         <v/>
@@ -31848,7 +31848,7 @@
         <v>v</v>
       </c>
       <c r="C1368" t="str">
-        <v>וודא</v>
+        <v>להבטיח</v>
       </c>
       <c r="D1368" t="str">
         <v/>
@@ -31871,7 +31871,7 @@
         <v>v</v>
       </c>
       <c r="C1369" t="str">
-        <v>בידור</v>
+        <v>לבדר</v>
       </c>
       <c r="D1369" t="str">
         <v>entertainment</v>
@@ -31894,7 +31894,7 @@
         <v>adj</v>
       </c>
       <c r="C1370" t="str">
-        <v>הכול</v>
+        <v>שלם</v>
       </c>
       <c r="D1370" t="str">
         <v>entirely</v>
@@ -31917,7 +31917,7 @@
         <v/>
       </c>
       <c r="C1371" t="str">
-        <v>ידידותיים לסביבה</v>
+        <v>ידידותית לסביבה</v>
       </c>
       <c r="D1371" t="str">
         <v/>
@@ -31963,7 +31963,7 @@
         <v>v</v>
       </c>
       <c r="C1373" t="str">
-        <v>רווח</v>
+        <v>לברוח</v>
       </c>
       <c r="D1373" t="str">
         <v/>
@@ -32032,7 +32032,7 @@
         <v>v</v>
       </c>
       <c r="C1376" t="str">
-        <v>הערכת שווי</v>
+        <v>להעריך</v>
       </c>
       <c r="D1376" t="str">
         <v/>
@@ -32078,7 +32078,7 @@
         <v>adv</v>
       </c>
       <c r="C1378" t="str">
-        <v>זוגי (zoogi)</v>
+        <v>אפילו</v>
       </c>
       <c r="D1378" t="str">
         <v/>
@@ -32101,7 +32101,7 @@
         <v>adv</v>
       </c>
       <c r="C1379" t="str">
-        <v>בסופו של דבר.</v>
+        <v>בסופו של דבר</v>
       </c>
       <c r="D1379" t="str">
         <v/>
@@ -32124,7 +32124,7 @@
         <v/>
       </c>
       <c r="C1380" t="str">
-        <v>מאז?</v>
+        <v>מאז ומעולם</v>
       </c>
       <c r="D1380" t="str">
         <v/>
@@ -32147,7 +32147,7 @@
         <v/>
       </c>
       <c r="C1381" t="str">
-        <v>כל יום</v>
+        <v>כל יחיד</v>
       </c>
       <c r="D1381" t="str">
         <v/>
@@ -32170,7 +32170,7 @@
         <v>n</v>
       </c>
       <c r="C1382" t="str">
-        <v>ראייה:</v>
+        <v>עדות</v>
       </c>
       <c r="D1382" t="str">
         <v/>
@@ -32193,7 +32193,7 @@
         <v>v</v>
       </c>
       <c r="C1383" t="str">
-        <v>מבחן</v>
+        <v>לבחון</v>
       </c>
       <c r="D1383" t="str">
         <v/>
@@ -32216,7 +32216,7 @@
         <v>n</v>
       </c>
       <c r="C1384" t="str">
-        <v>נש'מ</v>
+        <v>להחליף</v>
       </c>
       <c r="D1384" t="str">
         <v/>
@@ -32262,7 +32262,7 @@
         <v>n</v>
       </c>
       <c r="C1386" t="str">
-        <v>סְלִיחָה</v>
+        <v>תירוץ</v>
       </c>
       <c r="D1386" t="str">
         <v/>
@@ -32308,7 +32308,7 @@
         <v>n</v>
       </c>
       <c r="C1388" t="str">
-        <v>ציפיות מהתוכנית</v>
+        <v>תוחלת</v>
       </c>
       <c r="D1388" t="str">
         <v/>
@@ -32354,7 +32354,7 @@
         <v>n, v</v>
       </c>
       <c r="C1390" t="str">
-        <v>ניסוי</v>
+        <v>לנסות</v>
       </c>
       <c r="D1390" t="str">
         <v/>
@@ -32377,7 +32377,7 @@
         <v>n</v>
       </c>
       <c r="C1391" t="str">
-        <v>מומחיות</v>
+        <v>מומחה</v>
       </c>
       <c r="D1391" t="str">
         <v/>
@@ -32400,7 +32400,7 @@
         <v>n</v>
       </c>
       <c r="C1392" t="str">
-        <v>ביטוי</v>
+        <v>הבעה</v>
       </c>
       <c r="D1392" t="str">
         <v/>
@@ -32423,7 +32423,7 @@
         <v>n</v>
       </c>
       <c r="C1393" t="str">
-        <v>במידה</v>
+        <v>היקף</v>
       </c>
       <c r="D1393" t="str">
         <v/>
@@ -32446,7 +32446,7 @@
         <v>adj</v>
       </c>
       <c r="C1394" t="str">
-        <v>ניסיוני</v>
+        <v>חיצוני</v>
       </c>
       <c r="D1394" t="str">
         <v/>
@@ -32469,7 +32469,7 @@
         <v>adv, n</v>
       </c>
       <c r="C1395" t="str">
-        <v>מיוחד</v>
+        <v>תוספת</v>
       </c>
       <c r="D1395" t="str">
         <v/>
@@ -32538,7 +32538,7 @@
         <v>n</v>
       </c>
       <c r="C1398" t="str">
-        <v>מסגרת</v>
+        <v>מתקן</v>
       </c>
       <c r="D1398" t="str">
         <v/>
@@ -32561,7 +32561,7 @@
         <v>n</v>
       </c>
       <c r="C1399" t="str">
-        <v>גן</v>
+        <v>גורם</v>
       </c>
       <c r="D1399" t="str">
         <v/>
@@ -32607,7 +32607,7 @@
         <v>n</v>
       </c>
       <c r="C1401" t="str">
-        <v>יריד</v>
+        <v>הוגן</v>
       </c>
       <c r="D1401" t="str">
         <v/>
@@ -32653,7 +32653,7 @@
         <v>n</v>
       </c>
       <c r="C1403" t="str">
-        <v>ליפול</v>
+        <v>נפילה</v>
       </c>
       <c r="D1403" t="str">
         <v/>
@@ -32676,7 +32676,7 @@
         <v>v</v>
       </c>
       <c r="C1404" t="str">
-        <v>ליפול</v>
+        <v>נפילה</v>
       </c>
       <c r="D1404" t="str">
         <v/>
@@ -32745,7 +32745,7 @@
         <v>n</v>
       </c>
       <c r="C1407" t="str">
-        <v>&amp; מועדף</v>
+        <v>טובה</v>
       </c>
       <c r="D1407" t="str">
         <v/>
@@ -32768,7 +32768,7 @@
         <v>n</v>
       </c>
       <c r="C1408" t="str">
-        <v>עמל.</v>
+        <v>תשלום</v>
       </c>
       <c r="D1408" t="str">
         <v/>
@@ -32837,7 +32837,7 @@
         <v/>
       </c>
       <c r="C1411" t="str">
-        <v>להרגיש רע עם משהו/לעשות משהו</v>
+        <v>מרגיש רע לגבי sth / עושה sth</v>
       </c>
       <c r="D1411" t="str">
         <v/>
@@ -32860,7 +32860,7 @@
         <v/>
       </c>
       <c r="C1412" t="str">
-        <v>מרגיש כמו משהו/לעשות משהו</v>
+        <v>מתחשק/לעשות משהו</v>
       </c>
       <c r="D1412" t="str">
         <v/>
@@ -32883,7 +32883,7 @@
         <v/>
       </c>
       <c r="C1413" t="str">
-        <v>מרגיש כאילו / כאילו</v>
+        <v>מרגיש כמו/כאילו</v>
       </c>
       <c r="D1413" t="str">
         <v/>
@@ -32929,7 +32929,7 @@
         <v>adj, n</v>
       </c>
       <c r="C1415" t="str">
-        <v>אישה</v>
+        <v>נקבה</v>
       </c>
       <c r="D1415" t="str">
         <v/>
@@ -33021,7 +33021,7 @@
         <v>n</v>
       </c>
       <c r="C1419" t="str">
-        <v>סיפורת</v>
+        <v>פיקציה</v>
       </c>
       <c r="D1419" t="str">
         <v/>
@@ -33044,7 +33044,7 @@
         <v>v, n</v>
       </c>
       <c r="C1420" t="str">
-        <v>להלחם!</v>
+        <v>להילחם</v>
       </c>
       <c r="D1420" t="str">
         <v>fighting</v>
@@ -33090,7 +33090,7 @@
         <v>n</v>
       </c>
       <c r="C1422" t="str">
-        <v>תמונה</v>
+        <v>קובץ</v>
       </c>
       <c r="D1422" t="str">
         <v/>
@@ -33113,7 +33113,7 @@
         <v>adv</v>
       </c>
       <c r="C1423" t="str">
-        <v>סוף סוף</v>
+        <v>לבסוף</v>
       </c>
       <c r="D1423" t="str">
         <v/>
@@ -33136,7 +33136,7 @@
         <v/>
       </c>
       <c r="C1424" t="str">
-        <v>למצוא שיחה/משהו קל/משעמם/מצחיק וכו'</v>
+        <v>למצוא sb/sth קל/משעמם/ מצחיק וכו'</v>
       </c>
       <c r="D1424" t="str">
         <v/>
@@ -33159,7 +33159,7 @@
         <v>n</v>
       </c>
       <c r="C1425" t="str">
-        <v>לגמור</v>
+        <v>סיום</v>
       </c>
       <c r="D1425" t="str">
         <v/>
@@ -33228,7 +33228,7 @@
         <v>n</v>
       </c>
       <c r="C1428" t="str">
-        <v>מכבי אש</v>
+        <v>כבאי</v>
       </c>
       <c r="D1428" t="str">
         <v/>
@@ -33251,7 +33251,7 @@
         <v>n</v>
       </c>
       <c r="C1429" t="str">
-        <v>תיבל (tee-BEL)</v>
+        <v>טעם</v>
       </c>
       <c r="D1429" t="str">
         <v/>
@@ -33274,7 +33274,7 @@
         <v>v, n</v>
       </c>
       <c r="C1430" t="str">
-        <v>לזרום</v>
+        <v>זרימה</v>
       </c>
       <c r="D1430" t="str">
         <v/>
@@ -33297,7 +33297,7 @@
         <v>n</v>
       </c>
       <c r="C1431" t="str">
-        <v>אוהד</v>
+        <v>חסיד</v>
       </c>
       <c r="D1431" t="str">
         <v/>
@@ -33343,7 +33343,7 @@
         <v>prep</v>
       </c>
       <c r="C1433" t="str">
-        <v>ל</v>
+        <v>עבור</v>
       </c>
       <c r="D1433" t="str">
         <v/>
@@ -33389,7 +33389,7 @@
         <v/>
       </c>
       <c r="C1435" t="str">
-        <v>לדוגמא,</v>
+        <v>למשל</v>
       </c>
       <c r="D1435" t="str">
         <v/>
@@ -33412,7 +33412,7 @@
         <v/>
       </c>
       <c r="C1436" t="str">
-        <v>ברור.</v>
+        <v>על בטוח</v>
       </c>
       <c r="D1436" t="str">
         <v/>
@@ -33458,7 +33458,7 @@
         <v>n</v>
       </c>
       <c r="C1438" t="str">
-        <v>כפה</v>
+        <v>כוח</v>
       </c>
       <c r="D1438" t="str">
         <v/>
@@ -33481,7 +33481,7 @@
         <v>adj</v>
       </c>
       <c r="C1439" t="str">
-        <v>חוץ</v>
+        <v>זר</v>
       </c>
       <c r="D1439" t="str">
         <v>foreigner</v>
@@ -33527,7 +33527,7 @@
         <v>v</v>
       </c>
       <c r="C1441" t="str">
-        <v>נבחרים</v>
+        <v>לסלוח</v>
       </c>
       <c r="D1441" t="str">
         <v/>
@@ -33619,7 +33619,7 @@
         <v>v</v>
       </c>
       <c r="C1445" t="str">
-        <v>הקפאDock this window</v>
+        <v>להקפיא</v>
       </c>
       <c r="D1445" t="str">
         <v/>
@@ -33642,7 +33642,7 @@
         <v>adv</v>
       </c>
       <c r="C1446" t="str">
-        <v>תכופות</v>
+        <v>לעתים קרובות</v>
       </c>
       <c r="D1446" t="str">
         <v/>
@@ -33665,7 +33665,7 @@
         <v>prep</v>
       </c>
       <c r="C1447" t="str">
-        <v>מאת</v>
+        <v>מ</v>
       </c>
       <c r="D1447" t="str">
         <v/>
@@ -33688,7 +33688,7 @@
         <v>v</v>
       </c>
       <c r="C1448" t="str">
-        <v>ילדות</v>
+        <v>לטגן</v>
       </c>
       <c r="D1448" t="str">
         <v>fried</v>
@@ -33734,7 +33734,7 @@
         <v/>
       </c>
       <c r="C1450" t="str">
-        <v>לימודים מלאים</v>
+        <v>במשרה מלאה</v>
       </c>
       <c r="D1450" t="str">
         <v/>
@@ -33780,7 +33780,7 @@
         <v>n</v>
       </c>
       <c r="C1452" t="str">
-        <v>עתיד</v>
+        <v>עתידי</v>
       </c>
       <c r="D1452" t="str">
         <v/>
@@ -33803,7 +33803,7 @@
         <v>adj</v>
       </c>
       <c r="C1453" t="str">
-        <v>עתיד</v>
+        <v>עתידי</v>
       </c>
       <c r="D1453" t="str">
         <v/>
@@ -33895,7 +33895,7 @@
         <v>adj</v>
       </c>
       <c r="C1457" t="str">
-        <v>גיי</v>
+        <v>הומו</v>
       </c>
       <c r="D1457" t="str">
         <v/>
@@ -33964,7 +33964,7 @@
         <v/>
       </c>
       <c r="C1460" t="str">
-        <v>להסתובב (באיזשהו מקום)</v>
+        <v>להסתובב</v>
       </c>
       <c r="D1460" t="str">
         <v/>
@@ -33987,7 +33987,7 @@
         <v/>
       </c>
       <c r="C1461" t="str">
-        <v>להיפטר מ- sth</v>
+        <v>להיפטר מס'</v>
       </c>
       <c r="D1461" t="str">
         <v/>
@@ -34010,7 +34010,7 @@
         <v/>
       </c>
       <c r="C1462" t="str">
-        <v>להכיר מישהו/מישהו</v>
+        <v>להכיר את sb/sth</v>
       </c>
       <c r="D1462" t="str">
         <v/>
@@ -34033,7 +34033,7 @@
         <v/>
       </c>
       <c r="C1463" t="str">
-        <v>להתרגל למשהו/לעשות משהו</v>
+        <v>להתרגל/להתרגל ל-sb/sth/לעשות sth</v>
       </c>
       <c r="D1463" t="str">
         <v/>
@@ -34056,7 +34056,7 @@
         <v/>
       </c>
       <c r="C1464" t="str">
-        <v>לך לישון.</v>
+        <v>להגיע/ללכת לישון</v>
       </c>
       <c r="D1464" t="str">
         <v/>
@@ -34102,7 +34102,7 @@
         <v/>
       </c>
       <c r="C1466" t="str">
-        <v>להתקשר/להתקשר לאדם</v>
+        <v>תתקשר/צלצל ל-sb</v>
       </c>
       <c r="D1466" t="str">
         <v/>
@@ -34171,7 +34171,7 @@
         <v/>
       </c>
       <c r="C1469" t="str">
-        <v>רד למטה.</v>
+        <v>לרדת</v>
       </c>
       <c r="D1469" t="str">
         <v/>
@@ -34194,7 +34194,7 @@
         <v/>
       </c>
       <c r="C1470" t="str">
-        <v>הלך'הָלַךְ</v>
+        <v>להמשיך הלאה</v>
       </c>
       <c r="D1470" t="str">
         <v/>
@@ -34240,7 +34240,7 @@
         <v/>
       </c>
       <c r="C1472" t="str">
-        <v>למעלה</v>
+        <v>לעלות</v>
       </c>
       <c r="D1472" t="str">
         <v/>
@@ -34286,7 +34286,7 @@
         <v>n</v>
       </c>
       <c r="C1474" t="str">
-        <v>יעד</v>
+        <v>מטרה</v>
       </c>
       <c r="D1474" t="str">
         <v/>
@@ -34378,7 +34378,7 @@
         <v>v, n</v>
       </c>
       <c r="C1478" t="str">
-        <v>מעניקים</v>
+        <v>מענק</v>
       </c>
       <c r="D1478" t="str">
         <v/>
@@ -34447,7 +34447,7 @@
         <v>n</v>
       </c>
       <c r="C1481" t="str">
-        <v>שטחים</v>
+        <v>עילה</v>
       </c>
       <c r="D1481" t="str">
         <v>playground</v>
@@ -34470,7 +34470,7 @@
         <v>v</v>
       </c>
       <c r="C1482" t="str">
-        <v>כחול</v>
+        <v>לגדול</v>
       </c>
       <c r="D1482" t="str">
         <v>growing growth</v>
@@ -34493,7 +34493,7 @@
         <v>n</v>
       </c>
       <c r="C1483" t="str">
-        <v>ניחוש</v>
+        <v>לנחש</v>
       </c>
       <c r="D1483" t="str">
         <v/>
@@ -34516,7 +34516,7 @@
         <v>adj</v>
       </c>
       <c r="C1484" t="str">
-        <v>אשמה</v>
+        <v>אשם</v>
       </c>
       <c r="D1484" t="str">
         <v/>
@@ -34539,7 +34539,7 @@
         <v>n</v>
       </c>
       <c r="C1485" t="str">
-        <v>תסרוקת</v>
+        <v>תספורת</v>
       </c>
       <c r="D1485" t="str">
         <v/>
@@ -34562,7 +34562,7 @@
         <v/>
       </c>
       <c r="C1486" t="str">
-        <v>למסור משהו או למסור משהו</v>
+        <v>יד ב sth או יד sth פנימה</v>
       </c>
       <c r="D1486" t="str">
         <v/>
@@ -34585,7 +34585,7 @@
         <v>v</v>
       </c>
       <c r="C1487" t="str">
-        <v>נקודת אחיזה</v>
+        <v>ידית</v>
       </c>
       <c r="D1487" t="str">
         <v/>
@@ -34631,7 +34631,7 @@
         <v/>
       </c>
       <c r="C1489" t="str">
-        <v>ניתוק</v>
+        <v>לתלות</v>
       </c>
       <c r="D1489" t="str">
         <v/>
@@ -34654,7 +34654,7 @@
         <v>n</v>
       </c>
       <c r="C1490" t="str">
-        <v>מרוב אושר.</v>
+        <v>שמחה</v>
       </c>
       <c r="D1490" t="str">
         <v/>
@@ -34677,7 +34677,7 @@
         <v/>
       </c>
       <c r="C1491" t="str">
-        <v>יש לי משהו או יש לי משהו</v>
+        <v>יש על sth או יש sth על</v>
       </c>
       <c r="D1491" t="str">
         <v/>
@@ -34700,7 +34700,7 @@
         <v/>
       </c>
       <c r="C1492" t="str">
-        <v>נו דאוט</v>
+        <v>אין ספק</v>
       </c>
       <c r="D1492" t="str">
         <v/>
@@ -34723,7 +34723,7 @@
         <v/>
       </c>
       <c r="C1493" t="str">
-        <v>אין לי מושג</v>
+        <v>אין לך מושג</v>
       </c>
       <c r="D1493" t="str">
         <v/>
@@ -34746,7 +34746,7 @@
         <v/>
       </c>
       <c r="C1494" t="str">
-        <v>יש משהו במשותף</v>
+        <v>יש דבר משותף</v>
       </c>
       <c r="D1494" t="str">
         <v/>
@@ -34815,7 +34815,7 @@
         <v/>
       </c>
       <c r="C1497" t="str">
-        <v>לעזור לעצמך (למשהו)</v>
+        <v>עזור לעצמך</v>
       </c>
       <c r="D1497" t="str">
         <v/>
@@ -34861,7 +34861,7 @@
         <v>adj</v>
       </c>
       <c r="C1499" t="str">
-        <v>היי-טק/הייטק</v>
+        <v>הייטק/היי-טק</v>
       </c>
       <c r="D1499" t="str">
         <v/>
@@ -34953,7 +34953,7 @@
         <v>n</v>
       </c>
       <c r="C1503" t="str">
-        <v>להכות</v>
+        <v>להיט</v>
       </c>
       <c r="D1503" t="str">
         <v/>
@@ -34976,7 +34976,7 @@
         <v/>
       </c>
       <c r="C1504" t="str">
-        <v>לעצור את נשימתך</v>
+        <v>לעצור את הנשימה</v>
       </c>
       <c r="D1504" t="str">
         <v/>
@@ -35068,7 +35068,7 @@
         <v/>
       </c>
       <c r="C1508" t="str">
-        <v>מקווה לעשות משהו</v>
+        <v>מקווה לעשות דבר</v>
       </c>
       <c r="D1508" t="str">
         <v/>
@@ -35137,7 +35137,7 @@
         <v>n</v>
       </c>
       <c r="C1511" t="str">
-        <v>עבודות בית</v>
+        <v>עבודת בית</v>
       </c>
       <c r="D1511" t="str">
         <v/>
@@ -35160,7 +35160,7 @@
         <v>n</v>
       </c>
       <c r="C1512" t="str">
-        <v>האדם הנבון</v>
+        <v>אנושי</v>
       </c>
       <c r="D1512" t="str">
         <v>human being</v>
@@ -35206,7 +35206,7 @@
         <v>v</v>
       </c>
       <c r="C1514" t="str">
-        <v>פְּגִיעָה</v>
+        <v>כאב</v>
       </c>
       <c r="D1514" t="str">
         <v/>
@@ -35229,7 +35229,7 @@
         <v/>
       </c>
       <c r="C1515" t="str">
-        <v>אני מתערב איתך...</v>
+        <v>אני מתערב</v>
       </c>
       <c r="D1515" t="str">
         <v/>
@@ -35252,7 +35252,7 @@
         <v/>
       </c>
       <c r="C1516" t="str">
-        <v>אני מניחה.</v>
+        <v>אני מניח</v>
       </c>
       <c r="D1516" t="str">
         <v/>
@@ -35275,7 +35275,7 @@
         <v/>
       </c>
       <c r="C1517" t="str">
-        <v>אני מניחה שכן.</v>
+        <v>אני מניח</v>
       </c>
       <c r="D1517" t="str">
         <v/>
@@ -35321,7 +35321,7 @@
         <v>n</v>
       </c>
       <c r="C1519" t="str">
-        <v>תעודת זהות</v>
+        <v>זהות</v>
       </c>
       <c r="D1519" t="str">
         <v/>
@@ -35344,7 +35344,7 @@
         <v>conj</v>
       </c>
       <c r="C1520" t="str">
-        <v>סכומי</v>
+        <v>אם</v>
       </c>
       <c r="D1520" t="str">
         <v/>
@@ -35459,7 +35459,7 @@
         <v>n</v>
       </c>
       <c r="C1525" t="str">
-        <v>מפותח.</v>
+        <v>דמיון</v>
       </c>
       <c r="D1525" t="str">
         <v/>
@@ -35482,7 +35482,7 @@
         <v/>
       </c>
       <c r="C1526" t="str">
-        <v>בצורה מסוימת או בדרכים מסוימות / רבות</v>
+        <v>בצורה מסוימת או במובנים מסוימים / רבים</v>
       </c>
       <c r="D1526" t="str">
         <v/>
@@ -35528,7 +35528,7 @@
         <v/>
       </c>
       <c r="C1528" t="str">
-        <v>במשותף / יש משהו במשותף</v>
+        <v>משותף/יש דבר משותף</v>
       </c>
       <c r="D1528" t="str">
         <v/>
@@ -35551,7 +35551,7 @@
         <v/>
       </c>
       <c r="C1529" t="str">
-        <v>בהרחבה</v>
+        <v>בפירוט</v>
       </c>
       <c r="D1529" t="str">
         <v/>
@@ -35574,7 +35574,7 @@
         <v/>
       </c>
       <c r="C1530" t="str">
-        <v>למעשה/למעשה</v>
+        <v>למעשה/בפועל</v>
       </c>
       <c r="D1530" t="str">
         <v/>
@@ -35597,7 +35597,7 @@
         <v/>
       </c>
       <c r="C1531" t="str">
-        <v>באופן כללי ?</v>
+        <v>בכלל</v>
       </c>
       <c r="D1531" t="str">
         <v/>
@@ -35620,7 +35620,7 @@
         <v/>
       </c>
       <c r="C1532" t="str">
-        <v>כדי (שאדם/כל דבר) לעשות משהו</v>
+        <v>על מנת לעשות sth</v>
       </c>
       <c r="D1532" t="str">
         <v/>
@@ -35666,7 +35666,7 @@
         <v/>
       </c>
       <c r="C1534" t="str">
-        <v>בפרט.</v>
+        <v>בפרט</v>
       </c>
       <c r="D1534" t="str">
         <v/>
@@ -35689,7 +35689,7 @@
         <v/>
       </c>
       <c r="C1535" t="str">
-        <v>למרות כל דבר</v>
+        <v>למרות sth</v>
       </c>
       <c r="D1535" t="str">
         <v/>
@@ -35758,7 +35758,7 @@
         <v>adv</v>
       </c>
       <c r="C1538" t="str">
-        <v>אמנם,</v>
+        <v>אכן</v>
       </c>
       <c r="D1538" t="str">
         <v/>
@@ -35781,7 +35781,7 @@
         <v>n</v>
       </c>
       <c r="C1539" t="str">
-        <v>עצמאות:</v>
+        <v>עצמאות</v>
       </c>
       <c r="D1539" t="str">
         <v>independent</v>
@@ -35804,7 +35804,7 @@
         <v>adj</v>
       </c>
       <c r="C1540" t="str">
-        <v>עמית יחיד</v>
+        <v>אישי</v>
       </c>
       <c r="D1540" t="str">
         <v/>
@@ -35827,7 +35827,7 @@
         <v>v, n</v>
       </c>
       <c r="C1541" t="str">
-        <v>השפעה</v>
+        <v>להשפיע</v>
       </c>
       <c r="D1541" t="str">
         <v/>
@@ -35850,7 +35850,7 @@
         <v>v</v>
       </c>
       <c r="C1542" t="str">
-        <v>טראומה גופנית</v>
+        <v>לפגוע</v>
       </c>
       <c r="D1542" t="str">
         <v>injury</v>
@@ -35919,7 +35919,7 @@
         <v>n</v>
       </c>
       <c r="C1545" t="str">
-        <v>כמוסד.</v>
+        <v>מוסד</v>
       </c>
       <c r="D1545" t="str">
         <v>institute</v>
@@ -35965,7 +35965,7 @@
         <v>adj</v>
       </c>
       <c r="C1547" t="str">
-        <v>מעוניינים</v>
+        <v>מתעניינים</v>
       </c>
       <c r="D1547" t="str">
         <v/>
@@ -36126,7 +36126,7 @@
         <v/>
       </c>
       <c r="C1554" t="str">
-        <v>נראה...</v>
+        <v>נראה…</v>
       </c>
       <c r="D1554" t="str">
         <v/>
@@ -36149,7 +36149,7 @@
         <v>n</v>
       </c>
       <c r="C1555" t="str">
-        <v>צנצנת</v>
+        <v>קנקן</v>
       </c>
       <c r="D1555" t="str">
         <v/>
@@ -36195,7 +36195,7 @@
         <v>v</v>
       </c>
       <c r="C1557" t="str">
-        <v>הרשמה</v>
+        <v>להצטרף</v>
       </c>
       <c r="D1557" t="str">
         <v/>
@@ -36218,7 +36218,7 @@
         <v>v</v>
       </c>
       <c r="C1558" t="str">
-        <v>שופט</v>
+        <v>לשפוט</v>
       </c>
       <c r="D1558" t="str">
         <v>judgement</v>
@@ -36264,7 +36264,7 @@
         <v/>
       </c>
       <c r="C1560" t="str">
-        <v>לכל מקרה שלא יקרה.</v>
+        <v>למקרה</v>
       </c>
       <c r="D1560" t="str">
         <v/>
@@ -36287,7 +36287,7 @@
         <v/>
       </c>
       <c r="C1561" t="str">
-        <v>לשמור על סוד</v>
+        <v>לשמור סוד</v>
       </c>
       <c r="D1561" t="str">
         <v/>
@@ -36310,7 +36310,7 @@
         <v/>
       </c>
       <c r="C1562" t="str">
-        <v>שמרו על קשר</v>
+        <v>לשמור על קשר</v>
       </c>
       <c r="D1562" t="str">
         <v/>
@@ -36379,7 +36379,7 @@
         <v>adj</v>
       </c>
       <c r="C1565" t="str">
-        <v>אדיב</v>
+        <v>סוג</v>
       </c>
       <c r="D1565" t="str">
         <v/>
@@ -36402,7 +36402,7 @@
         <v>v, n</v>
       </c>
       <c r="C1566" t="str">
-        <v>לדפוק</v>
+        <v>נקישה</v>
       </c>
       <c r="D1566" t="str">
         <v/>
@@ -36425,7 +36425,7 @@
         <v>n</v>
       </c>
       <c r="C1567" t="str">
-        <v>הקוראן</v>
+        <v>קוראן</v>
       </c>
       <c r="D1567" t="str">
         <v/>
@@ -36494,7 +36494,7 @@
         <v>n</v>
       </c>
       <c r="C1570" t="str">
-        <v>צירי לידה</v>
+        <v>עבודה</v>
       </c>
       <c r="D1570" t="str">
         <v/>
@@ -36540,7 +36540,7 @@
         <v>n</v>
       </c>
       <c r="C1572" t="str">
-        <v>ליידי</v>
+        <v>גברת</v>
       </c>
       <c r="D1572" t="str">
         <v/>
@@ -36655,7 +36655,7 @@
         <v>n</v>
       </c>
       <c r="C1577" t="str">
-        <v>דין</v>
+        <v>משפטים</v>
       </c>
       <c r="D1577" t="str">
         <v/>
@@ -36678,7 +36678,7 @@
         <v/>
       </c>
       <c r="C1578" t="str">
-        <v>להניח משהו בתוך/על וכו'</v>
+        <v>להשכיב את זה/עליו וכו'</v>
       </c>
       <c r="D1578" t="str">
         <v/>
@@ -36701,7 +36701,7 @@
         <v/>
       </c>
       <c r="C1579" t="str">
-        <v>ערוך את השולחן</v>
+        <v>להניח את השולחן</v>
       </c>
       <c r="D1579" t="str">
         <v/>
@@ -36724,7 +36724,7 @@
         <v>v</v>
       </c>
       <c r="C1580" t="str">
-        <v>עופרת</v>
+        <v>להוביל</v>
       </c>
       <c r="D1580" t="str">
         <v/>
@@ -36770,7 +36770,7 @@
         <v/>
       </c>
       <c r="C1582" t="str">
-        <v>להישען (כלומר) על משהו</v>
+        <v>להישען נגד/על sth</v>
       </c>
       <c r="D1582" t="str">
         <v/>
@@ -36816,7 +36816,7 @@
         <v>adj</v>
       </c>
       <c r="C1584" t="str">
-        <v>חוקי/משפטי</v>
+        <v>משפטי</v>
       </c>
       <c r="D1584" t="str">
         <v/>
@@ -36885,7 +36885,7 @@
         <v/>
       </c>
       <c r="C1587" t="str">
-        <v>תנו לי/לנו</v>
+        <v>תן לי/לנו</v>
       </c>
       <c r="D1587" t="str">
         <v/>
@@ -36908,7 +36908,7 @@
         <v>v</v>
       </c>
       <c r="C1588" t="str">
-        <v>לשכב (Lish'kav)</v>
+        <v>לשקר</v>
       </c>
       <c r="D1588" t="str">
         <v/>
@@ -36954,7 +36954,7 @@
         <v>n</v>
       </c>
       <c r="C1590" t="str">
-        <v>להרים</v>
+        <v>מעלית</v>
       </c>
       <c r="D1590" t="str">
         <v/>
@@ -36977,7 +36977,7 @@
         <v/>
       </c>
       <c r="C1591" t="str">
-        <v>אהבות ודחות</v>
+        <v>אוהב ולא אוהב</v>
       </c>
       <c r="D1591" t="str">
         <v/>
@@ -37000,7 +37000,7 @@
         <v>v, n</v>
       </c>
       <c r="C1592" t="str">
-        <v>קישור</v>
+        <v>לקשר</v>
       </c>
       <c r="D1592" t="str">
         <v/>
@@ -37069,7 +37069,7 @@
         <v>adj</v>
       </c>
       <c r="C1595" t="str">
-        <v>מפורסמים</v>
+        <v>בשידור חי</v>
       </c>
       <c r="D1595" t="str">
         <v/>
@@ -37092,7 +37092,7 @@
         <v/>
       </c>
       <c r="C1596" t="str">
-        <v>המון / המון</v>
+        <v>המון/עומס של</v>
       </c>
       <c r="D1596" t="str">
         <v/>
@@ -37184,7 +37184,7 @@
         <v>adj</v>
       </c>
       <c r="C1600" t="str">
-        <v>רס"ן</v>
+        <v>עיקרי</v>
       </c>
       <c r="D1600" t="str">
         <v/>
@@ -37253,7 +37253,7 @@
         <v/>
       </c>
       <c r="C1603" t="str">
-        <v>להתיידד (עם sb)</v>
+        <v>להתיידד</v>
       </c>
       <c r="D1603" t="str">
         <v/>
@@ -37276,7 +37276,7 @@
         <v/>
       </c>
       <c r="C1604" t="str">
-        <v>לגרום לאדם לעשות משהו</v>
+        <v>לעשות sb לעשות sth</v>
       </c>
       <c r="D1604" t="str">
         <v/>
@@ -37322,7 +37322,7 @@
         <v>adj, n</v>
       </c>
       <c r="C1606" t="str">
-        <v>גבר</v>
+        <v>זכר</v>
       </c>
       <c r="D1606" t="str">
         <v/>
@@ -37414,7 +37414,7 @@
         <v>n</v>
       </c>
       <c r="C1610" t="str">
-        <v>ראשי</v>
+        <v>לשלוט</v>
       </c>
       <c r="D1610" t="str">
         <v/>
@@ -37437,7 +37437,7 @@
         <v>n</v>
       </c>
       <c r="C1611" t="str">
-        <v>התאמה</v>
+        <v>משחק</v>
       </c>
       <c r="D1611" t="str">
         <v/>
@@ -37460,7 +37460,7 @@
         <v>n</v>
       </c>
       <c r="C1612" t="str">
-        <v>טקסטיל</v>
+        <v>חומר</v>
       </c>
       <c r="D1612" t="str">
         <v/>
@@ -37483,7 +37483,7 @@
         <v>n</v>
       </c>
       <c r="C1613" t="str">
-        <v>מתמטיקה</v>
+        <v>מתימטיקה</v>
       </c>
       <c r="D1613" t="str">
         <v>math</v>
@@ -37506,7 +37506,7 @@
         <v>v</v>
       </c>
       <c r="C1614" t="str">
-        <v>חומר</v>
+        <v>משנה</v>
       </c>
       <c r="D1614" t="str">
         <v/>
@@ -37529,7 +37529,7 @@
         <v>adj</v>
       </c>
       <c r="C1615" t="str">
-        <v>מרושע</v>
+        <v>מתכוון</v>
       </c>
       <c r="D1615" t="str">
         <v/>
@@ -37552,7 +37552,7 @@
         <v>v</v>
       </c>
       <c r="C1616" t="str">
-        <v>מרושע</v>
+        <v>מתכוון</v>
       </c>
       <c r="D1616" t="str">
         <v/>
@@ -37667,7 +37667,7 @@
         <v>v</v>
       </c>
       <c r="C1621" t="str">
-        <v>עוצמה</v>
+        <v>יכול</v>
       </c>
       <c r="D1621" t="str">
         <v/>
@@ -37713,7 +37713,7 @@
         <v>v</v>
       </c>
       <c r="C1623" t="str">
-        <v>רוח (f)</v>
+        <v>ראש</v>
       </c>
       <c r="D1623" t="str">
         <v/>
@@ -37736,7 +37736,7 @@
         <v>v</v>
       </c>
       <c r="C1624" t="str">
-        <v>רוח (f)</v>
+        <v>ראש</v>
       </c>
       <c r="D1624" t="str">
         <v/>
@@ -37782,7 +37782,7 @@
         <v>adj, n</v>
       </c>
       <c r="C1626" t="str">
-        <v>ילדות</v>
+        <v>קטין</v>
       </c>
       <c r="D1626" t="str">
         <v/>
@@ -37805,7 +37805,7 @@
         <v>v</v>
       </c>
       <c r="C1627" t="str">
-        <v>בת</v>
+        <v>מתגעגע</v>
       </c>
       <c r="D1627" t="str">
         <v/>
@@ -37828,7 +37828,7 @@
         <v/>
       </c>
       <c r="C1628" t="str">
-        <v>החמצת הזדמנות / הזדמנות</v>
+        <v>להחמיץ הזדמנות/הזדמנות</v>
       </c>
       <c r="D1628" t="str">
         <v/>
@@ -37851,7 +37851,7 @@
         <v>adj</v>
       </c>
       <c r="C1629" t="str">
-        <v>חוסרים</v>
+        <v>חסר</v>
       </c>
       <c r="D1629" t="str">
         <v/>
@@ -37874,7 +37874,7 @@
         <v>n</v>
       </c>
       <c r="C1630" t="str">
-        <v>לערבב</v>
+        <v>שילוב</v>
       </c>
       <c r="D1630" t="str">
         <v/>
@@ -37943,7 +37943,7 @@
         <v>n</v>
       </c>
       <c r="C1633" t="str">
-        <v>בירושלים.</v>
+        <v>מנוע</v>
       </c>
       <c r="D1633" t="str">
         <v/>
@@ -37989,7 +37989,7 @@
         <v>adv, prep</v>
       </c>
       <c r="C1635" t="str">
-        <v>באיזור</v>
+        <v>קרוב</v>
       </c>
       <c r="D1635" t="str">
         <v/>
@@ -38035,7 +38035,7 @@
         <v>n</v>
       </c>
       <c r="C1637" t="str">
-        <v>איזור שני</v>
+        <v>שכונה</v>
       </c>
       <c r="D1637" t="str">
         <v/>
@@ -38058,7 +38058,7 @@
         <v>n</v>
       </c>
       <c r="C1638" t="str">
-        <v>קורדינטות</v>
+        <v>רשת</v>
       </c>
       <c r="D1638" t="str">
         <v/>
@@ -38081,7 +38081,7 @@
         <v>adv</v>
       </c>
       <c r="C1639" t="str">
-        <v>הבאה</v>
+        <v>הבא</v>
       </c>
       <c r="D1639" t="str">
         <v/>
@@ -38104,7 +38104,7 @@
         <v/>
       </c>
       <c r="C1640" t="str">
-        <v>לא עוד.</v>
+        <v>כבר לא</v>
       </c>
       <c r="D1640" t="str">
         <v/>
@@ -38127,7 +38127,7 @@
         <v/>
       </c>
       <c r="C1641" t="str">
-        <v>אין מצב.</v>
+        <v>אין מצב</v>
       </c>
       <c r="D1641" t="str">
         <v/>
@@ -38150,7 +38150,7 @@
         <v>conj</v>
       </c>
       <c r="C1642" t="str">
-        <v>סטנסיליםStencils</v>
+        <v>גם לא</v>
       </c>
       <c r="D1642" t="str">
         <v/>
@@ -38173,7 +38173,7 @@
         <v>adj</v>
       </c>
       <c r="C1643" t="str">
-        <v>קוריאה הצפוניתafrica. kgm</v>
+        <v>צפוני</v>
       </c>
       <c r="D1643" t="str">
         <v/>
@@ -38219,7 +38219,7 @@
         <v/>
       </c>
       <c r="C1645" t="str">
-        <v>לא ממש</v>
+        <v>לא באמת</v>
       </c>
       <c r="D1645" t="str">
         <v/>
@@ -38288,7 +38288,7 @@
         <v>adv</v>
       </c>
       <c r="C1648" t="str">
-        <v>הווה</v>
+        <v>כיום</v>
       </c>
       <c r="D1648" t="str">
         <v/>
@@ -38311,7 +38311,7 @@
         <v>adv</v>
       </c>
       <c r="C1649" t="str">
-        <v>בשום מקום</v>
+        <v>לשום מקום</v>
       </c>
       <c r="D1649" t="str">
         <v/>
@@ -38357,7 +38357,7 @@
         <v>v</v>
       </c>
       <c r="C1651" t="str">
-        <v>נשמע ל-/שמע ל-</v>
+        <v>לציית</v>
       </c>
       <c r="D1651" t="str">
         <v/>
@@ -38403,7 +38403,7 @@
         <v>v</v>
       </c>
       <c r="C1653" t="str">
-        <v>הלך'הָלַךְ</v>
+        <v>להתרחש</v>
       </c>
       <c r="D1653" t="str">
         <v/>
@@ -38426,7 +38426,7 @@
         <v>n</v>
       </c>
       <c r="C1654" t="str">
-        <v>אוקיינוס</v>
+        <v>ים</v>
       </c>
       <c r="D1654" t="str">
         <v/>
@@ -38449,7 +38449,7 @@
         <v>adj</v>
       </c>
       <c r="C1655" t="str">
-        <v>מְשׁוּנֶה</v>
+        <v>מוזר</v>
       </c>
       <c r="D1655" t="str">
         <v/>
@@ -38472,7 +38472,7 @@
         <v>prep</v>
       </c>
       <c r="C1656" t="str">
-        <v>מתוך</v>
+        <v>של</v>
       </c>
       <c r="D1656" t="str">
         <v/>
@@ -38495,7 +38495,7 @@
         <v>n</v>
       </c>
       <c r="C1657" t="str">
-        <v>שוטר</v>
+        <v>קצין</v>
       </c>
       <c r="D1657" t="str">
         <v/>
@@ -38564,7 +38564,7 @@
         <v/>
       </c>
       <c r="C1660" t="str">
-        <v>בדרך אל/ממנה</v>
+        <v>בדרך מ/אל</v>
       </c>
       <c r="D1660" t="str">
         <v/>
@@ -38587,7 +38587,7 @@
         <v/>
       </c>
       <c r="C1661" t="str">
-        <v>שוב פעם / עוד פעם אחת</v>
+        <v>פעם נוספת/עוד פעם</v>
       </c>
       <c r="D1661" t="str">
         <v/>
@@ -38610,7 +38610,7 @@
         <v>det</v>
       </c>
       <c r="C1662" t="str">
-        <v>אחד</v>
+        <v>אחת</v>
       </c>
       <c r="D1662" t="str">
         <v/>
@@ -38633,7 +38633,7 @@
         <v>det</v>
       </c>
       <c r="C1663" t="str">
-        <v>אחד</v>
+        <v>אחת</v>
       </c>
       <c r="D1663" t="str">
         <v/>
@@ -38656,7 +38656,7 @@
         <v/>
       </c>
       <c r="C1664" t="str">
-        <v>יום אחד / מתישהו / באחד הימים האלה</v>
+        <v>יום אחד / יום אחד / אחד מהימים האלה</v>
       </c>
       <c r="D1664" t="str">
         <v/>
@@ -38679,7 +38679,7 @@
         <v/>
       </c>
       <c r="C1665" t="str">
-        <v>על/על אל</v>
+        <v>על / על</v>
       </c>
       <c r="D1665" t="str">
         <v/>
@@ -38702,7 +38702,7 @@
         <v>adj</v>
       </c>
       <c r="C1666" t="str">
-        <v>לפתוח</v>
+        <v>פתוח</v>
       </c>
       <c r="D1666" t="str">
         <v/>
@@ -38771,7 +38771,7 @@
         <v>adj</v>
       </c>
       <c r="C1669" t="str">
-        <v>shenkin מול הפארק</v>
+        <v>הפוך</v>
       </c>
       <c r="D1669" t="str">
         <v/>
@@ -38817,7 +38817,7 @@
         <v/>
       </c>
       <c r="C1671" t="str">
-        <v>או שלא..</v>
+        <v>או לא</v>
       </c>
       <c r="D1671" t="str">
         <v/>
@@ -38840,7 +38840,7 @@
         <v>v, n</v>
       </c>
       <c r="C1672" t="str">
-        <v>הזמנה</v>
+        <v>סדר</v>
       </c>
       <c r="D1672" t="str">
         <v/>
@@ -38863,7 +38863,7 @@
         <v>n</v>
       </c>
       <c r="C1673" t="str">
-        <v>הזמנה</v>
+        <v>סדר</v>
       </c>
       <c r="D1673" t="str">
         <v/>
@@ -38955,7 +38955,7 @@
         <v>adv</v>
       </c>
       <c r="C1677" t="str">
-        <v>נשלל</v>
+        <v>החוצה , כבוי )</v>
       </c>
       <c r="D1677" t="str">
         <v/>
@@ -39024,7 +39024,7 @@
         <v/>
       </c>
       <c r="C1680" t="str">
-        <v>מחוסר עבודה</v>
+        <v>ללא עבודה</v>
       </c>
       <c r="D1680" t="str">
         <v/>
@@ -39047,7 +39047,7 @@
         <v>adv, adj</v>
       </c>
       <c r="C1681" t="str">
-        <v>חיצוני</v>
+        <v>בחוץ</v>
       </c>
       <c r="D1681" t="str">
         <v/>
@@ -39116,7 +39116,7 @@
         <v>adv</v>
       </c>
       <c r="C1684" t="str">
-        <v>יותר מאשר</v>
+        <v>נגמר</v>
       </c>
       <c r="D1684" t="str">
         <v/>
@@ -39162,7 +39162,7 @@
         <v>v</v>
       </c>
       <c r="C1686" t="str">
-        <v>מפרט</v>
+        <v>משלו</v>
       </c>
       <c r="D1686" t="str">
         <v>owner</v>
@@ -39185,7 +39185,7 @@
         <v>n</v>
       </c>
       <c r="C1687" t="str">
-        <v>מחבת</v>
+        <v>פאן</v>
       </c>
       <c r="D1687" t="str">
         <v/>
@@ -39231,7 +39231,7 @@
         <v>n</v>
       </c>
       <c r="C1689" t="str">
-        <v>פסקה</v>
+        <v>סעיף</v>
       </c>
       <c r="D1689" t="str">
         <v/>
@@ -39277,7 +39277,7 @@
         <v>n</v>
       </c>
       <c r="C1691" t="str">
-        <v>בית הנבחרים</v>
+        <v>פרלמנט</v>
       </c>
       <c r="D1691" t="str">
         <v/>
@@ -39300,7 +39300,7 @@
         <v>n</v>
       </c>
       <c r="C1692" t="str">
-        <v>שותפה</v>
+        <v>בן זוג</v>
       </c>
       <c r="D1692" t="str">
         <v/>
@@ -39323,7 +39323,7 @@
         <v>n</v>
       </c>
       <c r="C1693" t="str">
-        <v>מסיבה</v>
+        <v>מפלגה</v>
       </c>
       <c r="D1693" t="str">
         <v/>
@@ -39346,7 +39346,7 @@
         <v>v</v>
       </c>
       <c r="C1694" t="str">
-        <v>הלך'הָלַךְ</v>
+        <v>להעביר</v>
       </c>
       <c r="D1694" t="str">
         <v/>
@@ -39369,7 +39369,7 @@
         <v/>
       </c>
       <c r="C1695" t="str">
-        <v>לעבור/מעל/דרך וכו'</v>
+        <v>לעבור/מעבר/דרך וכו'</v>
       </c>
       <c r="D1695" t="str">
         <v/>
@@ -39415,7 +39415,7 @@
         <v>v</v>
       </c>
       <c r="C1697" t="str">
-        <v>לשלם</v>
+        <v>שכר</v>
       </c>
       <c r="D1697" t="str">
         <v>payment</v>
@@ -39438,7 +39438,7 @@
         <v/>
       </c>
       <c r="C1698" t="str">
-        <v>לשים לב (למשהו)</v>
+        <v>שים לב</v>
       </c>
       <c r="D1698" t="str">
         <v/>
@@ -39484,7 +39484,7 @@
         <v>prep</v>
       </c>
       <c r="C1700" t="str">
-        <v>ל-</v>
+        <v>לכל</v>
       </c>
       <c r="D1700" t="str">
         <v/>
@@ -39530,7 +39530,7 @@
         <v>adv</v>
       </c>
       <c r="C1702" t="str">
-        <v>לא מושלם</v>
+        <v>בצורה מושלמת</v>
       </c>
       <c r="D1702" t="str">
         <v/>
@@ -39553,7 +39553,7 @@
         <v>v</v>
       </c>
       <c r="C1703" t="str">
-        <v>לְבַצֵעַ</v>
+        <v>להופיע</v>
       </c>
       <c r="D1703" t="str">
         <v>performer</v>
@@ -39622,7 +39622,7 @@
         <v>v</v>
       </c>
       <c r="C1706" t="str">
-        <v>היתר*</v>
+        <v>להתיר</v>
       </c>
       <c r="D1706" t="str">
         <v>permission</v>
@@ -39668,7 +39668,7 @@
         <v>n</v>
       </c>
       <c r="C1708" t="str">
-        <v>מכונת צילום</v>
+        <v>לצלם</v>
       </c>
       <c r="D1708" t="str">
         <v>photocopier photocopied</v>
@@ -39714,7 +39714,7 @@
         <v>n</v>
       </c>
       <c r="C1710" t="str">
-        <v>ביטוי</v>
+        <v>משפט</v>
       </c>
       <c r="D1710" t="str">
         <v/>
@@ -39760,7 +39760,7 @@
         <v>n</v>
       </c>
       <c r="C1712" t="str">
-        <v>ערימה</v>
+        <v>ערמה</v>
       </c>
       <c r="D1712" t="str">
         <v/>
@@ -39783,7 +39783,7 @@
         <v>n</v>
       </c>
       <c r="C1713" t="str">
-        <v>צנרת</v>
+        <v>מקטרת</v>
       </c>
       <c r="D1713" t="str">
         <v/>
@@ -39806,7 +39806,7 @@
         <v>n</v>
       </c>
       <c r="C1714" t="str">
-        <v>להניח</v>
+        <v>מקום</v>
       </c>
       <c r="D1714" t="str">
         <v/>
@@ -39829,7 +39829,7 @@
         <v>adj</v>
       </c>
       <c r="C1715" t="str">
-        <v>פשוט</v>
+        <v>רגיל</v>
       </c>
       <c r="D1715" t="str">
         <v/>
@@ -39875,7 +39875,7 @@
         <v>n, v</v>
       </c>
       <c r="C1717" t="str">
-        <v>לשחק</v>
+        <v>משחק</v>
       </c>
       <c r="D1717" t="str">
         <v/>
@@ -39898,7 +39898,7 @@
         <v/>
       </c>
       <c r="C1718" t="str">
-        <v>לעשות בדיחה/תעלול על מישהו</v>
+        <v>לשחק בדיחה/טריק על sb</v>
       </c>
       <c r="D1718" t="str">
         <v/>
@@ -39921,7 +39921,7 @@
         <v/>
       </c>
       <c r="C1719" t="str">
-        <v>נעים להכיר אותך.</v>
+        <v>שמח לפגוש אותך</v>
       </c>
       <c r="D1719" t="str">
         <v/>
@@ -39944,7 +39944,7 @@
         <v>pron</v>
       </c>
       <c r="C1720" t="str">
-        <v>מספיק</v>
+        <v>הרבה</v>
       </c>
       <c r="D1720" t="str">
         <v/>
@@ -40082,7 +40082,7 @@
         <v>adj</v>
       </c>
       <c r="C1726" t="str">
-        <v>עני</v>
+        <v>מסכן</v>
       </c>
       <c r="D1726" t="str">
         <v/>
@@ -40174,7 +40174,7 @@
         <v>adv</v>
       </c>
       <c r="C1730" t="str">
-        <v>יתכן.</v>
+        <v>יתכן</v>
       </c>
       <c r="D1730" t="str">
         <v/>
@@ -40197,7 +40197,7 @@
         <v>v, n</v>
       </c>
       <c r="C1731" t="str">
-        <v>פוסט</v>
+        <v>פוסט )</v>
       </c>
       <c r="D1731" t="str">
         <v/>
@@ -40312,7 +40312,7 @@
         <v>adj</v>
       </c>
       <c r="C1736" t="str">
-        <v>מעשית</v>
+        <v>מעשי</v>
       </c>
       <c r="D1736" t="str">
         <v>practice</v>
@@ -40381,7 +40381,7 @@
         <v>adj</v>
       </c>
       <c r="C1739" t="str">
-        <v>הקודם</v>
+        <v>קודם</v>
       </c>
       <c r="D1739" t="str">
         <v>previously</v>
@@ -40404,7 +40404,7 @@
         <v>n</v>
       </c>
       <c r="C1740" t="str">
-        <v>פרינס</v>
+        <v>נסיך</v>
       </c>
       <c r="D1740" t="str">
         <v>princess</v>
@@ -40427,7 +40427,7 @@
         <v>v,n</v>
       </c>
       <c r="C1741" t="str">
-        <v>הדפיסי</v>
+        <v>הדפס</v>
       </c>
       <c r="D1741" t="str">
         <v>printer</v>
@@ -40450,7 +40450,7 @@
         <v>n</v>
       </c>
       <c r="C1742" t="str">
-        <v>פרוצדורה</v>
+        <v>תהליך</v>
       </c>
       <c r="D1742" t="str">
         <v/>
@@ -40473,7 +40473,7 @@
         <v>n</v>
       </c>
       <c r="C1743" t="str">
-        <v>רווח</v>
+        <v>להרויח</v>
       </c>
       <c r="D1743" t="str">
         <v/>
@@ -40519,7 +40519,7 @@
         <v>n</v>
       </c>
       <c r="C1745" t="str">
-        <v>בתהליך</v>
+        <v>התקדמות</v>
       </c>
       <c r="D1745" t="str">
         <v/>
@@ -40542,7 +40542,7 @@
         <v>v</v>
       </c>
       <c r="C1746" t="str">
-        <v>הגייה</v>
+        <v>לבטא</v>
       </c>
       <c r="D1746" t="str">
         <v>pronunciation</v>
@@ -40588,7 +40588,7 @@
         <v>n</v>
       </c>
       <c r="C1748" t="str">
-        <v>נכס</v>
+        <v>רכוש</v>
       </c>
       <c r="D1748" t="str">
         <v/>
@@ -40611,7 +40611,7 @@
         <v>v</v>
       </c>
       <c r="C1749" t="str">
-        <v>לְסַפֵּק.</v>
+        <v>לספק</v>
       </c>
       <c r="D1749" t="str">
         <v/>
@@ -40657,7 +40657,7 @@
         <v>v</v>
       </c>
       <c r="C1751" t="str">
-        <v>פרסום</v>
+        <v>לפרסם</v>
       </c>
       <c r="D1751" t="str">
         <v>publisher publication</v>
@@ -40680,7 +40680,7 @@
         <v/>
       </c>
       <c r="C1752" t="str">
-        <v>די הרבה</v>
+        <v>לא מעט</v>
       </c>
       <c r="D1752" t="str">
         <v/>
@@ -40703,7 +40703,7 @@
         <v/>
       </c>
       <c r="C1753" t="str">
-        <v>לא מעט / הרבה</v>
+        <v>לא מעט/הרבה</v>
       </c>
       <c r="D1753" t="str">
         <v/>
@@ -40726,7 +40726,7 @@
         <v/>
       </c>
       <c r="C1754" t="str">
-        <v>לא מעט זמן</v>
+        <v>די הרבה זמן</v>
       </c>
       <c r="D1754" t="str">
         <v/>
@@ -40749,7 +40749,7 @@
         <v>v</v>
       </c>
       <c r="C1755" t="str">
-        <v>להרים</v>
+        <v>להעלות</v>
       </c>
       <c r="D1755" t="str">
         <v/>
@@ -40795,7 +40795,7 @@
         <v>n</v>
       </c>
       <c r="C1757" t="str">
-        <v>דירוג</v>
+        <v>תעריף</v>
       </c>
       <c r="D1757" t="str">
         <v/>
@@ -40818,7 +40818,7 @@
         <v>n</v>
       </c>
       <c r="C1758" t="str">
-        <v>דירוג</v>
+        <v>תעריף</v>
       </c>
       <c r="D1758" t="str">
         <v/>
@@ -40841,7 +40841,7 @@
         <v>adv</v>
       </c>
       <c r="C1759" t="str">
-        <v>העדיפו :</v>
+        <v>אלא</v>
       </c>
       <c r="D1759" t="str">
         <v/>
@@ -40887,7 +40887,7 @@
         <v>adj</v>
       </c>
       <c r="C1761" t="str">
-        <v>מאוד (məód) (1)</v>
+        <v>אמיתי</v>
       </c>
       <c r="D1761" t="str">
         <v/>
@@ -40910,7 +40910,7 @@
         <v>n</v>
       </c>
       <c r="C1762" t="str">
-        <v>המציאות</v>
+        <v>מציאות</v>
       </c>
       <c r="D1762" t="str">
         <v/>
@@ -41025,7 +41025,7 @@
         <v>v</v>
       </c>
       <c r="C1767" t="str">
-        <v>שחזור</v>
+        <v>להתאושש</v>
       </c>
       <c r="D1767" t="str">
         <v>recovery</v>
@@ -41048,7 +41048,7 @@
         <v>v</v>
       </c>
       <c r="C1768" t="str">
-        <v>לסרב</v>
+        <v>אשפה</v>
       </c>
       <c r="D1768" t="str">
         <v/>
@@ -41071,7 +41071,7 @@
         <v>adj</v>
       </c>
       <c r="C1769" t="str">
-        <v>רגילים</v>
+        <v>רגיל</v>
       </c>
       <c r="D1769" t="str">
         <v>regularly</v>
@@ -41094,7 +41094,7 @@
         <v>n</v>
       </c>
       <c r="C1770" t="str">
-        <v>יחסי</v>
+        <v>קרוב משפחה</v>
       </c>
       <c r="D1770" t="str">
         <v>relation</v>
@@ -41117,7 +41117,7 @@
         <v/>
       </c>
       <c r="C1771" t="str">
-        <v>יחסית טוב/רע/זול וכו'.</v>
+        <v>יחסית טוב / רע / זול וכו'.</v>
       </c>
       <c r="D1771" t="str">
         <v/>
@@ -41140,7 +41140,7 @@
         <v>v, n</v>
       </c>
       <c r="C1772" t="str">
-        <v>לשחרר</v>
+        <v>שחרור</v>
       </c>
       <c r="D1772" t="str">
         <v/>
@@ -41163,7 +41163,7 @@
         <v/>
       </c>
       <c r="C1773" t="str">
-        <v>להזכיר לאדם משהו/דבר</v>
+        <v>להזכיר sb של sth/sb</v>
       </c>
       <c r="D1773" t="str">
         <v/>
@@ -41186,7 +41186,7 @@
         <v>n, v</v>
       </c>
       <c r="C1774" t="str">
-        <v>דוח</v>
+        <v>דווח</v>
       </c>
       <c r="D1774" t="str">
         <v/>
@@ -41232,7 +41232,7 @@
         <v>v</v>
       </c>
       <c r="C1776" t="str">
-        <v>חובה</v>
+        <v>לדרוש</v>
       </c>
       <c r="D1776" t="str">
         <v>requirement</v>
@@ -41255,7 +41255,7 @@
         <v>v</v>
       </c>
       <c r="C1777" t="str">
-        <v>עונה (m) - Oné)</v>
+        <v>להגיב</v>
       </c>
       <c r="D1777" t="str">
         <v>response</v>
@@ -41278,7 +41278,7 @@
         <v/>
       </c>
       <c r="C1778" t="str">
-        <v>תוצאה של משהו</v>
+        <v>התוצאה במקום</v>
       </c>
       <c r="D1778" t="str">
         <v/>
@@ -41301,7 +41301,7 @@
         <v>n</v>
       </c>
       <c r="C1779" t="str">
-        <v>תשלום</v>
+        <v>גמול</v>
       </c>
       <c r="D1779" t="str">
         <v/>
@@ -41324,7 +41324,7 @@
         <v>v</v>
       </c>
       <c r="C1780" t="str">
-        <v>לרכוב</v>
+        <v>נסיעה</v>
       </c>
       <c r="D1780" t="str">
         <v>rider</v>
@@ -41370,7 +41370,7 @@
         <v>v, n</v>
       </c>
       <c r="C1782" t="str">
-        <v>עליית מדד</v>
+        <v>לעלות</v>
       </c>
       <c r="D1782" t="str">
         <v/>
@@ -41393,7 +41393,7 @@
         <v>v, adj</v>
       </c>
       <c r="C1783" t="str">
-        <v>צלייה</v>
+        <v>צלי</v>
       </c>
       <c r="D1783" t="str">
         <v>roast</v>
@@ -41416,7 +41416,7 @@
         <v>n</v>
       </c>
       <c r="C1784" t="str">
-        <v>לגלגל</v>
+        <v>גליל</v>
       </c>
       <c r="D1784" t="str">
         <v/>
@@ -41485,7 +41485,7 @@
         <v>adj</v>
       </c>
       <c r="C1787" t="str">
-        <v>גס</v>
+        <v>מחוספס</v>
       </c>
       <c r="D1787" t="str">
         <v/>
@@ -41508,7 +41508,7 @@
         <v>n</v>
       </c>
       <c r="C1788" t="str">
-        <v>נתיב</v>
+        <v>מסלול</v>
       </c>
       <c r="D1788" t="str">
         <v/>
@@ -41554,7 +41554,7 @@
         <v>n</v>
       </c>
       <c r="C1790" t="str">
-        <v>בועות</v>
+        <v>גומי</v>
       </c>
       <c r="D1790" t="str">
         <v/>
@@ -41600,7 +41600,7 @@
         <v>v</v>
       </c>
       <c r="C1792" t="str">
-        <v>מפרש</v>
+        <v>להפליג</v>
       </c>
       <c r="D1792" t="str">
         <v>sailor</v>
@@ -41669,7 +41669,7 @@
         <v>v</v>
       </c>
       <c r="C1795" t="str">
-        <v>שמירה</v>
+        <v>לשמור</v>
       </c>
       <c r="D1795" t="str">
         <v/>
@@ -41692,7 +41692,7 @@
         <v>n</v>
       </c>
       <c r="C1796" t="str">
-        <v>חיסכונות</v>
+        <v>חיסכון</v>
       </c>
       <c r="D1796" t="str">
         <v/>
@@ -41761,7 +41761,7 @@
         <v>n</v>
       </c>
       <c r="C1799" t="str">
-        <v>סצינה</v>
+        <v>סצנה</v>
       </c>
       <c r="D1799" t="str">
         <v/>
@@ -41784,7 +41784,7 @@
         <v>n, v</v>
       </c>
       <c r="C1800" t="str">
-        <v>חיפוש</v>
+        <v>לחפש</v>
       </c>
       <c r="D1800" t="str">
         <v/>
@@ -41807,7 +41807,7 @@
         <v>adv</v>
       </c>
       <c r="C1801" t="str">
-        <v>שניה</v>
+        <v>שני</v>
       </c>
       <c r="D1801" t="str">
         <v>secondly secondary</v>
@@ -41853,7 +41853,7 @@
         <v>n</v>
       </c>
       <c r="C1803" t="str">
-        <v>אבטחה</v>
+        <v>בטחון</v>
       </c>
       <c r="D1803" t="str">
         <v>secure</v>
@@ -41899,7 +41899,7 @@
         <v/>
       </c>
       <c r="C1805" t="str">
-        <v>לראות משהו/אדם</v>
+        <v>ראה ל sth/sb</v>
       </c>
       <c r="D1805" t="str">
         <v/>
@@ -41945,7 +41945,7 @@
         <v>v</v>
       </c>
       <c r="C1807" t="str">
-        <v>חפש</v>
+        <v>לחפש</v>
       </c>
       <c r="D1807" t="str">
         <v/>
@@ -41968,7 +41968,7 @@
         <v/>
       </c>
       <c r="C1808" t="str">
-        <v>נראה כמו/כאילו/כדי</v>
+        <v>נראה כמו/כאילו/ל</v>
       </c>
       <c r="D1808" t="str">
         <v/>
@@ -41991,7 +41991,7 @@
         <v/>
       </c>
       <c r="C1809" t="str">
-        <v>בשירות עצמי</v>
+        <v>שירות עצמי</v>
       </c>
       <c r="D1809" t="str">
         <v/>
@@ -42014,7 +42014,7 @@
         <v/>
       </c>
       <c r="C1810" t="str">
-        <v>לשלוח משהו בחזרה או לשלוח משהו בחזרה</v>
+        <v>שלח sth בחזרה או שלח בחזרה sth</v>
       </c>
       <c r="D1810" t="str">
         <v/>
@@ -42083,7 +42083,7 @@
         <v>n</v>
       </c>
       <c r="C1813" t="str">
-        <v>הפעלה</v>
+        <v>מושב</v>
       </c>
       <c r="D1813" t="str">
         <v/>
@@ -42106,7 +42106,7 @@
         <v/>
       </c>
       <c r="C1814" t="str">
-        <v>לקבוע תאריך/שעה (למשהו)</v>
+        <v>להגדיר תאריך/שעה</v>
       </c>
       <c r="D1814" t="str">
         <v/>
@@ -42129,7 +42129,7 @@
         <v/>
       </c>
       <c r="C1815" t="str">
-        <v>לצאת לדרך / לצאת לדרך</v>
+        <v>לצאת לדרך/לצאת לדרך</v>
       </c>
       <c r="D1815" t="str">
         <v/>
@@ -42152,7 +42152,7 @@
         <v/>
       </c>
       <c r="C1816" t="str">
-        <v>ערוך את השולחן</v>
+        <v>לערוך את השולחן</v>
       </c>
       <c r="D1816" t="str">
         <v/>
@@ -42175,7 +42175,7 @@
         <v>v</v>
       </c>
       <c r="C1817" t="str">
-        <v>תפירה</v>
+        <v>לתפור</v>
       </c>
       <c r="D1817" t="str">
         <v/>
@@ -42244,7 +42244,7 @@
         <v>adj</v>
       </c>
       <c r="C1820" t="str">
-        <v>חדות</v>
+        <v>חד</v>
       </c>
       <c r="D1820" t="str">
         <v/>
@@ -42267,7 +42267,7 @@
         <v>v</v>
       </c>
       <c r="C1821" t="str">
-        <v>ניצוצות</v>
+        <v>צחצוח</v>
       </c>
       <c r="D1821" t="str">
         <v/>
@@ -42313,7 +42313,7 @@
         <v>v</v>
       </c>
       <c r="C1823" t="str">
-        <v>'שוט'...</v>
+        <v>לירות</v>
       </c>
       <c r="D1823" t="str">
         <v>shot</v>
@@ -42336,7 +42336,7 @@
         <v>v</v>
       </c>
       <c r="C1824" t="str">
-        <v>חנות</v>
+        <v>לקנות</v>
       </c>
       <c r="D1824" t="str">
         <v/>
@@ -42359,7 +42359,7 @@
         <v/>
       </c>
       <c r="C1825" t="str">
-        <v>מוכר בחנות</v>
+        <v>עוזר בחנות</v>
       </c>
       <c r="D1825" t="str">
         <v/>
@@ -42382,7 +42382,7 @@
         <v/>
       </c>
       <c r="C1826" t="str">
-        <v>זמן קצר לאחר מכן; זמן קצר לאחר / לפני משהו</v>
+        <v>זמן קצר לאחר מכן; זמן קצר אחרי/לפני ה'</v>
       </c>
       <c r="D1826" t="str">
         <v/>
@@ -42428,7 +42428,7 @@
         <v>n</v>
       </c>
       <c r="C1828" t="str">
-        <v>להתקלח</v>
+        <v>מקלחת</v>
       </c>
       <c r="D1828" t="str">
         <v/>
@@ -42520,7 +42520,7 @@
         <v>adj</v>
       </c>
       <c r="C1832" t="str">
-        <v>יחיד</v>
+        <v>רווק</v>
       </c>
       <c r="D1832" t="str">
         <v/>
@@ -42543,7 +42543,7 @@
         <v/>
       </c>
       <c r="C1833" t="str">
-        <v>הורה יחידני</v>
+        <v>הורה יחיד</v>
       </c>
       <c r="D1833" t="str">
         <v/>
@@ -42566,7 +42566,7 @@
         <v>adj</v>
       </c>
       <c r="C1834" t="str">
-        <v>יחידה</v>
+        <v>יחיד</v>
       </c>
       <c r="D1834" t="str">
         <v/>
@@ -42658,7 +42658,7 @@
         <v>adv</v>
       </c>
       <c r="C1838" t="str">
-        <v>אז.</v>
+        <v>אז</v>
       </c>
       <c r="D1838" t="str">
         <v/>
@@ -42704,7 +42704,7 @@
         <v/>
       </c>
       <c r="C1840" t="str">
-        <v>רשת חברתית</v>
+        <v>מדיה חברתית</v>
       </c>
       <c r="D1840" t="str">
         <v/>
@@ -42727,7 +42727,7 @@
         <v/>
       </c>
       <c r="C1841" t="str">
-        <v>רשתות חברתיות</v>
+        <v>רשת חברתית</v>
       </c>
       <c r="D1841" t="str">
         <v/>
@@ -42750,7 +42750,7 @@
         <v>n</v>
       </c>
       <c r="C1842" t="str">
-        <v>גילדה</v>
+        <v>חברה</v>
       </c>
       <c r="D1842" t="str">
         <v>social</v>
@@ -42773,7 +42773,7 @@
         <v>adj</v>
       </c>
       <c r="C1843" t="str">
-        <v>זריקה רכה</v>
+        <v>רך</v>
       </c>
       <c r="D1843" t="str">
         <v/>
@@ -42796,7 +42796,7 @@
         <v>adj</v>
       </c>
       <c r="C1844" t="str">
-        <v>אחיד</v>
+        <v>מוצק</v>
       </c>
       <c r="D1844" t="str">
         <v/>
@@ -42842,7 +42842,7 @@
         <v>adv</v>
       </c>
       <c r="C1846" t="str">
-        <v>במידה מסוימת</v>
+        <v>קצת</v>
       </c>
       <c r="D1846" t="str">
         <v/>
@@ -42888,7 +42888,7 @@
         <v>n</v>
       </c>
       <c r="C1848" t="str">
-        <v>נפש.</v>
+        <v>נפש</v>
       </c>
       <c r="D1848" t="str">
         <v/>
@@ -42934,7 +42934,7 @@
         <v/>
       </c>
       <c r="C1850" t="str">
-        <v>נשמע/ים טוב/מעניין/מוזר וכו'.</v>
+        <v>צלילים טובים / מעניינים / מוזרים וכו'.</v>
       </c>
       <c r="D1850" t="str">
         <v/>
@@ -42957,7 +42957,7 @@
         <v>n</v>
       </c>
       <c r="C1851" t="str">
-        <v>וולס.</v>
+        <v>מקור</v>
       </c>
       <c r="D1851" t="str">
         <v/>
@@ -42980,7 +42980,7 @@
         <v>adj</v>
       </c>
       <c r="C1852" t="str">
-        <v>דרום אמריקהncamerica. kgm</v>
+        <v>דרומי</v>
       </c>
       <c r="D1852" t="str">
         <v/>
@@ -43003,7 +43003,7 @@
         <v/>
       </c>
       <c r="C1853" t="str">
-        <v>קורט</v>
+        <v>נוסף</v>
       </c>
       <c r="D1853" t="str">
         <v>spare</v>
@@ -43072,7 +43072,7 @@
         <v>n</v>
       </c>
       <c r="C1856" t="str">
-        <v>תבלין</v>
+        <v>לתבל</v>
       </c>
       <c r="D1856" t="str">
         <v>spicy</v>
@@ -43118,7 +43118,7 @@
         <v>n</v>
       </c>
       <c r="C1858" t="str">
-        <v>מוקדם.</v>
+        <v>שלב</v>
       </c>
       <c r="D1858" t="str">
         <v/>
@@ -43141,7 +43141,7 @@
         <v>n</v>
       </c>
       <c r="C1859" t="str">
-        <v>רגיל</v>
+        <v>סטנדרטי</v>
       </c>
       <c r="D1859" t="str">
         <v/>
@@ -43302,7 +43302,7 @@
         <v>v</v>
       </c>
       <c r="C1866" t="str">
-        <v>לערבב</v>
+        <v>לרגש</v>
       </c>
       <c r="D1866" t="str">
         <v/>
@@ -43325,7 +43325,7 @@
         <v>v</v>
       </c>
       <c r="C1867" t="str">
-        <v>חנות</v>
+        <v>לאחסן</v>
       </c>
       <c r="D1867" t="str">
         <v>storage</v>
@@ -43371,7 +43371,7 @@
         <v>n</v>
       </c>
       <c r="C1869" t="str">
-        <v>תפעולית</v>
+        <v>אסטרטגיה</v>
       </c>
       <c r="D1869" t="str">
         <v>strategic</v>
@@ -43509,7 +43509,7 @@
         <v>n</v>
       </c>
       <c r="C1875" t="str">
-        <v>מוחשי</v>
+        <v>דברים</v>
       </c>
       <c r="D1875" t="str">
         <v/>
@@ -43532,7 +43532,7 @@
         <v>adj</v>
       </c>
       <c r="C1876" t="str">
-        <v>טיפש</v>
+        <v>מטופש</v>
       </c>
       <c r="D1876" t="str">
         <v/>
@@ -43578,7 +43578,7 @@
         <v>n</v>
       </c>
       <c r="C1878" t="str">
-        <v>בוצע</v>
+        <v>הצלחה</v>
       </c>
       <c r="D1878" t="str">
         <v>successful successfully</v>
@@ -43624,7 +43624,7 @@
         <v>adj</v>
       </c>
       <c r="C1880" t="str">
-        <v>פתאוםי</v>
+        <v>פתאומי</v>
       </c>
       <c r="D1880" t="str">
         <v>suddenly</v>
@@ -43670,7 +43670,7 @@
         <v>adj</v>
       </c>
       <c r="C1882" t="str">
-        <v>שמתאימות</v>
+        <v>מתאים</v>
       </c>
       <c r="D1882" t="str">
         <v/>
@@ -43739,7 +43739,7 @@
         <v>n</v>
       </c>
       <c r="C1885" t="str">
-        <v>שקיעה.</v>
+        <v>שקיעת השמש</v>
       </c>
       <c r="D1885" t="str">
         <v/>
@@ -43785,7 +43785,7 @@
         <v>v, n</v>
       </c>
       <c r="C1887" t="str">
-        <v>אספקה:</v>
+        <v>לספק</v>
       </c>
       <c r="D1887" t="str">
         <v/>
@@ -43831,7 +43831,7 @@
         <v>v</v>
       </c>
       <c r="C1889" t="str">
-        <v>סביבה</v>
+        <v>להקיף</v>
       </c>
       <c r="D1889" t="str">
         <v/>
@@ -43854,7 +43854,7 @@
         <v>v</v>
       </c>
       <c r="C1890" t="str">
-        <v>סנוניתיים</v>
+        <v>לבלוע</v>
       </c>
       <c r="D1890" t="str">
         <v/>
@@ -43877,7 +43877,7 @@
         <v>v</v>
       </c>
       <c r="C1891" t="str">
-        <v>בורר</v>
+        <v>להחליף</v>
       </c>
       <c r="D1891" t="str">
         <v/>
@@ -43900,7 +43900,7 @@
         <v/>
       </c>
       <c r="C1892" t="str">
-        <v>לכבות משהו או לכבות משהו / להדליק משהו או להדליק משהו</v>
+        <v>כבה sth או כבה sth / הפעל sth או הפעל sth</v>
       </c>
       <c r="D1892" t="str">
         <v/>
@@ -44015,7 +44015,7 @@
         <v/>
       </c>
       <c r="C1897" t="str">
-        <v>קח נשימה עמוקה.</v>
+        <v>לקחת נשימה עמוקה</v>
       </c>
       <c r="D1897" t="str">
         <v/>
@@ -44038,7 +44038,7 @@
         <v/>
       </c>
       <c r="C1898" t="str">
-        <v>לטפל באדם/בכל דבר</v>
+        <v>לטפל sb/sth</v>
       </c>
       <c r="D1898" t="str">
         <v/>
@@ -44084,7 +44084,7 @@
         <v/>
       </c>
       <c r="C1900" t="str">
-        <v>להסיר</v>
+        <v>להמריא</v>
       </c>
       <c r="D1900" t="str">
         <v/>
@@ -44107,7 +44107,7 @@
         <v/>
       </c>
       <c r="C1901" t="str">
-        <v>לקחת משהו או לקחת משהו</v>
+        <v>לקחת sth או לקחת sth</v>
       </c>
       <c r="D1901" t="str">
         <v/>
@@ -44130,7 +44130,7 @@
         <v>n</v>
       </c>
       <c r="C1902" t="str">
-        <v>פיתוח</v>
+        <v>כשרון</v>
       </c>
       <c r="D1902" t="str">
         <v>talented</v>
@@ -44153,7 +44153,7 @@
         <v>n</v>
       </c>
       <c r="C1903" t="str">
-        <v>לדבר</v>
+        <v>שיחה</v>
       </c>
       <c r="D1903" t="str">
         <v/>
@@ -44222,7 +44222,7 @@
         <v>n</v>
       </c>
       <c r="C1906" t="str">
-        <v>מיסים</v>
+        <v>מס</v>
       </c>
       <c r="D1906" t="str">
         <v/>
@@ -44291,7 +44291,7 @@
         <v>n</v>
       </c>
       <c r="C1909" t="str">
-        <v>טלקומונייקציה</v>
+        <v>תקשורת</v>
       </c>
       <c r="D1909" t="str">
         <v/>
@@ -44383,7 +44383,7 @@
         <v>n</v>
       </c>
       <c r="C1913" t="str">
-        <v>&amp; זמן:</v>
+        <v>זמן</v>
       </c>
       <c r="D1913" t="str">
         <v/>
@@ -44452,7 +44452,7 @@
         <v>adj</v>
       </c>
       <c r="C1916" t="str">
-        <v>נפלא!</v>
+        <v>מצוין</v>
       </c>
       <c r="D1916" t="str">
         <v/>
@@ -44475,7 +44475,7 @@
         <v>n, v</v>
       </c>
       <c r="C1917" t="str">
-        <v>מבחן</v>
+        <v>בדיקה</v>
       </c>
       <c r="D1917" t="str">
         <v/>
@@ -44498,7 +44498,7 @@
         <v>det</v>
       </c>
       <c r="C1918" t="str">
-        <v>בתאריך</v>
+        <v>את</v>
       </c>
       <c r="D1918" t="str">
         <v/>
@@ -44521,7 +44521,7 @@
         <v/>
       </c>
       <c r="C1919" t="str">
-        <v>דין:</v>
+        <v>החוק</v>
       </c>
       <c r="D1919" t="str">
         <v/>
@@ -44544,7 +44544,7 @@
         <v/>
       </c>
       <c r="C1920" t="str">
-        <v>ביום/שבוע אחר וכו'.</v>
+        <v>יום/שבוע אחר וכו'.</v>
       </c>
       <c r="D1920" t="str">
         <v/>
@@ -44613,7 +44613,7 @@
         <v/>
       </c>
       <c r="C1923" t="str">
-        <v>אותו הדבר</v>
+        <v>אותו דבר</v>
       </c>
       <c r="D1923" t="str">
         <v/>
@@ -44636,7 +44636,7 @@
         <v/>
       </c>
       <c r="C1924" t="str">
-        <v>המראות</v>
+        <v>את המראות</v>
       </c>
       <c r="D1924" t="str">
         <v/>
@@ -44682,7 +44682,7 @@
         <v>adv</v>
       </c>
       <c r="C1926" t="str">
-        <v>אז</v>
+        <v>ואז</v>
       </c>
       <c r="D1926" t="str">
         <v/>
@@ -44705,7 +44705,7 @@
         <v/>
       </c>
       <c r="C1927" t="str">
-        <v>בימים אלו</v>
+        <v>בימינו</v>
       </c>
       <c r="D1927" t="str">
         <v/>
@@ -44751,7 +44751,7 @@
         <v>n</v>
       </c>
       <c r="C1929" t="str">
-        <v>הדברים האלה.</v>
+        <v>דברים</v>
       </c>
       <c r="D1929" t="str">
         <v/>
@@ -44774,7 +44774,7 @@
         <v/>
       </c>
       <c r="C1930" t="str">
-        <v>דברים כאלה.</v>
+        <v>דברים כאלה</v>
       </c>
       <c r="D1930" t="str">
         <v/>
@@ -44843,7 +44843,7 @@
         <v>conj, adv</v>
       </c>
       <c r="C1933" t="str">
-        <v>למרות זאת</v>
+        <v>אמנם</v>
       </c>
       <c r="D1933" t="str">
         <v/>
@@ -44866,7 +44866,7 @@
         <v>n</v>
       </c>
       <c r="C1934" t="str">
-        <v>תבריג</v>
+        <v>פתיל</v>
       </c>
       <c r="D1934" t="str">
         <v/>
@@ -44889,7 +44889,7 @@
         <v>prep</v>
       </c>
       <c r="C1935" t="str">
-        <v>מילת יחס</v>
+        <v>דרך</v>
       </c>
       <c r="D1935" t="str">
         <v/>
@@ -45004,7 +45004,7 @@
         <v>prep</v>
       </c>
       <c r="C1940" t="str">
-        <v>אֶל</v>
+        <v>כדי</v>
       </c>
       <c r="D1940" t="str">
         <v/>
@@ -45027,7 +45027,7 @@
         <v/>
       </c>
       <c r="C1941" t="str">
-        <v>ולמען האמת,</v>
+        <v>למען האמת</v>
       </c>
       <c r="D1941" t="str">
         <v/>
@@ -45073,7 +45073,7 @@
         <v>n</v>
       </c>
       <c r="C1943" t="str">
-        <v>תו</v>
+        <v>טון</v>
       </c>
       <c r="D1943" t="str">
         <v/>
@@ -45096,7 +45096,7 @@
         <v>n</v>
       </c>
       <c r="C1944" t="str">
-        <v>כלים</v>
+        <v>כלי</v>
       </c>
       <c r="D1944" t="str">
         <v/>
@@ -45119,7 +45119,7 @@
         <v>n</v>
       </c>
       <c r="C1945" t="str">
-        <v>סַך הַכֹּל</v>
+        <v>סה"כ</v>
       </c>
       <c r="D1945" t="str">
         <v/>
@@ -45211,7 +45211,7 @@
         <v>v</v>
       </c>
       <c r="C1949" t="str">
-        <v>הזזה</v>
+        <v>לתרגם</v>
       </c>
       <c r="D1949" t="str">
         <v>translation translator</v>
@@ -45280,7 +45280,7 @@
         <v>n</v>
       </c>
       <c r="C1952" t="str">
-        <v>ש"ע) ניסיון</v>
+        <v>משפט</v>
       </c>
       <c r="D1952" t="str">
         <v/>
@@ -45326,7 +45326,7 @@
         <v/>
       </c>
       <c r="C1954" t="str">
-        <v>לנסות משהו או לנסות משהו</v>
+        <v>נסה sth או נסה sth out</v>
       </c>
       <c r="D1954" t="str">
         <v/>
@@ -45395,7 +45395,7 @@
         <v/>
       </c>
       <c r="C1957" t="str">
-        <v>להנמיך משהו או להנמיך משהו</v>
+        <v>להוריד sth או להוריד sth למטה</v>
       </c>
       <c r="D1957" t="str">
         <v/>
@@ -45418,7 +45418,7 @@
         <v>n</v>
       </c>
       <c r="C1958" t="str">
-        <v>לצייץ</v>
+        <v>ציוץ</v>
       </c>
       <c r="D1958" t="str">
         <v/>
@@ -45441,7 +45441,7 @@
         <v>v</v>
       </c>
       <c r="C1959" t="str">
-        <v>סוג</v>
+        <v>הקלד</v>
       </c>
       <c r="D1959" t="str">
         <v/>
@@ -45487,7 +45487,7 @@
         <v>prep</v>
       </c>
       <c r="C1961" t="str">
-        <v>מתחת ל:</v>
+        <v>מתחת</v>
       </c>
       <c r="D1961" t="str">
         <v/>
@@ -45510,7 +45510,7 @@
         <v>adj, adv, n</v>
       </c>
       <c r="C1962" t="str">
-        <v>מתחת לקרקע</v>
+        <v>מחתרת</v>
       </c>
       <c r="D1962" t="str">
         <v/>
@@ -45533,7 +45533,7 @@
         <v>v</v>
       </c>
       <c r="C1963" t="str">
-        <v>קו תחתי</v>
+        <v>קו תחתון</v>
       </c>
       <c r="D1963" t="str">
         <v/>
@@ -45671,7 +45671,7 @@
         <v>adj</v>
       </c>
       <c r="C1969" t="str">
-        <v>אותיות דפוס</v>
+        <v>עליון</v>
       </c>
       <c r="D1969" t="str">
         <v/>
@@ -45694,7 +45694,7 @@
         <v>v, adj</v>
       </c>
       <c r="C1970" t="str">
-        <v>מודאג</v>
+        <v>לשבש</v>
       </c>
       <c r="D1970" t="str">
         <v/>
@@ -45740,7 +45740,7 @@
         <v/>
       </c>
       <c r="C1972" t="str">
-        <v>מעודכן/מעודכן</v>
+        <v>עדכני/עדכני</v>
       </c>
       <c r="D1972" t="str">
         <v/>
@@ -45901,7 +45901,7 @@
         <v>n, adj</v>
       </c>
       <c r="C1979" t="str">
-        <v>צמחונות</v>
+        <v>צמחוני</v>
       </c>
       <c r="D1979" t="str">
         <v/>
@@ -45970,7 +45970,7 @@
         <v>n</v>
       </c>
       <c r="C1982" t="str">
-        <v>במשפחה)</v>
+        <v>אלימות</v>
       </c>
       <c r="D1982" t="str">
         <v>violent</v>
@@ -45993,7 +45993,7 @@
         <v>adj</v>
       </c>
       <c r="C1983" t="str">
-        <v>נְגִיפִי</v>
+        <v>ויראלי</v>
       </c>
       <c r="D1983" t="str">
         <v/>
@@ -46039,7 +46039,7 @@
         <v>n</v>
       </c>
       <c r="C1985" t="str">
-        <v>לומא</v>
+        <v>חזון</v>
       </c>
       <c r="D1985" t="str">
         <v/>
@@ -46062,7 +46062,7 @@
         <v>n</v>
       </c>
       <c r="C1986" t="str">
-        <v>מתנדבים</v>
+        <v>להתנדב</v>
       </c>
       <c r="D1986" t="str">
         <v>voluntary</v>
@@ -46085,7 +46085,7 @@
         <v/>
       </c>
       <c r="C1987" t="str">
-        <v>ללכת הביתה/למשהו</v>
+        <v>ללכת sb הביתה / ל sth</v>
       </c>
       <c r="D1987" t="str">
         <v/>
@@ -46131,7 +46131,7 @@
         <v>n</v>
       </c>
       <c r="C1989" t="str">
-        <v>אשפה</v>
+        <v>פסולת</v>
       </c>
       <c r="D1989" t="str">
         <v/>
@@ -46154,7 +46154,7 @@
         <v>adj</v>
       </c>
       <c r="C1990" t="str">
-        <v>&lt;g id="8581"&gt;חלש&lt;/g&gt;&lt;g id="8584"&gt;.&lt;/g&gt;</v>
+        <v>חלש</v>
       </c>
       <c r="D1990" t="str">
         <v/>
@@ -46177,7 +46177,7 @@
         <v>n</v>
       </c>
       <c r="C1991" t="str">
-        <v>טהור</v>
+        <v>חתונה</v>
       </c>
       <c r="D1991" t="str">
         <v/>
@@ -46223,7 +46223,7 @@
         <v>adj</v>
       </c>
       <c r="C1993" t="str">
-        <v>מארקהsouthamerica. kgm</v>
+        <v>מערבי</v>
       </c>
       <c r="D1993" t="str">
         <v/>
@@ -46246,7 +46246,7 @@
         <v/>
       </c>
       <c r="C1994" t="str">
-        <v>מה לגבי...?</v>
+        <v>מה עם...?</v>
       </c>
       <c r="D1994" t="str">
         <v/>
@@ -46269,7 +46269,7 @@
         <v/>
       </c>
       <c r="C1995" t="str">
-        <v>הפכה למנהיגת הקבוצה הנוכחית.</v>
+        <v>מה אם…?</v>
       </c>
       <c r="D1995" t="str">
         <v/>
@@ -46292,7 +46292,7 @@
         <v/>
       </c>
       <c r="C1996" t="str">
-        <v>מה המצב?</v>
+        <v>מה קורה?</v>
       </c>
       <c r="D1996" t="str">
         <v/>
@@ -46315,7 +46315,7 @@
         <v>det, pron</v>
       </c>
       <c r="C1997" t="str">
-        <v>אֵיזֶה</v>
+        <v>אשר</v>
       </c>
       <c r="D1997" t="str">
         <v/>
@@ -46407,7 +46407,7 @@
         <v>v, n</v>
       </c>
       <c r="C2001" t="str">
-        <v>נקה</v>
+        <v>לנגב</v>
       </c>
       <c r="D2001" t="str">
         <v/>
@@ -46430,7 +46430,7 @@
         <v/>
       </c>
       <c r="C2002" t="str">
-        <v>מאחל לך בהצלחה</v>
+        <v>מאחל sb בהצלחה</v>
       </c>
       <c r="D2002" t="str">
         <v/>
@@ -46453,7 +46453,7 @@
         <v/>
       </c>
       <c r="C2003" t="str">
-        <v>בעזרתו של משהו</v>
+        <v>בעזרת sth</v>
       </c>
       <c r="D2003" t="str">
         <v/>
@@ -46522,7 +46522,7 @@
         <v>n</v>
       </c>
       <c r="C2006" t="str">
-        <v>יער</v>
+        <v>עץ</v>
       </c>
       <c r="D2006" t="str">
         <v/>
@@ -46545,7 +46545,7 @@
         <v>n</v>
       </c>
       <c r="C2007" t="str">
-        <v>לעבוד</v>
+        <v>עבודה</v>
       </c>
       <c r="D2007" t="str">
         <v>working</v>
@@ -46568,7 +46568,7 @@
         <v>n</v>
       </c>
       <c r="C2008" t="str">
-        <v>לעבוד</v>
+        <v>עבודה</v>
       </c>
       <c r="D2008" t="str">
         <v/>
@@ -46591,7 +46591,7 @@
         <v/>
       </c>
       <c r="C2009" t="str">
-        <v>היה (מודל)</v>
+        <v>היה</v>
       </c>
       <c r="D2009" t="str">
         <v/>
@@ -46637,7 +46637,7 @@
         <v/>
       </c>
       <c r="C2011" t="str">
-        <v>אכפת לך?</v>
+        <v>אכפת לך...?</v>
       </c>
       <c r="D2011" t="str">
         <v/>
@@ -46706,7 +46706,7 @@
         <v>adj</v>
       </c>
       <c r="C2014" t="str">
-        <v>כתיבה</v>
+        <v>שבכתב</v>
       </c>
       <c r="D2014" t="str">
         <v>in writing</v>
@@ -46729,7 +46729,7 @@
         <v>conj</v>
       </c>
       <c r="C2015" t="str">
-        <v>בכל אופן</v>
+        <v>עדיין</v>
       </c>
       <c r="D2015" t="str">
         <v/>
@@ -46775,7 +46775,7 @@
         <v/>
       </c>
       <c r="C2017" t="str">
-        <v>אזור זמן</v>
+        <v>אזור</v>
       </c>
       <c r="D2017" t="str">
         <v/>
